--- a/templates/tabel-template.xlsx
+++ b/templates/tabel-template.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6563D6BE-BF36-4B25-B459-8234CD7F5669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC93A4D3-F461-49A1-A473-2ED8AAB75736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5009,7 +5009,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="278">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5278,23 +5278,42 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5311,77 +5330,32 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="57" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="58" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5389,134 +5363,8 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="41" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="42" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5540,6 +5388,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5571,38 +5422,179 @@
     <xf numFmtId="2" fontId="0" fillId="5" borderId="58" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="57" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="58" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5610,32 +5602,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5661,6 +5632,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5673,25 +5671,73 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5754,79 +5800,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -5837,7 +5810,14 @@
     <cellStyle name="Обычный_ПК 2 Дагестан" xfId="4" xr:uid="{1E2D5320-D3D1-4DC8-B75C-9BA19B8CD367}"/>
     <cellStyle name="Финансовый 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5891,6 +5871,34 @@
       <fill>
         <patternFill>
           <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8511,199 +8519,199 @@
   <sheetData>
     <row r="1" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:25" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="224" t="s">
+      <c r="B2" s="214" t="s">
         <v>177</v>
       </c>
-      <c r="C2" s="225"/>
-      <c r="D2" s="225"/>
-      <c r="E2" s="225"/>
-      <c r="F2" s="225"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="225"/>
-      <c r="I2" s="225"/>
-      <c r="J2" s="225"/>
-      <c r="K2" s="225"/>
-      <c r="L2" s="225"/>
-      <c r="M2" s="225"/>
-      <c r="N2" s="225"/>
-      <c r="O2" s="225"/>
-      <c r="P2" s="225"/>
-      <c r="Q2" s="225"/>
-      <c r="R2" s="225"/>
-      <c r="S2" s="225"/>
-      <c r="T2" s="225"/>
-      <c r="U2" s="225"/>
-      <c r="V2" s="225"/>
-      <c r="W2" s="225"/>
-      <c r="X2" s="225"/>
-      <c r="Y2" s="226"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
+      <c r="M2" s="215"/>
+      <c r="N2" s="215"/>
+      <c r="O2" s="215"/>
+      <c r="P2" s="215"/>
+      <c r="Q2" s="215"/>
+      <c r="R2" s="215"/>
+      <c r="S2" s="215"/>
+      <c r="T2" s="215"/>
+      <c r="U2" s="215"/>
+      <c r="V2" s="215"/>
+      <c r="W2" s="215"/>
+      <c r="X2" s="215"/>
+      <c r="Y2" s="216"/>
     </row>
     <row r="3" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B4" s="223" t="s">
+      <c r="B4" s="209" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="223"/>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="223"/>
-      <c r="I4" s="223"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="223"/>
-      <c r="M4" s="223"/>
-      <c r="N4" s="223"/>
-      <c r="O4" s="223"/>
-      <c r="P4" s="223"/>
-      <c r="Q4" s="223"/>
-      <c r="R4" s="223"/>
-      <c r="S4" s="223"/>
-      <c r="T4" s="223"/>
-      <c r="U4" s="223"/>
-      <c r="V4" s="223"/>
-      <c r="W4" s="223"/>
-      <c r="X4" s="223"/>
-      <c r="Y4" s="223"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="209"/>
+      <c r="K4" s="209"/>
+      <c r="L4" s="209"/>
+      <c r="M4" s="209"/>
+      <c r="N4" s="209"/>
+      <c r="O4" s="209"/>
+      <c r="P4" s="209"/>
+      <c r="Q4" s="209"/>
+      <c r="R4" s="209"/>
+      <c r="S4" s="209"/>
+      <c r="T4" s="209"/>
+      <c r="U4" s="209"/>
+      <c r="V4" s="209"/>
+      <c r="W4" s="209"/>
+      <c r="X4" s="209"/>
+      <c r="Y4" s="209"/>
     </row>
     <row r="5" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="231" t="s">
+      <c r="B6" s="221" t="s">
         <v>179</v>
       </c>
-      <c r="C6" s="231"/>
-      <c r="D6" s="231"/>
-      <c r="E6" s="231"/>
-      <c r="F6" s="231"/>
-      <c r="G6" s="231"/>
-      <c r="H6" s="231"/>
-      <c r="I6" s="231"/>
-      <c r="J6" s="231"/>
-      <c r="K6" s="231"/>
-      <c r="L6" s="231"/>
-      <c r="M6" s="231"/>
-      <c r="N6" s="231"/>
-      <c r="O6" s="231"/>
-      <c r="P6" s="231"/>
-      <c r="Q6" s="231"/>
-      <c r="R6" s="231"/>
-      <c r="S6" s="231"/>
-      <c r="T6" s="231"/>
-      <c r="U6" s="231"/>
-      <c r="V6" s="231"/>
-      <c r="W6" s="231"/>
-      <c r="X6" s="231"/>
-      <c r="Y6" s="231"/>
+      <c r="C6" s="221"/>
+      <c r="D6" s="221"/>
+      <c r="E6" s="221"/>
+      <c r="F6" s="221"/>
+      <c r="G6" s="221"/>
+      <c r="H6" s="221"/>
+      <c r="I6" s="221"/>
+      <c r="J6" s="221"/>
+      <c r="K6" s="221"/>
+      <c r="L6" s="221"/>
+      <c r="M6" s="221"/>
+      <c r="N6" s="221"/>
+      <c r="O6" s="221"/>
+      <c r="P6" s="221"/>
+      <c r="Q6" s="221"/>
+      <c r="R6" s="221"/>
+      <c r="S6" s="221"/>
+      <c r="T6" s="221"/>
+      <c r="U6" s="221"/>
+      <c r="V6" s="221"/>
+      <c r="W6" s="221"/>
+      <c r="X6" s="221"/>
+      <c r="Y6" s="221"/>
     </row>
     <row r="7" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B7" s="231"/>
-      <c r="C7" s="231"/>
-      <c r="D7" s="231"/>
-      <c r="E7" s="231"/>
-      <c r="F7" s="231"/>
-      <c r="G7" s="231"/>
-      <c r="H7" s="231"/>
-      <c r="I7" s="231"/>
-      <c r="J7" s="231"/>
-      <c r="K7" s="231"/>
-      <c r="L7" s="231"/>
-      <c r="M7" s="231"/>
-      <c r="N7" s="231"/>
-      <c r="O7" s="231"/>
-      <c r="P7" s="231"/>
-      <c r="Q7" s="231"/>
-      <c r="R7" s="231"/>
-      <c r="S7" s="231"/>
-      <c r="T7" s="231"/>
-      <c r="U7" s="231"/>
-      <c r="V7" s="231"/>
-      <c r="W7" s="231"/>
-      <c r="X7" s="231"/>
-      <c r="Y7" s="231"/>
+      <c r="B7" s="221"/>
+      <c r="C7" s="221"/>
+      <c r="D7" s="221"/>
+      <c r="E7" s="221"/>
+      <c r="F7" s="221"/>
+      <c r="G7" s="221"/>
+      <c r="H7" s="221"/>
+      <c r="I7" s="221"/>
+      <c r="J7" s="221"/>
+      <c r="K7" s="221"/>
+      <c r="L7" s="221"/>
+      <c r="M7" s="221"/>
+      <c r="N7" s="221"/>
+      <c r="O7" s="221"/>
+      <c r="P7" s="221"/>
+      <c r="Q7" s="221"/>
+      <c r="R7" s="221"/>
+      <c r="S7" s="221"/>
+      <c r="T7" s="221"/>
+      <c r="U7" s="221"/>
+      <c r="V7" s="221"/>
+      <c r="W7" s="221"/>
+      <c r="X7" s="221"/>
+      <c r="Y7" s="221"/>
     </row>
     <row r="8" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B8" s="231"/>
-      <c r="C8" s="231"/>
-      <c r="D8" s="231"/>
-      <c r="E8" s="231"/>
-      <c r="F8" s="231"/>
-      <c r="G8" s="231"/>
-      <c r="H8" s="231"/>
-      <c r="I8" s="231"/>
-      <c r="J8" s="231"/>
-      <c r="K8" s="231"/>
-      <c r="L8" s="231"/>
-      <c r="M8" s="231"/>
-      <c r="N8" s="231"/>
-      <c r="O8" s="231"/>
-      <c r="P8" s="231"/>
-      <c r="Q8" s="231"/>
-      <c r="R8" s="231"/>
-      <c r="S8" s="231"/>
-      <c r="T8" s="231"/>
-      <c r="U8" s="231"/>
-      <c r="V8" s="231"/>
-      <c r="W8" s="231"/>
-      <c r="X8" s="231"/>
-      <c r="Y8" s="231"/>
+      <c r="B8" s="221"/>
+      <c r="C8" s="221"/>
+      <c r="D8" s="221"/>
+      <c r="E8" s="221"/>
+      <c r="F8" s="221"/>
+      <c r="G8" s="221"/>
+      <c r="H8" s="221"/>
+      <c r="I8" s="221"/>
+      <c r="J8" s="221"/>
+      <c r="K8" s="221"/>
+      <c r="L8" s="221"/>
+      <c r="M8" s="221"/>
+      <c r="N8" s="221"/>
+      <c r="O8" s="221"/>
+      <c r="P8" s="221"/>
+      <c r="Q8" s="221"/>
+      <c r="R8" s="221"/>
+      <c r="S8" s="221"/>
+      <c r="T8" s="221"/>
+      <c r="U8" s="221"/>
+      <c r="V8" s="221"/>
+      <c r="W8" s="221"/>
+      <c r="X8" s="221"/>
+      <c r="Y8" s="221"/>
     </row>
     <row r="9" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B10" s="223" t="s">
+      <c r="B10" s="209" t="s">
         <v>180</v>
       </c>
-      <c r="C10" s="223"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="223"/>
-      <c r="F10" s="223"/>
-      <c r="G10" s="223"/>
-      <c r="H10" s="223"/>
-      <c r="I10" s="223"/>
-      <c r="J10" s="223"/>
-      <c r="K10" s="223"/>
-      <c r="L10" s="223"/>
-      <c r="M10" s="223"/>
-      <c r="N10" s="223"/>
-      <c r="O10" s="223"/>
-      <c r="P10" s="223"/>
-      <c r="Q10" s="223"/>
-      <c r="R10" s="223"/>
-      <c r="S10" s="223"/>
-      <c r="T10" s="223"/>
-      <c r="U10" s="223"/>
-      <c r="V10" s="223"/>
-      <c r="W10" s="223"/>
-      <c r="X10" s="223"/>
-      <c r="Y10" s="223"/>
+      <c r="C10" s="209"/>
+      <c r="D10" s="209"/>
+      <c r="E10" s="209"/>
+      <c r="F10" s="209"/>
+      <c r="G10" s="209"/>
+      <c r="H10" s="209"/>
+      <c r="I10" s="209"/>
+      <c r="J10" s="209"/>
+      <c r="K10" s="209"/>
+      <c r="L10" s="209"/>
+      <c r="M10" s="209"/>
+      <c r="N10" s="209"/>
+      <c r="O10" s="209"/>
+      <c r="P10" s="209"/>
+      <c r="Q10" s="209"/>
+      <c r="R10" s="209"/>
+      <c r="S10" s="209"/>
+      <c r="T10" s="209"/>
+      <c r="U10" s="209"/>
+      <c r="V10" s="209"/>
+      <c r="W10" s="209"/>
+      <c r="X10" s="209"/>
+      <c r="Y10" s="209"/>
     </row>
     <row r="11" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B12" s="227"/>
-      <c r="C12" s="228"/>
-      <c r="D12" s="229"/>
-      <c r="E12" s="230"/>
-      <c r="G12" s="223" t="s">
+      <c r="B12" s="217"/>
+      <c r="C12" s="218"/>
+      <c r="D12" s="219"/>
+      <c r="E12" s="220"/>
+      <c r="G12" s="209" t="s">
         <v>181</v>
       </c>
-      <c r="H12" s="223"/>
-      <c r="I12" s="223"/>
-      <c r="J12" s="223"/>
-      <c r="K12" s="223"/>
-      <c r="L12" s="223"/>
-      <c r="M12" s="223"/>
-      <c r="N12" s="223"/>
-      <c r="O12" s="223"/>
-      <c r="P12" s="223"/>
-      <c r="Q12" s="223"/>
-      <c r="R12" s="223"/>
-      <c r="S12" s="223"/>
-      <c r="T12" s="223"/>
-      <c r="U12" s="223"/>
-      <c r="V12" s="223"/>
-      <c r="W12" s="223"/>
-      <c r="X12" s="223"/>
-      <c r="Y12" s="223"/>
+      <c r="H12" s="209"/>
+      <c r="I12" s="209"/>
+      <c r="J12" s="209"/>
+      <c r="K12" s="209"/>
+      <c r="L12" s="209"/>
+      <c r="M12" s="209"/>
+      <c r="N12" s="209"/>
+      <c r="O12" s="209"/>
+      <c r="P12" s="209"/>
+      <c r="Q12" s="209"/>
+      <c r="R12" s="209"/>
+      <c r="S12" s="209"/>
+      <c r="T12" s="209"/>
+      <c r="U12" s="209"/>
+      <c r="V12" s="209"/>
+      <c r="W12" s="209"/>
+      <c r="X12" s="209"/>
+      <c r="Y12" s="209"/>
     </row>
     <row r="13" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:25" x14ac:dyDescent="0.3">
@@ -8711,27 +8719,27 @@
       <c r="C14" s="41"/>
       <c r="D14" s="41"/>
       <c r="E14" s="38"/>
-      <c r="G14" s="223" t="s">
+      <c r="G14" s="209" t="s">
         <v>182</v>
       </c>
-      <c r="H14" s="223"/>
-      <c r="I14" s="223"/>
-      <c r="J14" s="223"/>
-      <c r="K14" s="223"/>
-      <c r="L14" s="223"/>
-      <c r="M14" s="223"/>
-      <c r="N14" s="223"/>
-      <c r="O14" s="223"/>
-      <c r="P14" s="223"/>
-      <c r="Q14" s="223"/>
-      <c r="R14" s="223"/>
-      <c r="S14" s="223"/>
-      <c r="T14" s="223"/>
-      <c r="U14" s="223"/>
-      <c r="V14" s="223"/>
-      <c r="W14" s="223"/>
-      <c r="X14" s="223"/>
-      <c r="Y14" s="223"/>
+      <c r="H14" s="209"/>
+      <c r="I14" s="209"/>
+      <c r="J14" s="209"/>
+      <c r="K14" s="209"/>
+      <c r="L14" s="209"/>
+      <c r="M14" s="209"/>
+      <c r="N14" s="209"/>
+      <c r="O14" s="209"/>
+      <c r="P14" s="209"/>
+      <c r="Q14" s="209"/>
+      <c r="R14" s="209"/>
+      <c r="S14" s="209"/>
+      <c r="T14" s="209"/>
+      <c r="U14" s="209"/>
+      <c r="V14" s="209"/>
+      <c r="W14" s="209"/>
+      <c r="X14" s="209"/>
+      <c r="Y14" s="209"/>
     </row>
     <row r="15" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="2:25" x14ac:dyDescent="0.3">
@@ -8739,27 +8747,27 @@
       <c r="C16" s="42"/>
       <c r="D16" s="42"/>
       <c r="E16" s="40"/>
-      <c r="G16" s="223" t="s">
+      <c r="G16" s="209" t="s">
         <v>183</v>
       </c>
-      <c r="H16" s="223"/>
-      <c r="I16" s="223"/>
-      <c r="J16" s="223"/>
-      <c r="K16" s="223"/>
-      <c r="L16" s="223"/>
-      <c r="M16" s="223"/>
-      <c r="N16" s="223"/>
-      <c r="O16" s="223"/>
-      <c r="P16" s="223"/>
-      <c r="Q16" s="223"/>
-      <c r="R16" s="223"/>
-      <c r="S16" s="223"/>
-      <c r="T16" s="223"/>
-      <c r="U16" s="223"/>
-      <c r="V16" s="223"/>
-      <c r="W16" s="223"/>
-      <c r="X16" s="223"/>
-      <c r="Y16" s="223"/>
+      <c r="H16" s="209"/>
+      <c r="I16" s="209"/>
+      <c r="J16" s="209"/>
+      <c r="K16" s="209"/>
+      <c r="L16" s="209"/>
+      <c r="M16" s="209"/>
+      <c r="N16" s="209"/>
+      <c r="O16" s="209"/>
+      <c r="P16" s="209"/>
+      <c r="Q16" s="209"/>
+      <c r="R16" s="209"/>
+      <c r="S16" s="209"/>
+      <c r="T16" s="209"/>
+      <c r="U16" s="209"/>
+      <c r="V16" s="209"/>
+      <c r="W16" s="209"/>
+      <c r="X16" s="209"/>
+      <c r="Y16" s="209"/>
     </row>
     <row r="17" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
@@ -8769,217 +8777,217 @@
     </row>
     <row r="19" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B20" s="223" t="s">
+      <c r="B20" s="209" t="s">
         <v>207</v>
       </c>
-      <c r="C20" s="223"/>
-      <c r="D20" s="223"/>
-      <c r="E20" s="223"/>
-      <c r="F20" s="223"/>
-      <c r="G20" s="223"/>
-      <c r="H20" s="223"/>
-      <c r="I20" s="223"/>
-      <c r="J20" s="223"/>
-      <c r="K20" s="223"/>
-      <c r="L20" s="223"/>
-      <c r="M20" s="223"/>
-      <c r="N20" s="223"/>
-      <c r="O20" s="223"/>
-      <c r="P20" s="223"/>
-      <c r="Q20" s="223"/>
-      <c r="R20" s="223"/>
-      <c r="S20" s="223"/>
-      <c r="T20" s="223"/>
-      <c r="U20" s="223"/>
-      <c r="V20" s="223"/>
-      <c r="W20" s="223"/>
-      <c r="X20" s="223"/>
-      <c r="Y20" s="223"/>
+      <c r="C20" s="209"/>
+      <c r="D20" s="209"/>
+      <c r="E20" s="209"/>
+      <c r="F20" s="209"/>
+      <c r="G20" s="209"/>
+      <c r="H20" s="209"/>
+      <c r="I20" s="209"/>
+      <c r="J20" s="209"/>
+      <c r="K20" s="209"/>
+      <c r="L20" s="209"/>
+      <c r="M20" s="209"/>
+      <c r="N20" s="209"/>
+      <c r="O20" s="209"/>
+      <c r="P20" s="209"/>
+      <c r="Q20" s="209"/>
+      <c r="R20" s="209"/>
+      <c r="S20" s="209"/>
+      <c r="T20" s="209"/>
+      <c r="U20" s="209"/>
+      <c r="V20" s="209"/>
+      <c r="W20" s="209"/>
+      <c r="X20" s="209"/>
+      <c r="Y20" s="209"/>
     </row>
     <row r="21" spans="2:25" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B22" s="219"/>
+      <c r="B22" s="224"/>
       <c r="C22" s="54"/>
-      <c r="D22" s="213" t="s">
+      <c r="D22" s="210" t="s">
         <v>212</v>
       </c>
-      <c r="E22" s="213"/>
-      <c r="F22" s="213"/>
-      <c r="G22" s="213"/>
-      <c r="H22" s="213"/>
-      <c r="I22" s="213"/>
-      <c r="J22" s="213"/>
-      <c r="K22" s="213"/>
-      <c r="L22" s="213"/>
-      <c r="M22" s="213"/>
-      <c r="N22" s="213"/>
-      <c r="O22" s="213"/>
-      <c r="P22" s="213"/>
-      <c r="Q22" s="213"/>
-      <c r="R22" s="213"/>
-      <c r="S22" s="213"/>
-      <c r="T22" s="213"/>
-      <c r="U22" s="213"/>
-      <c r="V22" s="213"/>
-      <c r="W22" s="213"/>
-      <c r="X22" s="213"/>
-      <c r="Y22" s="214"/>
+      <c r="E22" s="210"/>
+      <c r="F22" s="210"/>
+      <c r="G22" s="210"/>
+      <c r="H22" s="210"/>
+      <c r="I22" s="210"/>
+      <c r="J22" s="210"/>
+      <c r="K22" s="210"/>
+      <c r="L22" s="210"/>
+      <c r="M22" s="210"/>
+      <c r="N22" s="210"/>
+      <c r="O22" s="210"/>
+      <c r="P22" s="210"/>
+      <c r="Q22" s="210"/>
+      <c r="R22" s="210"/>
+      <c r="S22" s="210"/>
+      <c r="T22" s="210"/>
+      <c r="U22" s="210"/>
+      <c r="V22" s="210"/>
+      <c r="W22" s="210"/>
+      <c r="X22" s="210"/>
+      <c r="Y22" s="211"/>
     </row>
     <row r="23" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="220"/>
+      <c r="B23" s="225"/>
       <c r="C23" s="55"/>
-      <c r="D23" s="217"/>
-      <c r="E23" s="217"/>
-      <c r="F23" s="217"/>
-      <c r="G23" s="217"/>
-      <c r="H23" s="217"/>
-      <c r="I23" s="217"/>
-      <c r="J23" s="217"/>
-      <c r="K23" s="217"/>
-      <c r="L23" s="217"/>
-      <c r="M23" s="217"/>
-      <c r="N23" s="217"/>
-      <c r="O23" s="217"/>
-      <c r="P23" s="217"/>
-      <c r="Q23" s="217"/>
-      <c r="R23" s="217"/>
-      <c r="S23" s="217"/>
-      <c r="T23" s="217"/>
-      <c r="U23" s="217"/>
-      <c r="V23" s="217"/>
-      <c r="W23" s="217"/>
-      <c r="X23" s="217"/>
-      <c r="Y23" s="218"/>
+      <c r="D23" s="212"/>
+      <c r="E23" s="212"/>
+      <c r="F23" s="212"/>
+      <c r="G23" s="212"/>
+      <c r="H23" s="212"/>
+      <c r="I23" s="212"/>
+      <c r="J23" s="212"/>
+      <c r="K23" s="212"/>
+      <c r="L23" s="212"/>
+      <c r="M23" s="212"/>
+      <c r="N23" s="212"/>
+      <c r="O23" s="212"/>
+      <c r="P23" s="212"/>
+      <c r="Q23" s="212"/>
+      <c r="R23" s="212"/>
+      <c r="S23" s="212"/>
+      <c r="T23" s="212"/>
+      <c r="U23" s="212"/>
+      <c r="V23" s="212"/>
+      <c r="W23" s="212"/>
+      <c r="X23" s="212"/>
+      <c r="Y23" s="213"/>
     </row>
     <row r="24" spans="2:25" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="25" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="219"/>
+      <c r="B25" s="224"/>
       <c r="C25" s="54"/>
-      <c r="D25" s="213" t="s">
+      <c r="D25" s="210" t="s">
         <v>186</v>
       </c>
-      <c r="E25" s="213"/>
-      <c r="F25" s="213"/>
-      <c r="G25" s="213"/>
-      <c r="H25" s="213"/>
-      <c r="I25" s="213"/>
-      <c r="J25" s="213"/>
-      <c r="K25" s="213"/>
-      <c r="L25" s="213"/>
-      <c r="M25" s="213"/>
-      <c r="N25" s="213"/>
-      <c r="O25" s="213"/>
-      <c r="P25" s="213"/>
-      <c r="Q25" s="213"/>
-      <c r="R25" s="213"/>
-      <c r="S25" s="213"/>
-      <c r="T25" s="213"/>
-      <c r="U25" s="213"/>
-      <c r="V25" s="213"/>
-      <c r="W25" s="213"/>
-      <c r="X25" s="213"/>
-      <c r="Y25" s="214"/>
+      <c r="E25" s="210"/>
+      <c r="F25" s="210"/>
+      <c r="G25" s="210"/>
+      <c r="H25" s="210"/>
+      <c r="I25" s="210"/>
+      <c r="J25" s="210"/>
+      <c r="K25" s="210"/>
+      <c r="L25" s="210"/>
+      <c r="M25" s="210"/>
+      <c r="N25" s="210"/>
+      <c r="O25" s="210"/>
+      <c r="P25" s="210"/>
+      <c r="Q25" s="210"/>
+      <c r="R25" s="210"/>
+      <c r="S25" s="210"/>
+      <c r="T25" s="210"/>
+      <c r="U25" s="210"/>
+      <c r="V25" s="210"/>
+      <c r="W25" s="210"/>
+      <c r="X25" s="210"/>
+      <c r="Y25" s="211"/>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B26" s="221"/>
-      <c r="D26" s="215"/>
-      <c r="E26" s="215"/>
-      <c r="F26" s="215"/>
-      <c r="G26" s="215"/>
-      <c r="H26" s="215"/>
-      <c r="I26" s="215"/>
-      <c r="J26" s="215"/>
-      <c r="K26" s="215"/>
-      <c r="L26" s="215"/>
-      <c r="M26" s="215"/>
-      <c r="N26" s="215"/>
-      <c r="O26" s="215"/>
-      <c r="P26" s="215"/>
-      <c r="Q26" s="215"/>
-      <c r="R26" s="215"/>
-      <c r="S26" s="215"/>
-      <c r="T26" s="215"/>
-      <c r="U26" s="215"/>
-      <c r="V26" s="215"/>
-      <c r="W26" s="215"/>
-      <c r="X26" s="215"/>
-      <c r="Y26" s="216"/>
+      <c r="B26" s="226"/>
+      <c r="D26" s="222"/>
+      <c r="E26" s="222"/>
+      <c r="F26" s="222"/>
+      <c r="G26" s="222"/>
+      <c r="H26" s="222"/>
+      <c r="I26" s="222"/>
+      <c r="J26" s="222"/>
+      <c r="K26" s="222"/>
+      <c r="L26" s="222"/>
+      <c r="M26" s="222"/>
+      <c r="N26" s="222"/>
+      <c r="O26" s="222"/>
+      <c r="P26" s="222"/>
+      <c r="Q26" s="222"/>
+      <c r="R26" s="222"/>
+      <c r="S26" s="222"/>
+      <c r="T26" s="222"/>
+      <c r="U26" s="222"/>
+      <c r="V26" s="222"/>
+      <c r="W26" s="222"/>
+      <c r="X26" s="222"/>
+      <c r="Y26" s="223"/>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B27" s="56"/>
-      <c r="D27" s="215"/>
-      <c r="E27" s="215"/>
-      <c r="F27" s="215"/>
-      <c r="G27" s="215"/>
-      <c r="H27" s="215"/>
-      <c r="I27" s="215"/>
-      <c r="J27" s="215"/>
-      <c r="K27" s="215"/>
-      <c r="L27" s="215"/>
-      <c r="M27" s="215"/>
-      <c r="N27" s="215"/>
-      <c r="O27" s="215"/>
-      <c r="P27" s="215"/>
-      <c r="Q27" s="215"/>
-      <c r="R27" s="215"/>
-      <c r="S27" s="215"/>
-      <c r="T27" s="215"/>
-      <c r="U27" s="215"/>
-      <c r="V27" s="215"/>
-      <c r="W27" s="215"/>
-      <c r="X27" s="215"/>
-      <c r="Y27" s="216"/>
+      <c r="D27" s="222"/>
+      <c r="E27" s="222"/>
+      <c r="F27" s="222"/>
+      <c r="G27" s="222"/>
+      <c r="H27" s="222"/>
+      <c r="I27" s="222"/>
+      <c r="J27" s="222"/>
+      <c r="K27" s="222"/>
+      <c r="L27" s="222"/>
+      <c r="M27" s="222"/>
+      <c r="N27" s="222"/>
+      <c r="O27" s="222"/>
+      <c r="P27" s="222"/>
+      <c r="Q27" s="222"/>
+      <c r="R27" s="222"/>
+      <c r="S27" s="222"/>
+      <c r="T27" s="222"/>
+      <c r="U27" s="222"/>
+      <c r="V27" s="222"/>
+      <c r="W27" s="222"/>
+      <c r="X27" s="222"/>
+      <c r="Y27" s="223"/>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B28" s="56"/>
-      <c r="D28" s="215"/>
-      <c r="E28" s="215"/>
-      <c r="F28" s="215"/>
-      <c r="G28" s="215"/>
-      <c r="H28" s="215"/>
-      <c r="I28" s="215"/>
-      <c r="J28" s="215"/>
-      <c r="K28" s="215"/>
-      <c r="L28" s="215"/>
-      <c r="M28" s="215"/>
-      <c r="N28" s="215"/>
-      <c r="O28" s="215"/>
-      <c r="P28" s="215"/>
-      <c r="Q28" s="215"/>
-      <c r="R28" s="215"/>
-      <c r="S28" s="215"/>
-      <c r="T28" s="215"/>
-      <c r="U28" s="215"/>
-      <c r="V28" s="215"/>
-      <c r="W28" s="215"/>
-      <c r="X28" s="215"/>
-      <c r="Y28" s="216"/>
+      <c r="D28" s="222"/>
+      <c r="E28" s="222"/>
+      <c r="F28" s="222"/>
+      <c r="G28" s="222"/>
+      <c r="H28" s="222"/>
+      <c r="I28" s="222"/>
+      <c r="J28" s="222"/>
+      <c r="K28" s="222"/>
+      <c r="L28" s="222"/>
+      <c r="M28" s="222"/>
+      <c r="N28" s="222"/>
+      <c r="O28" s="222"/>
+      <c r="P28" s="222"/>
+      <c r="Q28" s="222"/>
+      <c r="R28" s="222"/>
+      <c r="S28" s="222"/>
+      <c r="T28" s="222"/>
+      <c r="U28" s="222"/>
+      <c r="V28" s="222"/>
+      <c r="W28" s="222"/>
+      <c r="X28" s="222"/>
+      <c r="Y28" s="223"/>
     </row>
     <row r="29" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="57"/>
       <c r="C29" s="55"/>
-      <c r="D29" s="217"/>
-      <c r="E29" s="217"/>
-      <c r="F29" s="217"/>
-      <c r="G29" s="217"/>
-      <c r="H29" s="217"/>
-      <c r="I29" s="217"/>
-      <c r="J29" s="217"/>
-      <c r="K29" s="217"/>
-      <c r="L29" s="217"/>
-      <c r="M29" s="217"/>
-      <c r="N29" s="217"/>
-      <c r="O29" s="217"/>
-      <c r="P29" s="217"/>
-      <c r="Q29" s="217"/>
-      <c r="R29" s="217"/>
-      <c r="S29" s="217"/>
-      <c r="T29" s="217"/>
-      <c r="U29" s="217"/>
-      <c r="V29" s="217"/>
-      <c r="W29" s="217"/>
-      <c r="X29" s="217"/>
-      <c r="Y29" s="218"/>
+      <c r="D29" s="212"/>
+      <c r="E29" s="212"/>
+      <c r="F29" s="212"/>
+      <c r="G29" s="212"/>
+      <c r="H29" s="212"/>
+      <c r="I29" s="212"/>
+      <c r="J29" s="212"/>
+      <c r="K29" s="212"/>
+      <c r="L29" s="212"/>
+      <c r="M29" s="212"/>
+      <c r="N29" s="212"/>
+      <c r="O29" s="212"/>
+      <c r="P29" s="212"/>
+      <c r="Q29" s="212"/>
+      <c r="R29" s="212"/>
+      <c r="S29" s="212"/>
+      <c r="T29" s="212"/>
+      <c r="U29" s="212"/>
+      <c r="V29" s="212"/>
+      <c r="W29" s="212"/>
+      <c r="X29" s="212"/>
+      <c r="Y29" s="213"/>
     </row>
     <row r="30" spans="2:25" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="2:25" x14ac:dyDescent="0.3">
@@ -9202,9 +9210,9 @@
       <c r="D46" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="E46" s="222"/>
-      <c r="F46" s="222"/>
-      <c r="G46" s="222"/>
+      <c r="E46" s="227"/>
+      <c r="F46" s="227"/>
+      <c r="G46" s="227"/>
       <c r="H46" s="50"/>
       <c r="I46" s="50"/>
       <c r="J46" s="50"/>
@@ -9312,57 +9320,57 @@
     </row>
     <row r="50" spans="2:25" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="51" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B51" s="219"/>
+      <c r="B51" s="224"/>
       <c r="C51" s="54"/>
-      <c r="D51" s="213" t="s">
+      <c r="D51" s="210" t="s">
         <v>184</v>
       </c>
-      <c r="E51" s="213"/>
-      <c r="F51" s="213"/>
-      <c r="G51" s="213"/>
-      <c r="H51" s="213"/>
-      <c r="I51" s="213"/>
-      <c r="J51" s="213"/>
-      <c r="K51" s="213"/>
-      <c r="L51" s="213"/>
-      <c r="M51" s="213"/>
-      <c r="N51" s="213"/>
-      <c r="O51" s="213"/>
-      <c r="P51" s="213"/>
-      <c r="Q51" s="213"/>
-      <c r="R51" s="213"/>
-      <c r="S51" s="213"/>
-      <c r="T51" s="213"/>
-      <c r="U51" s="213"/>
-      <c r="V51" s="213"/>
-      <c r="W51" s="213"/>
-      <c r="X51" s="213"/>
-      <c r="Y51" s="214"/>
+      <c r="E51" s="210"/>
+      <c r="F51" s="210"/>
+      <c r="G51" s="210"/>
+      <c r="H51" s="210"/>
+      <c r="I51" s="210"/>
+      <c r="J51" s="210"/>
+      <c r="K51" s="210"/>
+      <c r="L51" s="210"/>
+      <c r="M51" s="210"/>
+      <c r="N51" s="210"/>
+      <c r="O51" s="210"/>
+      <c r="P51" s="210"/>
+      <c r="Q51" s="210"/>
+      <c r="R51" s="210"/>
+      <c r="S51" s="210"/>
+      <c r="T51" s="210"/>
+      <c r="U51" s="210"/>
+      <c r="V51" s="210"/>
+      <c r="W51" s="210"/>
+      <c r="X51" s="210"/>
+      <c r="Y51" s="211"/>
     </row>
     <row r="52" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B52" s="221"/>
-      <c r="D52" s="215"/>
-      <c r="E52" s="215"/>
-      <c r="F52" s="215"/>
-      <c r="G52" s="215"/>
-      <c r="H52" s="215"/>
-      <c r="I52" s="215"/>
-      <c r="J52" s="215"/>
-      <c r="K52" s="215"/>
-      <c r="L52" s="215"/>
-      <c r="M52" s="215"/>
-      <c r="N52" s="215"/>
-      <c r="O52" s="215"/>
-      <c r="P52" s="215"/>
-      <c r="Q52" s="215"/>
-      <c r="R52" s="215"/>
-      <c r="S52" s="215"/>
-      <c r="T52" s="215"/>
-      <c r="U52" s="215"/>
-      <c r="V52" s="215"/>
-      <c r="W52" s="215"/>
-      <c r="X52" s="215"/>
-      <c r="Y52" s="216"/>
+      <c r="B52" s="226"/>
+      <c r="D52" s="222"/>
+      <c r="E52" s="222"/>
+      <c r="F52" s="222"/>
+      <c r="G52" s="222"/>
+      <c r="H52" s="222"/>
+      <c r="I52" s="222"/>
+      <c r="J52" s="222"/>
+      <c r="K52" s="222"/>
+      <c r="L52" s="222"/>
+      <c r="M52" s="222"/>
+      <c r="N52" s="222"/>
+      <c r="O52" s="222"/>
+      <c r="P52" s="222"/>
+      <c r="Q52" s="222"/>
+      <c r="R52" s="222"/>
+      <c r="S52" s="222"/>
+      <c r="T52" s="222"/>
+      <c r="U52" s="222"/>
+      <c r="V52" s="222"/>
+      <c r="W52" s="222"/>
+      <c r="X52" s="222"/>
+      <c r="Y52" s="223"/>
     </row>
     <row r="53" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="56"/>
@@ -9534,6 +9542,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="D25:Y29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="D51:Y52"/>
+    <mergeCell ref="E46:G46"/>
     <mergeCell ref="G16:Y16"/>
     <mergeCell ref="B20:Y20"/>
     <mergeCell ref="D22:Y23"/>
@@ -9545,12 +9559,6 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="B6:Y8"/>
-    <mergeCell ref="D25:Y29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="D51:Y52"/>
-    <mergeCell ref="E46:G46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9600,170 +9608,170 @@
       <c r="Y1"/>
     </row>
     <row r="2" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="C2" s="107"/>
-      <c r="I2" s="107"/>
+      <c r="C2" s="143"/>
+      <c r="I2" s="143"/>
       <c r="Y2"/>
-      <c r="AM2" s="107"/>
+      <c r="AM2" s="143"/>
     </row>
     <row r="3" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="C3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="AM3" s="107"/>
+      <c r="C3" s="143"/>
+      <c r="I3" s="143"/>
+      <c r="AM3" s="143"/>
     </row>
     <row r="4" spans="2:57" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="2:57" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="188" t="s">
+      <c r="B5" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="108" t="s">
+      <c r="C5" s="187" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="191" t="s">
+      <c r="D5" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="131" t="s">
+      <c r="E5" s="196" t="s">
         <v>165</v>
       </c>
-      <c r="F5" s="125" t="s">
+      <c r="F5" s="191" t="s">
         <v>168</v>
       </c>
-      <c r="G5" s="137" t="s">
+      <c r="G5" s="200" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="125" t="str">
+      <c r="H5" s="191" t="str">
         <f>IFERROR(INDEX(#REF!,MATCH(пример!$C$9,#REF!,0)),"")</f>
         <v/>
       </c>
-      <c r="I5" s="127" t="s">
+      <c r="I5" s="192" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="128"/>
-      <c r="T5" s="128"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="128"/>
-      <c r="W5" s="128"/>
-      <c r="X5" s="128"/>
-      <c r="Y5" s="128"/>
-      <c r="Z5" s="128"/>
-      <c r="AA5" s="128"/>
-      <c r="AB5" s="128"/>
-      <c r="AC5" s="128"/>
-      <c r="AD5" s="128"/>
-      <c r="AE5" s="128"/>
-      <c r="AF5" s="128"/>
-      <c r="AG5" s="128"/>
-      <c r="AH5" s="128"/>
-      <c r="AI5" s="128"/>
-      <c r="AJ5" s="128"/>
-      <c r="AK5" s="128"/>
-      <c r="AL5" s="128"/>
-      <c r="AM5" s="131" t="s">
+      <c r="J5" s="193"/>
+      <c r="K5" s="193"/>
+      <c r="L5" s="193"/>
+      <c r="M5" s="193"/>
+      <c r="N5" s="193"/>
+      <c r="O5" s="193"/>
+      <c r="P5" s="193"/>
+      <c r="Q5" s="193"/>
+      <c r="R5" s="193"/>
+      <c r="S5" s="193"/>
+      <c r="T5" s="193"/>
+      <c r="U5" s="193"/>
+      <c r="V5" s="193"/>
+      <c r="W5" s="193"/>
+      <c r="X5" s="193"/>
+      <c r="Y5" s="193"/>
+      <c r="Z5" s="193"/>
+      <c r="AA5" s="193"/>
+      <c r="AB5" s="193"/>
+      <c r="AC5" s="193"/>
+      <c r="AD5" s="193"/>
+      <c r="AE5" s="193"/>
+      <c r="AF5" s="193"/>
+      <c r="AG5" s="193"/>
+      <c r="AH5" s="193"/>
+      <c r="AI5" s="193"/>
+      <c r="AJ5" s="193"/>
+      <c r="AK5" s="193"/>
+      <c r="AL5" s="193"/>
+      <c r="AM5" s="196" t="s">
         <v>39</v>
       </c>
-      <c r="AN5" s="132"/>
-      <c r="AO5" s="132"/>
-      <c r="AP5" s="132"/>
-      <c r="AQ5" s="132"/>
-      <c r="AR5" s="132"/>
-      <c r="AS5" s="132"/>
-      <c r="AT5" s="133"/>
-      <c r="AU5" s="205" t="s">
+      <c r="AN5" s="112"/>
+      <c r="AO5" s="112"/>
+      <c r="AP5" s="112"/>
+      <c r="AQ5" s="112"/>
+      <c r="AR5" s="112"/>
+      <c r="AS5" s="112"/>
+      <c r="AT5" s="197"/>
+      <c r="AU5" s="111" t="s">
         <v>174</v>
       </c>
-      <c r="AV5" s="132"/>
-      <c r="AW5" s="132"/>
-      <c r="AX5" s="132"/>
-      <c r="AY5" s="132"/>
-      <c r="AZ5" s="132"/>
-      <c r="BA5" s="132"/>
-      <c r="BB5" s="206"/>
-      <c r="BC5" s="193" t="s">
+      <c r="AV5" s="112"/>
+      <c r="AW5" s="112"/>
+      <c r="AX5" s="112"/>
+      <c r="AY5" s="112"/>
+      <c r="AZ5" s="112"/>
+      <c r="BA5" s="112"/>
+      <c r="BB5" s="113"/>
+      <c r="BC5" s="144" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="6" spans="2:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="189"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="192"/>
-      <c r="E6" s="139"/>
-      <c r="F6" s="126"/>
-      <c r="G6" s="138"/>
-      <c r="H6" s="126"/>
-      <c r="I6" s="129"/>
-      <c r="J6" s="130"/>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="130"/>
-      <c r="O6" s="130"/>
-      <c r="P6" s="130"/>
-      <c r="Q6" s="130"/>
-      <c r="R6" s="130"/>
-      <c r="S6" s="130"/>
-      <c r="T6" s="130"/>
-      <c r="U6" s="130"/>
-      <c r="V6" s="130"/>
-      <c r="W6" s="130"/>
-      <c r="X6" s="130"/>
-      <c r="Y6" s="130"/>
-      <c r="Z6" s="130"/>
-      <c r="AA6" s="130"/>
-      <c r="AB6" s="130"/>
-      <c r="AC6" s="130"/>
-      <c r="AD6" s="130"/>
-      <c r="AE6" s="130"/>
-      <c r="AF6" s="130"/>
-      <c r="AG6" s="130"/>
-      <c r="AH6" s="130"/>
-      <c r="AI6" s="130"/>
-      <c r="AJ6" s="130"/>
-      <c r="AK6" s="130"/>
-      <c r="AL6" s="130"/>
-      <c r="AM6" s="134"/>
-      <c r="AN6" s="135"/>
-      <c r="AO6" s="135"/>
-      <c r="AP6" s="135"/>
-      <c r="AQ6" s="135"/>
-      <c r="AR6" s="135"/>
-      <c r="AS6" s="135"/>
-      <c r="AT6" s="136"/>
-      <c r="AU6" s="207"/>
-      <c r="AV6" s="135"/>
-      <c r="AW6" s="135"/>
-      <c r="AX6" s="135"/>
-      <c r="AY6" s="135"/>
-      <c r="AZ6" s="135"/>
-      <c r="BA6" s="135"/>
-      <c r="BB6" s="208"/>
-      <c r="BC6" s="194"/>
+      <c r="B6" s="139"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="142"/>
+      <c r="E6" s="202"/>
+      <c r="F6" s="186"/>
+      <c r="G6" s="201"/>
+      <c r="H6" s="186"/>
+      <c r="I6" s="194"/>
+      <c r="J6" s="195"/>
+      <c r="K6" s="195"/>
+      <c r="L6" s="195"/>
+      <c r="M6" s="195"/>
+      <c r="N6" s="195"/>
+      <c r="O6" s="195"/>
+      <c r="P6" s="195"/>
+      <c r="Q6" s="195"/>
+      <c r="R6" s="195"/>
+      <c r="S6" s="195"/>
+      <c r="T6" s="195"/>
+      <c r="U6" s="195"/>
+      <c r="V6" s="195"/>
+      <c r="W6" s="195"/>
+      <c r="X6" s="195"/>
+      <c r="Y6" s="195"/>
+      <c r="Z6" s="195"/>
+      <c r="AA6" s="195"/>
+      <c r="AB6" s="195"/>
+      <c r="AC6" s="195"/>
+      <c r="AD6" s="195"/>
+      <c r="AE6" s="195"/>
+      <c r="AF6" s="195"/>
+      <c r="AG6" s="195"/>
+      <c r="AH6" s="195"/>
+      <c r="AI6" s="195"/>
+      <c r="AJ6" s="195"/>
+      <c r="AK6" s="195"/>
+      <c r="AL6" s="195"/>
+      <c r="AM6" s="198"/>
+      <c r="AN6" s="115"/>
+      <c r="AO6" s="115"/>
+      <c r="AP6" s="115"/>
+      <c r="AQ6" s="115"/>
+      <c r="AR6" s="115"/>
+      <c r="AS6" s="115"/>
+      <c r="AT6" s="199"/>
+      <c r="AU6" s="114"/>
+      <c r="AV6" s="115"/>
+      <c r="AW6" s="115"/>
+      <c r="AX6" s="115"/>
+      <c r="AY6" s="115"/>
+      <c r="AZ6" s="115"/>
+      <c r="BA6" s="115"/>
+      <c r="BB6" s="116"/>
+      <c r="BC6" s="145"/>
     </row>
     <row r="7" spans="2:57" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="189"/>
-      <c r="C7" s="151" t="s">
+      <c r="B7" s="139"/>
+      <c r="C7" s="206" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="153" t="s">
+      <c r="D7" s="208" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="186" t="s">
+      <c r="E7" s="136" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="186" t="s">
+      <c r="F7" s="136" t="s">
         <v>797</v>
       </c>
-      <c r="G7" s="140" t="s">
+      <c r="G7" s="203" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="144" t="s">
+      <c r="H7" s="205" t="s">
         <v>38</v>
       </c>
       <c r="I7" s="30" t="str">
@@ -9886,52 +9894,52 @@
         <f>VLOOKUP(WEEKDAY(AL8,11),'Справочный лист'!$J$3:$K$9,2,FALSE)</f>
         <v>ЧТ</v>
       </c>
-      <c r="AM7" s="145" t="s">
+      <c r="AM7" s="182" t="s">
         <v>43</v>
       </c>
-      <c r="AN7" s="146"/>
-      <c r="AO7" s="146"/>
-      <c r="AP7" s="147"/>
-      <c r="AQ7" s="142" t="s">
+      <c r="AN7" s="183"/>
+      <c r="AO7" s="183"/>
+      <c r="AP7" s="184"/>
+      <c r="AQ7" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="AR7" s="142" t="s">
+      <c r="AR7" s="133" t="s">
         <v>44</v>
       </c>
-      <c r="AS7" s="142" t="s">
+      <c r="AS7" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="AT7" s="154" t="s">
+      <c r="AT7" s="185" t="s">
         <v>46</v>
       </c>
-      <c r="AU7" s="145" t="s">
+      <c r="AU7" s="182" t="s">
         <v>43</v>
       </c>
-      <c r="AV7" s="146"/>
-      <c r="AW7" s="146"/>
-      <c r="AX7" s="147"/>
-      <c r="AY7" s="142" t="s">
+      <c r="AV7" s="183"/>
+      <c r="AW7" s="183"/>
+      <c r="AX7" s="184"/>
+      <c r="AY7" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="AZ7" s="142" t="s">
+      <c r="AZ7" s="133" t="s">
         <v>44</v>
       </c>
-      <c r="BA7" s="142" t="s">
+      <c r="BA7" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="BB7" s="211" t="s">
+      <c r="BB7" s="131" t="s">
         <v>46</v>
       </c>
-      <c r="BC7" s="194"/>
+      <c r="BC7" s="145"/>
     </row>
     <row r="8" spans="2:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="190"/>
-      <c r="C8" s="152"/>
-      <c r="D8" s="143"/>
-      <c r="E8" s="187"/>
-      <c r="F8" s="187"/>
-      <c r="G8" s="141"/>
-      <c r="H8" s="109"/>
+      <c r="B8" s="140"/>
+      <c r="C8" s="207"/>
+      <c r="D8" s="134"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="204"/>
+      <c r="H8" s="188"/>
       <c r="I8" s="28" t="str">
         <f>'Справочный лист'!M3&amp;"."&amp;VLOOKUP($D$5,'Справочный лист'!$M$6:$N$17,2,FALSE)&amp;"."&amp;'Справочный лист'!$M$4</f>
         <v>1.4.26</v>
@@ -10064,10 +10072,10 @@
       <c r="AP8" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="AQ8" s="143"/>
-      <c r="AR8" s="143"/>
-      <c r="AS8" s="143"/>
-      <c r="AT8" s="126"/>
+      <c r="AQ8" s="134"/>
+      <c r="AR8" s="134"/>
+      <c r="AS8" s="134"/>
+      <c r="AT8" s="186"/>
       <c r="AU8" s="31" t="s">
         <v>40</v>
       </c>
@@ -10080,31 +10088,31 @@
       <c r="AX8" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="AY8" s="143"/>
-      <c r="AZ8" s="143"/>
-      <c r="BA8" s="143"/>
-      <c r="BB8" s="212"/>
-      <c r="BC8" s="195"/>
+      <c r="AY8" s="134"/>
+      <c r="AZ8" s="134"/>
+      <c r="BA8" s="134"/>
+      <c r="BB8" s="132"/>
+      <c r="BC8" s="146"/>
     </row>
     <row r="9" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="B9" s="182">
+      <c r="B9" s="154">
         <v>1</v>
       </c>
-      <c r="C9" s="173" t="str">
+      <c r="C9" s="157" t="str">
         <f>[1]ШР!P8</f>
         <v>Эскеров Аднан Эскерович</v>
       </c>
-      <c r="D9" s="184" t="s">
+      <c r="D9" s="160" t="s">
         <v>362</v>
       </c>
-      <c r="E9" s="162" t="s">
+      <c r="E9" s="153" t="s">
         <v>1077</v>
       </c>
-      <c r="F9" s="162" t="str">
+      <c r="F9" s="153" t="str">
         <f>IFERROR(INDEX([1]ШР!M:M,MATCH('[1]Шаблон Табеля'!C9:C10,[1]ШР!P:P,0)),"")</f>
         <v>Отдел Единой государственной автоматизированной информационной системы</v>
       </c>
-      <c r="G9" s="166" t="s">
+      <c r="G9" s="171" t="s">
         <v>142</v>
       </c>
       <c r="H9" s="32" t="s">
@@ -10160,7 +10168,7 @@
       <c r="AJ9" s="91"/>
       <c r="AK9" s="91"/>
       <c r="AL9" s="91"/>
-      <c r="AM9" s="165">
+      <c r="AM9" s="178">
         <f>IF(C9="","",COUNTIF(I9:W9,"Я")+COUNTIF(I9:W9,"Н")+COUNTIF(I9:W9,"Д")+COUNTIF(I9:W9,"РВ"))</f>
         <v>10</v>
       </c>
@@ -10168,26 +10176,26 @@
         <f>IF(C9="","",SUM(I10:W10))</f>
         <v>80</v>
       </c>
-      <c r="AO9" s="122">
+      <c r="AO9" s="178">
         <f>SUM(I10:W10)</f>
         <v>80</v>
       </c>
-      <c r="AP9" s="148">
+      <c r="AP9" s="135">
         <f>SUM(I11:W11)</f>
         <v>0</v>
       </c>
-      <c r="AQ9" s="110">
+      <c r="AQ9" s="126">
         <v>80</v>
       </c>
-      <c r="AR9" s="113">
+      <c r="AR9" s="119">
         <f>IF(G9="Женский",'ПК 2 Дагестан'!$G$22/2,'ПК 2 Дагестан'!$F$22/2)</f>
         <v>80.333333333333329</v>
       </c>
-      <c r="AS9" s="116">
+      <c r="AS9" s="122">
         <f>IFERROR(IF(C9="","",AN9-AQ9),"")</f>
         <v>0</v>
       </c>
-      <c r="AT9" s="119">
+      <c r="AT9" s="181">
         <f>IF(C9="","",AN9-AR9)</f>
         <v>-0.3333333333333286</v>
       </c>
@@ -10195,44 +10203,44 @@
         <f>IF(C9="","",COUNTIF(I9:AL9,"Я")+COUNTIF(I9:AL9,"Н")+COUNTIF(I9:AL9,"Д")+COUNTIF(I9:AL9,"РВ"))</f>
         <v>10</v>
       </c>
-      <c r="AV9" s="149">
+      <c r="AV9" s="124">
         <f>SUM(I10:AL11)</f>
         <v>80</v>
       </c>
-      <c r="AW9" s="122">
+      <c r="AW9" s="178">
         <f>SUM(I10:AL10)</f>
         <v>80</v>
       </c>
-      <c r="AX9" s="148">
+      <c r="AX9" s="135">
         <f>SUM(I11:AL11)</f>
         <v>0</v>
       </c>
-      <c r="AY9" s="110">
+      <c r="AY9" s="126">
         <v>159</v>
       </c>
-      <c r="AZ9" s="113">
+      <c r="AZ9" s="119">
         <f>IF(G9="Женский",'ПК 2 Дагестан'!$G$22,'ПК 2 Дагестан'!$F$22)</f>
         <v>160.66666666666666</v>
       </c>
-      <c r="BA9" s="199">
+      <c r="BA9" s="150">
         <f>IFERROR(IF(C9="","",AV9-AY9),"")</f>
         <v>-79</v>
       </c>
-      <c r="BB9" s="209">
+      <c r="BB9" s="117">
         <f>IF(C9="","",AV9-AZ9)</f>
         <v>-80.666666666666657</v>
       </c>
-      <c r="BC9" s="196"/>
-      <c r="BD9" s="107"/>
-      <c r="BE9" s="107"/>
+      <c r="BC9" s="147"/>
+      <c r="BD9" s="143"/>
+      <c r="BE9" s="143"/>
     </row>
     <row r="10" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="B10" s="171"/>
-      <c r="C10" s="174"/>
-      <c r="D10" s="162"/>
-      <c r="E10" s="162"/>
-      <c r="F10" s="162"/>
-      <c r="G10" s="167"/>
+      <c r="B10" s="155"/>
+      <c r="C10" s="158"/>
+      <c r="D10" s="153"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="172"/>
       <c r="H10" s="33" t="s">
         <v>48</v>
       </c>
@@ -10286,37 +10294,37 @@
       <c r="AJ10" s="92"/>
       <c r="AK10" s="92"/>
       <c r="AL10" s="92"/>
-      <c r="AM10" s="156"/>
-      <c r="AN10" s="149"/>
-      <c r="AO10" s="123"/>
-      <c r="AP10" s="149"/>
-      <c r="AQ10" s="111"/>
-      <c r="AR10" s="114"/>
-      <c r="AS10" s="117"/>
-      <c r="AT10" s="120"/>
-      <c r="AU10" s="149"/>
-      <c r="AV10" s="149"/>
-      <c r="AW10" s="123"/>
-      <c r="AX10" s="149"/>
-      <c r="AY10" s="111"/>
-      <c r="AZ10" s="114"/>
-      <c r="BA10" s="200"/>
-      <c r="BB10" s="203"/>
-      <c r="BC10" s="197"/>
-      <c r="BD10" s="107"/>
-      <c r="BE10" s="107"/>
+      <c r="AM10" s="179"/>
+      <c r="AN10" s="124"/>
+      <c r="AO10" s="179"/>
+      <c r="AP10" s="124"/>
+      <c r="AQ10" s="127"/>
+      <c r="AR10" s="120"/>
+      <c r="AS10" s="123"/>
+      <c r="AT10" s="176"/>
+      <c r="AU10" s="124"/>
+      <c r="AV10" s="124"/>
+      <c r="AW10" s="179"/>
+      <c r="AX10" s="124"/>
+      <c r="AY10" s="127"/>
+      <c r="AZ10" s="120"/>
+      <c r="BA10" s="151"/>
+      <c r="BB10" s="109"/>
+      <c r="BC10" s="148"/>
+      <c r="BD10" s="143"/>
+      <c r="BE10" s="143"/>
     </row>
     <row r="11" spans="2:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="183"/>
-      <c r="C11" s="175"/>
-      <c r="D11" s="185"/>
-      <c r="E11" s="162"/>
-      <c r="F11" s="162"/>
-      <c r="G11" s="168"/>
+      <c r="B11" s="156"/>
+      <c r="C11" s="159"/>
+      <c r="D11" s="161"/>
+      <c r="E11" s="153"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="173"/>
       <c r="H11" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I11" s="282"/>
+      <c r="I11" s="106"/>
       <c r="J11" s="90"/>
       <c r="K11" s="90"/>
       <c r="L11" s="90"/>
@@ -10347,44 +10355,44 @@
       <c r="AK11" s="90"/>
       <c r="AL11" s="90"/>
       <c r="AM11" s="180"/>
-      <c r="AN11" s="181"/>
-      <c r="AO11" s="124"/>
-      <c r="AP11" s="150"/>
-      <c r="AQ11" s="112"/>
-      <c r="AR11" s="115"/>
-      <c r="AS11" s="118"/>
-      <c r="AT11" s="121"/>
-      <c r="AU11" s="181"/>
-      <c r="AV11" s="149"/>
-      <c r="AW11" s="124"/>
-      <c r="AX11" s="150"/>
-      <c r="AY11" s="112"/>
-      <c r="AZ11" s="115"/>
-      <c r="BA11" s="201"/>
-      <c r="BB11" s="210"/>
-      <c r="BC11" s="198"/>
-      <c r="BD11" s="107"/>
-      <c r="BE11" s="107"/>
+      <c r="AN11" s="170"/>
+      <c r="AO11" s="180"/>
+      <c r="AP11" s="125"/>
+      <c r="AQ11" s="128"/>
+      <c r="AR11" s="121"/>
+      <c r="AS11" s="189"/>
+      <c r="AT11" s="190"/>
+      <c r="AU11" s="170"/>
+      <c r="AV11" s="124"/>
+      <c r="AW11" s="180"/>
+      <c r="AX11" s="125"/>
+      <c r="AY11" s="128"/>
+      <c r="AZ11" s="121"/>
+      <c r="BA11" s="152"/>
+      <c r="BB11" s="118"/>
+      <c r="BC11" s="149"/>
+      <c r="BD11" s="143"/>
+      <c r="BE11" s="143"/>
     </row>
     <row r="12" spans="2:57" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="170">
+      <c r="B12" s="164">
         <v>2</v>
       </c>
-      <c r="C12" s="173" t="str">
+      <c r="C12" s="157" t="str">
         <f>[1]ШР!P9</f>
         <v>Гасанов Камиль Мурадович</v>
       </c>
-      <c r="D12" s="176" t="s">
+      <c r="D12" s="162" t="s">
         <v>364</v>
       </c>
-      <c r="E12" s="162" t="s">
+      <c r="E12" s="153" t="s">
         <v>1078</v>
       </c>
-      <c r="F12" s="162" t="str">
+      <c r="F12" s="153" t="str">
         <f>IFERROR(INDEX([1]ШР!M:M,MATCH('[1]Шаблон Табеля'!C12:C13,[1]ШР!P:P,0)),"")</f>
         <v>Отдел Единой государственной автоматизированной информационной системы</v>
       </c>
-      <c r="G12" s="166" t="s">
+      <c r="G12" s="171" t="s">
         <v>142</v>
       </c>
       <c r="H12" s="32" t="s">
@@ -10442,79 +10450,79 @@
       <c r="AJ12" s="91"/>
       <c r="AK12" s="91"/>
       <c r="AL12" s="91"/>
-      <c r="AM12" s="155">
+      <c r="AM12" s="178">
         <f>IF(C12="","",COUNTIF(I12:W12,"Я")+COUNTIF(I12:W12,"Н")+COUNTIF(I12:W12,"Д")+COUNTIF(I12:W12,"РВ"))</f>
         <v>11</v>
       </c>
-      <c r="AN12" s="148">
+      <c r="AN12" s="135">
         <f>SUM(I13:W14)</f>
         <v>78</v>
       </c>
-      <c r="AO12" s="122">
-        <f t="shared" ref="AO12" si="0">SUM(I13:W13)</f>
+      <c r="AO12" s="178">
+        <f>SUM(I13:W13)</f>
         <v>55</v>
       </c>
-      <c r="AP12" s="148">
-        <f t="shared" ref="AP12" si="1">SUM(I14:W14)</f>
+      <c r="AP12" s="135">
+        <f>SUM(I14:W14)</f>
         <v>23</v>
       </c>
-      <c r="AQ12" s="110">
+      <c r="AQ12" s="126">
         <v>80</v>
       </c>
-      <c r="AR12" s="113">
+      <c r="AR12" s="119">
         <f>IF(G12="Женский",'ПК 2 Дагестан'!$G$22/2,'ПК 2 Дагестан'!$F$22/2)</f>
         <v>80.333333333333329</v>
       </c>
-      <c r="AS12" s="158">
+      <c r="AS12" s="129">
         <f>IFERROR(IF(C12="","",AN12-AQ12),"")</f>
         <v>-2</v>
       </c>
-      <c r="AT12" s="160">
+      <c r="AT12" s="175">
         <f>IF(C12="","",AN12-AR12)</f>
         <v>-2.3333333333333286</v>
       </c>
-      <c r="AU12" s="148">
+      <c r="AU12" s="135">
         <f>IF(C12="","",COUNTIF(I12:AL12,"Я")+COUNTIF(I12:AL12,"Н")+COUNTIF(I12:AL12,"Д")+COUNTIF(I12:AL12,"РВ"))</f>
         <v>11</v>
       </c>
-      <c r="AV12" s="149">
-        <f t="shared" ref="AV12" si="2">SUM(I13:AL14)</f>
+      <c r="AV12" s="124">
+        <f>SUM(I13:AL14)</f>
         <v>78</v>
       </c>
-      <c r="AW12" s="122">
-        <f t="shared" ref="AW12" si="3">SUM(I13:AL13)</f>
+      <c r="AW12" s="178">
+        <f>SUM(I13:AL13)</f>
         <v>55</v>
       </c>
-      <c r="AX12" s="148">
-        <f t="shared" ref="AX12" si="4">SUM(I14:AL14)</f>
+      <c r="AX12" s="135">
+        <f>SUM(I14:AL14)</f>
         <v>23</v>
       </c>
-      <c r="AY12" s="110">
+      <c r="AY12" s="126">
         <v>159</v>
       </c>
-      <c r="AZ12" s="113">
+      <c r="AZ12" s="119">
         <f>IF(G12="Женский",'ПК 2 Дагестан'!$G$22,'ПК 2 Дагестан'!$F$22)</f>
         <v>160.66666666666666</v>
       </c>
-      <c r="BA12" s="158">
+      <c r="BA12" s="129">
         <f>IFERROR(IF(C12="","",AV12-AY12),"")</f>
         <v>-81</v>
       </c>
-      <c r="BB12" s="202">
+      <c r="BB12" s="108">
         <f>IF(C12="","",AV12-AZ12)</f>
         <v>-82.666666666666657</v>
       </c>
-      <c r="BC12" s="196"/>
-      <c r="BD12" s="107"/>
-      <c r="BE12" s="107"/>
+      <c r="BC12" s="147"/>
+      <c r="BD12" s="143"/>
+      <c r="BE12" s="143"/>
     </row>
     <row r="13" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="B13" s="171"/>
-      <c r="C13" s="174"/>
-      <c r="D13" s="162"/>
-      <c r="E13" s="162"/>
-      <c r="F13" s="162"/>
-      <c r="G13" s="167"/>
+      <c r="B13" s="155"/>
+      <c r="C13" s="158"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="172"/>
       <c r="H13" s="33" t="s">
         <v>48</v>
       </c>
@@ -10570,33 +10578,33 @@
       <c r="AJ13" s="92"/>
       <c r="AK13" s="92"/>
       <c r="AL13" s="92"/>
-      <c r="AM13" s="156"/>
-      <c r="AN13" s="149"/>
-      <c r="AO13" s="123"/>
-      <c r="AP13" s="149"/>
-      <c r="AQ13" s="111"/>
-      <c r="AR13" s="114"/>
-      <c r="AS13" s="117"/>
-      <c r="AT13" s="120"/>
-      <c r="AU13" s="149"/>
-      <c r="AV13" s="149"/>
-      <c r="AW13" s="123"/>
-      <c r="AX13" s="149"/>
-      <c r="AY13" s="111"/>
-      <c r="AZ13" s="114"/>
-      <c r="BA13" s="117"/>
-      <c r="BB13" s="203"/>
-      <c r="BC13" s="197"/>
-      <c r="BD13" s="107"/>
-      <c r="BE13" s="107"/>
+      <c r="AM13" s="179"/>
+      <c r="AN13" s="124"/>
+      <c r="AO13" s="179"/>
+      <c r="AP13" s="124"/>
+      <c r="AQ13" s="127"/>
+      <c r="AR13" s="120"/>
+      <c r="AS13" s="123"/>
+      <c r="AT13" s="176"/>
+      <c r="AU13" s="124"/>
+      <c r="AV13" s="124"/>
+      <c r="AW13" s="179"/>
+      <c r="AX13" s="124"/>
+      <c r="AY13" s="127"/>
+      <c r="AZ13" s="120"/>
+      <c r="BA13" s="123"/>
+      <c r="BB13" s="109"/>
+      <c r="BC13" s="148"/>
+      <c r="BD13" s="143"/>
+      <c r="BE13" s="143"/>
     </row>
     <row r="14" spans="2:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="172"/>
-      <c r="C14" s="175"/>
-      <c r="D14" s="177"/>
-      <c r="E14" s="162"/>
-      <c r="F14" s="162"/>
-      <c r="G14" s="168"/>
+      <c r="B14" s="165"/>
+      <c r="C14" s="159"/>
+      <c r="D14" s="163"/>
+      <c r="E14" s="153"/>
+      <c r="F14" s="153"/>
+      <c r="G14" s="173"/>
       <c r="H14" s="34" t="s">
         <v>63</v>
       </c>
@@ -10644,45 +10652,45 @@
       <c r="AJ14" s="90"/>
       <c r="AK14" s="90"/>
       <c r="AL14" s="90"/>
-      <c r="AM14" s="157"/>
-      <c r="AN14" s="150"/>
-      <c r="AO14" s="124"/>
-      <c r="AP14" s="150"/>
-      <c r="AQ14" s="112"/>
-      <c r="AR14" s="115"/>
-      <c r="AS14" s="159"/>
-      <c r="AT14" s="161"/>
-      <c r="AU14" s="150"/>
-      <c r="AV14" s="149"/>
-      <c r="AW14" s="124"/>
-      <c r="AX14" s="150"/>
-      <c r="AY14" s="112"/>
-      <c r="AZ14" s="115"/>
-      <c r="BA14" s="159"/>
-      <c r="BB14" s="204"/>
-      <c r="BC14" s="198"/>
-      <c r="BD14" s="107"/>
-      <c r="BE14" s="107"/>
+      <c r="AM14" s="180"/>
+      <c r="AN14" s="125"/>
+      <c r="AO14" s="180"/>
+      <c r="AP14" s="125"/>
+      <c r="AQ14" s="128"/>
+      <c r="AR14" s="121"/>
+      <c r="AS14" s="130"/>
+      <c r="AT14" s="177"/>
+      <c r="AU14" s="125"/>
+      <c r="AV14" s="124"/>
+      <c r="AW14" s="180"/>
+      <c r="AX14" s="125"/>
+      <c r="AY14" s="128"/>
+      <c r="AZ14" s="121"/>
+      <c r="BA14" s="130"/>
+      <c r="BB14" s="110"/>
+      <c r="BC14" s="149"/>
+      <c r="BD14" s="143"/>
+      <c r="BE14" s="143"/>
     </row>
     <row r="15" spans="2:57" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="182">
+      <c r="B15" s="154">
         <v>3</v>
       </c>
-      <c r="C15" s="173" t="str">
+      <c r="C15" s="157" t="str">
         <f>[1]ШР!P10</f>
         <v>Герейханов Пирбала Тофикович</v>
       </c>
-      <c r="D15" s="176" t="s">
+      <c r="D15" s="162" t="s">
         <v>366</v>
       </c>
-      <c r="E15" s="162" t="s">
+      <c r="E15" s="153" t="s">
         <v>1078</v>
       </c>
-      <c r="F15" s="162" t="str">
+      <c r="F15" s="153" t="str">
         <f>IFERROR(INDEX([1]ШР!M:M,MATCH('[1]Шаблон Табеля'!C15:C16,[1]ШР!P:P,0)),"")</f>
         <v>Отдел Единой государственной автоматизированной информационной системы</v>
       </c>
-      <c r="G15" s="163" t="s">
+      <c r="G15" s="174" t="s">
         <v>142</v>
       </c>
       <c r="H15" s="32" t="s">
@@ -10738,34 +10746,34 @@
       <c r="AJ15" s="91"/>
       <c r="AK15" s="91"/>
       <c r="AL15" s="91"/>
-      <c r="AM15" s="165">
+      <c r="AM15" s="178">
         <f>IF(C15="","",COUNTIF(I15:W15,"Я")+COUNTIF(I15:W15,"Н")+COUNTIF(I15:W15,"Д")+COUNTIF(I15:W15,"РВ"))</f>
         <v>1</v>
       </c>
-      <c r="AN15" s="148">
-        <f t="shared" ref="AN15" si="5">SUM(I16:W17)</f>
+      <c r="AN15" s="135">
+        <f>SUM(I16:W17)</f>
         <v>11</v>
       </c>
-      <c r="AO15" s="122">
-        <f t="shared" ref="AO15" si="6">SUM(I16:W16)</f>
+      <c r="AO15" s="178">
+        <f>SUM(I16:W16)</f>
         <v>11</v>
       </c>
-      <c r="AP15" s="148">
-        <f t="shared" ref="AP15" si="7">SUM(I17:W17)</f>
+      <c r="AP15" s="135">
+        <f>SUM(I17:W17)</f>
         <v>0</v>
       </c>
-      <c r="AQ15" s="110">
+      <c r="AQ15" s="126">
         <v>80</v>
       </c>
-      <c r="AR15" s="113">
+      <c r="AR15" s="119">
         <f>IF(G15="Женский",'ПК 2 Дагестан'!$G$22/2,'ПК 2 Дагестан'!$F$22/2)</f>
         <v>80.333333333333329</v>
       </c>
-      <c r="AS15" s="116">
+      <c r="AS15" s="122">
         <f>IFERROR(IF(C15="","",AN15-AQ15),"")</f>
         <v>-69</v>
       </c>
-      <c r="AT15" s="119">
+      <c r="AT15" s="181">
         <f>IF(C15="","",AN15-AR15)</f>
         <v>-69.333333333333329</v>
       </c>
@@ -10773,48 +10781,48 @@
         <f>IF(C15="","",COUNTIF(I15:AL15,"Я")+COUNTIF(I15:AL15,"Н")+COUNTIF(I15:AL15,"Д")+COUNTIF(I15:AL15,"РВ"))</f>
         <v>1</v>
       </c>
-      <c r="AV15" s="149">
-        <f t="shared" ref="AV15" si="8">SUM(I16:AL17)</f>
+      <c r="AV15" s="124">
+        <f>SUM(I16:AL17)</f>
         <v>11</v>
       </c>
-      <c r="AW15" s="122">
-        <f t="shared" ref="AW15" si="9">SUM(I16:AL16)</f>
+      <c r="AW15" s="178">
+        <f>SUM(I16:AL16)</f>
         <v>11</v>
       </c>
-      <c r="AX15" s="148">
-        <f t="shared" ref="AX15" si="10">SUM(I17:AL17)</f>
+      <c r="AX15" s="135">
+        <f>SUM(I17:AL17)</f>
         <v>0</v>
       </c>
-      <c r="AY15" s="110">
+      <c r="AY15" s="126">
         <v>159</v>
       </c>
-      <c r="AZ15" s="113">
+      <c r="AZ15" s="119">
         <f>IF(G15="Женский",'ПК 2 Дагестан'!$G$22,'ПК 2 Дагестан'!$F$22)</f>
         <v>160.66666666666666</v>
       </c>
-      <c r="BA15" s="116">
+      <c r="BA15" s="122">
         <f>IFERROR(IF(C15="","",AV15-AY15),"")</f>
         <v>-148</v>
       </c>
-      <c r="BB15" s="209">
+      <c r="BB15" s="117">
         <f>IF(C15="","",AV15-AZ15)</f>
         <v>-149.66666666666666</v>
       </c>
-      <c r="BC15" s="196"/>
-      <c r="BD15" s="107"/>
-      <c r="BE15" s="107"/>
+      <c r="BC15" s="147"/>
+      <c r="BD15" s="143"/>
+      <c r="BE15" s="143"/>
     </row>
     <row r="16" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="B16" s="171"/>
-      <c r="C16" s="174"/>
-      <c r="D16" s="162"/>
-      <c r="E16" s="162"/>
-      <c r="F16" s="162"/>
-      <c r="G16" s="164"/>
+      <c r="B16" s="155"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
+      <c r="F16" s="153"/>
+      <c r="G16" s="167"/>
       <c r="H16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="283"/>
+      <c r="I16" s="100"/>
       <c r="J16" s="92"/>
       <c r="K16" s="92"/>
       <c r="L16" s="92"/>
@@ -10846,37 +10854,37 @@
       <c r="AJ16" s="92"/>
       <c r="AK16" s="92"/>
       <c r="AL16" s="92"/>
-      <c r="AM16" s="156"/>
-      <c r="AN16" s="149"/>
-      <c r="AO16" s="123"/>
-      <c r="AP16" s="149"/>
-      <c r="AQ16" s="111"/>
-      <c r="AR16" s="114"/>
-      <c r="AS16" s="117"/>
-      <c r="AT16" s="120"/>
-      <c r="AU16" s="149"/>
-      <c r="AV16" s="149"/>
-      <c r="AW16" s="123"/>
-      <c r="AX16" s="149"/>
-      <c r="AY16" s="111"/>
-      <c r="AZ16" s="114"/>
-      <c r="BA16" s="117"/>
-      <c r="BB16" s="203"/>
-      <c r="BC16" s="197"/>
-      <c r="BD16" s="107"/>
-      <c r="BE16" s="107"/>
+      <c r="AM16" s="179"/>
+      <c r="AN16" s="124"/>
+      <c r="AO16" s="179"/>
+      <c r="AP16" s="124"/>
+      <c r="AQ16" s="127"/>
+      <c r="AR16" s="120"/>
+      <c r="AS16" s="123"/>
+      <c r="AT16" s="176"/>
+      <c r="AU16" s="124"/>
+      <c r="AV16" s="124"/>
+      <c r="AW16" s="179"/>
+      <c r="AX16" s="124"/>
+      <c r="AY16" s="127"/>
+      <c r="AZ16" s="120"/>
+      <c r="BA16" s="123"/>
+      <c r="BB16" s="109"/>
+      <c r="BC16" s="148"/>
+      <c r="BD16" s="143"/>
+      <c r="BE16" s="143"/>
     </row>
     <row r="17" spans="2:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="171"/>
-      <c r="C17" s="175"/>
-      <c r="D17" s="177"/>
-      <c r="E17" s="162"/>
-      <c r="F17" s="162"/>
-      <c r="G17" s="164"/>
+      <c r="B17" s="155"/>
+      <c r="C17" s="159"/>
+      <c r="D17" s="163"/>
+      <c r="E17" s="153"/>
+      <c r="F17" s="153"/>
+      <c r="G17" s="167"/>
       <c r="H17" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="I17" s="282"/>
+      <c r="I17" s="106"/>
       <c r="J17" s="90"/>
       <c r="K17" s="90"/>
       <c r="L17" s="90"/>
@@ -10906,51 +10914,51 @@
       <c r="AJ17" s="90"/>
       <c r="AK17" s="90"/>
       <c r="AL17" s="90"/>
-      <c r="AM17" s="156"/>
-      <c r="AN17" s="150"/>
-      <c r="AO17" s="124"/>
-      <c r="AP17" s="150"/>
-      <c r="AQ17" s="112"/>
-      <c r="AR17" s="115"/>
-      <c r="AS17" s="117"/>
-      <c r="AT17" s="120"/>
-      <c r="AU17" s="149"/>
-      <c r="AV17" s="149"/>
-      <c r="AW17" s="124"/>
-      <c r="AX17" s="150"/>
-      <c r="AY17" s="112"/>
-      <c r="AZ17" s="115"/>
-      <c r="BA17" s="117"/>
-      <c r="BB17" s="203"/>
-      <c r="BC17" s="198"/>
-      <c r="BD17" s="107"/>
-      <c r="BE17" s="107"/>
+      <c r="AM17" s="180"/>
+      <c r="AN17" s="125"/>
+      <c r="AO17" s="180"/>
+      <c r="AP17" s="125"/>
+      <c r="AQ17" s="128"/>
+      <c r="AR17" s="121"/>
+      <c r="AS17" s="123"/>
+      <c r="AT17" s="176"/>
+      <c r="AU17" s="124"/>
+      <c r="AV17" s="124"/>
+      <c r="AW17" s="180"/>
+      <c r="AX17" s="125"/>
+      <c r="AY17" s="128"/>
+      <c r="AZ17" s="121"/>
+      <c r="BA17" s="123"/>
+      <c r="BB17" s="109"/>
+      <c r="BC17" s="149"/>
+      <c r="BD17" s="143"/>
+      <c r="BE17" s="143"/>
     </row>
     <row r="18" spans="2:57" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="170">
+      <c r="B18" s="164">
         <v>4</v>
       </c>
-      <c r="C18" s="173" t="str">
+      <c r="C18" s="157" t="str">
         <f>[1]ШР!P11</f>
         <v>Гусейнов Вели Гусеевич</v>
       </c>
-      <c r="D18" s="176" t="s">
+      <c r="D18" s="162" t="s">
         <v>1080</v>
       </c>
-      <c r="E18" s="162" t="s">
+      <c r="E18" s="153" t="s">
         <v>1078</v>
       </c>
-      <c r="F18" s="162" t="str">
+      <c r="F18" s="153" t="str">
         <f>IFERROR(INDEX([1]ШР!M:M,MATCH('[1]Шаблон Табеля'!C18:C19,[1]ШР!P:P,0)),"")</f>
         <v>Отдел Единой государственной автоматизированной информационной системы</v>
       </c>
-      <c r="G18" s="178" t="s">
+      <c r="G18" s="166" t="s">
         <v>142</v>
       </c>
       <c r="H18" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="I18" s="285"/>
+      <c r="I18" s="107"/>
       <c r="J18" s="91" t="s">
         <v>8</v>
       </c>
@@ -11000,83 +11008,83 @@
       <c r="AJ18" s="91"/>
       <c r="AK18" s="91"/>
       <c r="AL18" s="91"/>
-      <c r="AM18" s="155">
+      <c r="AM18" s="178">
         <f>IF(C18="","",COUNTIF(I18:W18,"Я")+COUNTIF(I18:W18,"Н")+COUNTIF(I18:W18,"Д")+COUNTIF(I18:W18,"РВ"))</f>
         <v>10</v>
       </c>
-      <c r="AN18" s="148">
-        <f t="shared" ref="AN18" si="11">SUM(I19:W20)</f>
+      <c r="AN18" s="135">
+        <f>SUM(I19:W20)</f>
         <v>82</v>
       </c>
-      <c r="AO18" s="122">
-        <f t="shared" ref="AO18" si="12">SUM(I19:W19)</f>
+      <c r="AO18" s="178">
+        <f>SUM(I19:W19)</f>
         <v>61</v>
       </c>
-      <c r="AP18" s="148">
-        <f t="shared" ref="AP18" si="13">SUM(I20:W20)</f>
+      <c r="AP18" s="135">
+        <f>SUM(I20:W20)</f>
         <v>21</v>
       </c>
-      <c r="AQ18" s="110">
+      <c r="AQ18" s="126">
         <v>80</v>
       </c>
-      <c r="AR18" s="113">
+      <c r="AR18" s="119">
         <f>IF(G18="Женский",'ПК 2 Дагестан'!$G$22/2,'ПК 2 Дагестан'!$F$22/2)</f>
         <v>80.333333333333329</v>
       </c>
-      <c r="AS18" s="158">
+      <c r="AS18" s="129">
         <f>IFERROR(IF(C18="","",AN18-AQ18),"")</f>
         <v>2</v>
       </c>
-      <c r="AT18" s="160">
+      <c r="AT18" s="175">
         <f>IF(C18="","",AN18-AR18)</f>
         <v>1.6666666666666714</v>
       </c>
-      <c r="AU18" s="148">
+      <c r="AU18" s="135">
         <f>IF(C18="","",COUNTIF(I18:AL18,"Я")+COUNTIF(I18:AL18,"Н")+COUNTIF(I18:AL18,"Д")+COUNTIF(I18:AL18,"РВ"))</f>
         <v>10</v>
       </c>
-      <c r="AV18" s="149">
-        <f t="shared" ref="AV18" si="14">SUM(I19:AL20)</f>
+      <c r="AV18" s="124">
+        <f>SUM(I19:AL20)</f>
         <v>82</v>
       </c>
-      <c r="AW18" s="122">
-        <f t="shared" ref="AW18" si="15">SUM(I19:AL19)</f>
+      <c r="AW18" s="178">
+        <f>SUM(I19:AL19)</f>
         <v>61</v>
       </c>
-      <c r="AX18" s="148">
-        <f t="shared" ref="AX18" si="16">SUM(I20:AL20)</f>
+      <c r="AX18" s="135">
+        <f>SUM(I20:AL20)</f>
         <v>21</v>
       </c>
-      <c r="AY18" s="110">
+      <c r="AY18" s="126">
         <v>159</v>
       </c>
-      <c r="AZ18" s="113">
+      <c r="AZ18" s="119">
         <f>IF(G18="Женский",'ПК 2 Дагестан'!$G$22,'ПК 2 Дагестан'!$F$22)</f>
         <v>160.66666666666666</v>
       </c>
-      <c r="BA18" s="158">
+      <c r="BA18" s="129">
         <f>IFERROR(IF(C18="","",AV18-AY18),"")</f>
         <v>-77</v>
       </c>
-      <c r="BB18" s="202">
+      <c r="BB18" s="108">
         <f>IF(C18="","",AV18-AZ18)</f>
         <v>-78.666666666666657</v>
       </c>
-      <c r="BC18" s="196"/>
-      <c r="BD18" s="107"/>
-      <c r="BE18" s="107"/>
+      <c r="BC18" s="147"/>
+      <c r="BD18" s="143"/>
+      <c r="BE18" s="143"/>
     </row>
     <row r="19" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="B19" s="171"/>
-      <c r="C19" s="174"/>
-      <c r="D19" s="162"/>
-      <c r="E19" s="162"/>
-      <c r="F19" s="162"/>
-      <c r="G19" s="164"/>
+      <c r="B19" s="155"/>
+      <c r="C19" s="158"/>
+      <c r="D19" s="153"/>
+      <c r="E19" s="153"/>
+      <c r="F19" s="153"/>
+      <c r="G19" s="167"/>
       <c r="H19" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="I19" s="283"/>
+      <c r="I19" s="100"/>
       <c r="J19" s="92">
         <v>11</v>
       </c>
@@ -11126,37 +11134,37 @@
       <c r="AJ19" s="92"/>
       <c r="AK19" s="92"/>
       <c r="AL19" s="92"/>
-      <c r="AM19" s="156"/>
-      <c r="AN19" s="149"/>
-      <c r="AO19" s="123"/>
-      <c r="AP19" s="149"/>
-      <c r="AQ19" s="111"/>
-      <c r="AR19" s="114"/>
-      <c r="AS19" s="117"/>
-      <c r="AT19" s="120"/>
-      <c r="AU19" s="149"/>
-      <c r="AV19" s="149"/>
-      <c r="AW19" s="123"/>
-      <c r="AX19" s="149"/>
-      <c r="AY19" s="111"/>
-      <c r="AZ19" s="114"/>
-      <c r="BA19" s="117"/>
-      <c r="BB19" s="203"/>
-      <c r="BC19" s="197"/>
-      <c r="BD19" s="107"/>
-      <c r="BE19" s="107"/>
+      <c r="AM19" s="179"/>
+      <c r="AN19" s="124"/>
+      <c r="AO19" s="179"/>
+      <c r="AP19" s="124"/>
+      <c r="AQ19" s="127"/>
+      <c r="AR19" s="120"/>
+      <c r="AS19" s="123"/>
+      <c r="AT19" s="176"/>
+      <c r="AU19" s="124"/>
+      <c r="AV19" s="124"/>
+      <c r="AW19" s="179"/>
+      <c r="AX19" s="124"/>
+      <c r="AY19" s="127"/>
+      <c r="AZ19" s="120"/>
+      <c r="BA19" s="123"/>
+      <c r="BB19" s="109"/>
+      <c r="BC19" s="148"/>
+      <c r="BD19" s="143"/>
+      <c r="BE19" s="143"/>
     </row>
     <row r="20" spans="2:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="172"/>
-      <c r="C20" s="175"/>
-      <c r="D20" s="177"/>
-      <c r="E20" s="162"/>
-      <c r="F20" s="162"/>
-      <c r="G20" s="179"/>
+      <c r="B20" s="165"/>
+      <c r="C20" s="159"/>
+      <c r="D20" s="163"/>
+      <c r="E20" s="153"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="168"/>
       <c r="H20" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="I20" s="284"/>
+      <c r="I20" s="90"/>
       <c r="J20" s="90"/>
       <c r="K20" s="90">
         <v>2</v>
@@ -11196,45 +11204,45 @@
       <c r="AJ20" s="90"/>
       <c r="AK20" s="90"/>
       <c r="AL20" s="90"/>
-      <c r="AM20" s="157"/>
-      <c r="AN20" s="150"/>
-      <c r="AO20" s="124"/>
-      <c r="AP20" s="150"/>
-      <c r="AQ20" s="112"/>
-      <c r="AR20" s="115"/>
-      <c r="AS20" s="159"/>
-      <c r="AT20" s="161"/>
-      <c r="AU20" s="150"/>
-      <c r="AV20" s="149"/>
-      <c r="AW20" s="124"/>
-      <c r="AX20" s="150"/>
-      <c r="AY20" s="112"/>
-      <c r="AZ20" s="115"/>
-      <c r="BA20" s="159"/>
-      <c r="BB20" s="204"/>
-      <c r="BC20" s="198"/>
-      <c r="BD20" s="107"/>
-      <c r="BE20" s="107"/>
+      <c r="AM20" s="180"/>
+      <c r="AN20" s="125"/>
+      <c r="AO20" s="180"/>
+      <c r="AP20" s="125"/>
+      <c r="AQ20" s="128"/>
+      <c r="AR20" s="121"/>
+      <c r="AS20" s="130"/>
+      <c r="AT20" s="177"/>
+      <c r="AU20" s="125"/>
+      <c r="AV20" s="124"/>
+      <c r="AW20" s="180"/>
+      <c r="AX20" s="125"/>
+      <c r="AY20" s="128"/>
+      <c r="AZ20" s="121"/>
+      <c r="BA20" s="130"/>
+      <c r="BB20" s="110"/>
+      <c r="BC20" s="149"/>
+      <c r="BD20" s="143"/>
+      <c r="BE20" s="143"/>
     </row>
     <row r="21" spans="2:57" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="170">
+      <c r="B21" s="164">
         <v>5</v>
       </c>
-      <c r="C21" s="173" t="str">
+      <c r="C21" s="157" t="str">
         <f>[1]ШР!P12</f>
         <v>Мирзоев Ханахмед Бегахмедович</v>
       </c>
-      <c r="D21" s="176" t="s">
+      <c r="D21" s="162" t="s">
         <v>370</v>
       </c>
-      <c r="E21" s="162" t="s">
+      <c r="E21" s="153" t="s">
         <v>1079</v>
       </c>
-      <c r="F21" s="162" t="str">
+      <c r="F21" s="153" t="str">
         <f>IFERROR(INDEX([1]ШР!M:M,MATCH('[1]Шаблон Табеля'!C21:C22,[1]ШР!P:P,0)),"")</f>
         <v>Отдел Единой государственной автоматизированной информационной системы</v>
       </c>
-      <c r="G21" s="178" t="s">
+      <c r="G21" s="166" t="s">
         <v>142</v>
       </c>
       <c r="H21" s="35" t="s">
@@ -11292,79 +11300,79 @@
       <c r="AJ21" s="91"/>
       <c r="AK21" s="91"/>
       <c r="AL21" s="91"/>
-      <c r="AM21" s="155">
+      <c r="AM21" s="178">
         <f>IF(C21="","",COUNTIF(I21:W21,"Я")+COUNTIF(I21:W21,"Н")+COUNTIF(I21:W21,"Д")+COUNTIF(I21:W21,"РВ"))</f>
         <v>11</v>
       </c>
-      <c r="AN21" s="148">
-        <f t="shared" ref="AN21" si="17">SUM(I22:W23)</f>
+      <c r="AN21" s="135">
+        <f>SUM(I22:W23)</f>
         <v>88</v>
       </c>
-      <c r="AO21" s="122">
-        <f t="shared" ref="AO21" si="18">SUM(I22:W22)</f>
+      <c r="AO21" s="178">
+        <f>SUM(I22:W22)</f>
         <v>67</v>
       </c>
-      <c r="AP21" s="148">
-        <f t="shared" ref="AP21" si="19">SUM(I23:W23)</f>
+      <c r="AP21" s="135">
+        <f>SUM(I23:W23)</f>
         <v>21</v>
       </c>
-      <c r="AQ21" s="110">
+      <c r="AQ21" s="126">
         <v>80</v>
       </c>
-      <c r="AR21" s="113">
+      <c r="AR21" s="119">
         <f>IF(G21="Женский",'ПК 2 Дагестан'!$G$22/2,'ПК 2 Дагестан'!$F$22/2)</f>
         <v>80.333333333333329</v>
       </c>
-      <c r="AS21" s="158">
+      <c r="AS21" s="129">
         <f>IFERROR(IF(C21="","",AN21-AQ21),"")</f>
         <v>8</v>
       </c>
-      <c r="AT21" s="160">
+      <c r="AT21" s="175">
         <f>IF(C21="","",AN21-AR21)</f>
         <v>7.6666666666666714</v>
       </c>
-      <c r="AU21" s="148">
+      <c r="AU21" s="135">
         <f>IF(C21="","",COUNTIF(I21:AL21,"Я")+COUNTIF(I21:AL21,"Н")+COUNTIF(I21:AL21,"Д")+COUNTIF(I21:AL21,"РВ"))</f>
         <v>11</v>
       </c>
-      <c r="AV21" s="149">
-        <f t="shared" ref="AV21" si="20">SUM(I22:AL23)</f>
+      <c r="AV21" s="124">
+        <f>SUM(I22:AL23)</f>
         <v>88</v>
       </c>
-      <c r="AW21" s="122">
-        <f t="shared" ref="AW21" si="21">SUM(I22:AL22)</f>
+      <c r="AW21" s="178">
+        <f>SUM(I22:AL22)</f>
         <v>67</v>
       </c>
-      <c r="AX21" s="148">
-        <f t="shared" ref="AX21" si="22">SUM(I23:AL23)</f>
+      <c r="AX21" s="135">
+        <f t="shared" ref="AX21" si="0">SUM(I23:AL23)</f>
         <v>21</v>
       </c>
-      <c r="AY21" s="110">
+      <c r="AY21" s="126">
         <v>159</v>
       </c>
-      <c r="AZ21" s="113">
+      <c r="AZ21" s="119">
         <f>IF(G21="Женский",'ПК 2 Дагестан'!$G$22,'ПК 2 Дагестан'!$F$22)</f>
         <v>160.66666666666666</v>
       </c>
-      <c r="BA21" s="158">
+      <c r="BA21" s="129">
         <f>IFERROR(IF(C21="","",AV21-AY21),"")</f>
         <v>-71</v>
       </c>
-      <c r="BB21" s="202">
+      <c r="BB21" s="108">
         <f>IF(C21="","",AV21-AZ21)</f>
         <v>-72.666666666666657</v>
       </c>
-      <c r="BC21" s="196"/>
-      <c r="BD21" s="107"/>
-      <c r="BE21" s="107"/>
+      <c r="BC21" s="147"/>
+      <c r="BD21" s="143"/>
+      <c r="BE21" s="143"/>
     </row>
     <row r="22" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="B22" s="171"/>
-      <c r="C22" s="174"/>
-      <c r="D22" s="162"/>
-      <c r="E22" s="162"/>
-      <c r="F22" s="162"/>
-      <c r="G22" s="164"/>
+      <c r="B22" s="155"/>
+      <c r="C22" s="158"/>
+      <c r="D22" s="153"/>
+      <c r="E22" s="153"/>
+      <c r="F22" s="153"/>
+      <c r="G22" s="167"/>
       <c r="H22" s="33" t="s">
         <v>48</v>
       </c>
@@ -11420,37 +11428,37 @@
       <c r="AJ22" s="92"/>
       <c r="AK22" s="92"/>
       <c r="AL22" s="92"/>
-      <c r="AM22" s="156"/>
-      <c r="AN22" s="149"/>
-      <c r="AO22" s="123"/>
-      <c r="AP22" s="149"/>
-      <c r="AQ22" s="111"/>
-      <c r="AR22" s="114"/>
-      <c r="AS22" s="117"/>
-      <c r="AT22" s="120"/>
-      <c r="AU22" s="149"/>
-      <c r="AV22" s="149"/>
-      <c r="AW22" s="123"/>
-      <c r="AX22" s="149"/>
-      <c r="AY22" s="111"/>
-      <c r="AZ22" s="114"/>
-      <c r="BA22" s="117"/>
-      <c r="BB22" s="203"/>
-      <c r="BC22" s="197"/>
-      <c r="BD22" s="107"/>
-      <c r="BE22" s="107"/>
+      <c r="AM22" s="179"/>
+      <c r="AN22" s="124"/>
+      <c r="AO22" s="179"/>
+      <c r="AP22" s="124"/>
+      <c r="AQ22" s="127"/>
+      <c r="AR22" s="120"/>
+      <c r="AS22" s="123"/>
+      <c r="AT22" s="176"/>
+      <c r="AU22" s="124"/>
+      <c r="AV22" s="124"/>
+      <c r="AW22" s="179"/>
+      <c r="AX22" s="124"/>
+      <c r="AY22" s="127"/>
+      <c r="AZ22" s="120"/>
+      <c r="BA22" s="123"/>
+      <c r="BB22" s="109"/>
+      <c r="BC22" s="148"/>
+      <c r="BD22" s="143"/>
+      <c r="BE22" s="143"/>
     </row>
     <row r="23" spans="2:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="172"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="177"/>
-      <c r="E23" s="162"/>
-      <c r="F23" s="162"/>
-      <c r="G23" s="179"/>
+      <c r="B23" s="165"/>
+      <c r="C23" s="159"/>
+      <c r="D23" s="163"/>
+      <c r="E23" s="153"/>
+      <c r="F23" s="153"/>
+      <c r="G23" s="168"/>
       <c r="H23" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="I23" s="282"/>
+      <c r="I23" s="106"/>
       <c r="J23" s="90"/>
       <c r="K23" s="90"/>
       <c r="L23" s="90">
@@ -11492,28 +11500,159 @@
       <c r="AJ23" s="90"/>
       <c r="AK23" s="90"/>
       <c r="AL23" s="90"/>
-      <c r="AM23" s="157"/>
-      <c r="AN23" s="150"/>
-      <c r="AO23" s="124"/>
-      <c r="AP23" s="150"/>
-      <c r="AQ23" s="112"/>
-      <c r="AR23" s="115"/>
-      <c r="AS23" s="159"/>
-      <c r="AT23" s="161"/>
-      <c r="AU23" s="150"/>
-      <c r="AV23" s="150"/>
-      <c r="AW23" s="124"/>
-      <c r="AX23" s="150"/>
-      <c r="AY23" s="112"/>
-      <c r="AZ23" s="115"/>
-      <c r="BA23" s="159"/>
-      <c r="BB23" s="204"/>
-      <c r="BC23" s="198"/>
-      <c r="BD23" s="107"/>
-      <c r="BE23" s="107"/>
+      <c r="AM23" s="180"/>
+      <c r="AN23" s="125"/>
+      <c r="AO23" s="180"/>
+      <c r="AP23" s="125"/>
+      <c r="AQ23" s="128"/>
+      <c r="AR23" s="121"/>
+      <c r="AS23" s="130"/>
+      <c r="AT23" s="177"/>
+      <c r="AU23" s="125"/>
+      <c r="AV23" s="125"/>
+      <c r="AW23" s="180"/>
+      <c r="AX23" s="125"/>
+      <c r="AY23" s="128"/>
+      <c r="AZ23" s="121"/>
+      <c r="BA23" s="130"/>
+      <c r="BB23" s="110"/>
+      <c r="BC23" s="149"/>
+      <c r="BD23" s="143"/>
+      <c r="BE23" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="155">
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="AQ9:AQ11"/>
+    <mergeCell ref="AR9:AR11"/>
+    <mergeCell ref="AS9:AS11"/>
+    <mergeCell ref="AT9:AT11"/>
+    <mergeCell ref="AW9:AW11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:AL6"/>
+    <mergeCell ref="AM5:AT6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="AR7:AR8"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="AU7:AX7"/>
+    <mergeCell ref="AX9:AX11"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="AM7:AP7"/>
+    <mergeCell ref="AT7:AT8"/>
+    <mergeCell ref="AS7:AS8"/>
+    <mergeCell ref="AX21:AX23"/>
+    <mergeCell ref="AW15:AW17"/>
+    <mergeCell ref="AW18:AW20"/>
+    <mergeCell ref="AW21:AW23"/>
+    <mergeCell ref="AO15:AO17"/>
+    <mergeCell ref="AO18:AO20"/>
+    <mergeCell ref="AO21:AO23"/>
+    <mergeCell ref="AN12:AN14"/>
+    <mergeCell ref="AQ12:AQ14"/>
+    <mergeCell ref="AR12:AR14"/>
+    <mergeCell ref="AM12:AM14"/>
+    <mergeCell ref="AM21:AM23"/>
+    <mergeCell ref="AR21:AR23"/>
+    <mergeCell ref="AS21:AS23"/>
+    <mergeCell ref="AQ21:AQ23"/>
+    <mergeCell ref="AT21:AT23"/>
+    <mergeCell ref="AX18:AX20"/>
+    <mergeCell ref="AS18:AS20"/>
+    <mergeCell ref="AQ18:AQ20"/>
+    <mergeCell ref="AR18:AR20"/>
+    <mergeCell ref="AT18:AT20"/>
+    <mergeCell ref="AY12:AY14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="AM15:AM17"/>
+    <mergeCell ref="AN15:AN17"/>
+    <mergeCell ref="AQ15:AQ17"/>
+    <mergeCell ref="AT12:AT14"/>
+    <mergeCell ref="AU12:AU14"/>
+    <mergeCell ref="AX15:AX17"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="AX12:AX14"/>
+    <mergeCell ref="AW12:AW14"/>
+    <mergeCell ref="AO12:AO14"/>
+    <mergeCell ref="AP12:AP14"/>
+    <mergeCell ref="AV12:AV14"/>
+    <mergeCell ref="AR15:AR17"/>
+    <mergeCell ref="AS15:AS17"/>
+    <mergeCell ref="AT15:AT17"/>
+    <mergeCell ref="AU15:AU17"/>
+    <mergeCell ref="AY7:AY8"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="AN21:AN23"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="AM18:AM20"/>
+    <mergeCell ref="AN18:AN20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="AS12:AS14"/>
+    <mergeCell ref="AU9:AU11"/>
+    <mergeCell ref="AU18:AU20"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="AP15:AP17"/>
+    <mergeCell ref="AP18:AP20"/>
+    <mergeCell ref="AP21:AP23"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="AP9:AP11"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="BE9:BE11"/>
+    <mergeCell ref="BE12:BE14"/>
+    <mergeCell ref="BE15:BE17"/>
+    <mergeCell ref="BE18:BE20"/>
+    <mergeCell ref="BE21:BE23"/>
+    <mergeCell ref="BD9:BD11"/>
+    <mergeCell ref="BD12:BD14"/>
+    <mergeCell ref="BD15:BD17"/>
+    <mergeCell ref="BD18:BD20"/>
+    <mergeCell ref="BD21:BD23"/>
+    <mergeCell ref="BC5:BC8"/>
+    <mergeCell ref="BC9:BC11"/>
+    <mergeCell ref="BC12:BC14"/>
+    <mergeCell ref="BC15:BC17"/>
+    <mergeCell ref="BC18:BC20"/>
+    <mergeCell ref="BC21:BC23"/>
+    <mergeCell ref="AZ9:AZ11"/>
+    <mergeCell ref="BA9:BA11"/>
+    <mergeCell ref="BB21:BB23"/>
+    <mergeCell ref="BB12:BB14"/>
     <mergeCell ref="BB18:BB20"/>
     <mergeCell ref="AU5:BB6"/>
     <mergeCell ref="BB9:BB11"/>
@@ -11538,170 +11677,39 @@
     <mergeCell ref="AZ18:AZ20"/>
     <mergeCell ref="AY15:AY17"/>
     <mergeCell ref="AV15:AV17"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="BE9:BE11"/>
-    <mergeCell ref="BE12:BE14"/>
-    <mergeCell ref="BE15:BE17"/>
-    <mergeCell ref="BE18:BE20"/>
-    <mergeCell ref="BE21:BE23"/>
-    <mergeCell ref="BD9:BD11"/>
-    <mergeCell ref="BD12:BD14"/>
-    <mergeCell ref="BD15:BD17"/>
-    <mergeCell ref="BD18:BD20"/>
-    <mergeCell ref="BD21:BD23"/>
-    <mergeCell ref="BC5:BC8"/>
-    <mergeCell ref="BC9:BC11"/>
-    <mergeCell ref="BC12:BC14"/>
-    <mergeCell ref="BC15:BC17"/>
-    <mergeCell ref="BC18:BC20"/>
-    <mergeCell ref="BC21:BC23"/>
-    <mergeCell ref="AZ9:AZ11"/>
-    <mergeCell ref="BA9:BA11"/>
-    <mergeCell ref="BB21:BB23"/>
-    <mergeCell ref="BB12:BB14"/>
-    <mergeCell ref="AU18:AU20"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="AP15:AP17"/>
-    <mergeCell ref="AP18:AP20"/>
-    <mergeCell ref="AP21:AP23"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="AP9:AP11"/>
-    <mergeCell ref="AY7:AY8"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="AN21:AN23"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="AM18:AM20"/>
-    <mergeCell ref="AN18:AN20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="AS12:AS14"/>
-    <mergeCell ref="AU9:AU11"/>
-    <mergeCell ref="AY12:AY14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="AM15:AM17"/>
-    <mergeCell ref="AN15:AN17"/>
-    <mergeCell ref="AQ15:AQ17"/>
-    <mergeCell ref="AT12:AT14"/>
-    <mergeCell ref="AU12:AU14"/>
-    <mergeCell ref="AX15:AX17"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="AX12:AX14"/>
-    <mergeCell ref="AW12:AW14"/>
-    <mergeCell ref="AO12:AO14"/>
-    <mergeCell ref="AP12:AP14"/>
-    <mergeCell ref="AV12:AV14"/>
-    <mergeCell ref="AR15:AR17"/>
-    <mergeCell ref="AS15:AS17"/>
-    <mergeCell ref="AT15:AT17"/>
-    <mergeCell ref="AU15:AU17"/>
-    <mergeCell ref="AM7:AP7"/>
-    <mergeCell ref="AT7:AT8"/>
-    <mergeCell ref="AS7:AS8"/>
-    <mergeCell ref="AX21:AX23"/>
-    <mergeCell ref="AW15:AW17"/>
-    <mergeCell ref="AW18:AW20"/>
-    <mergeCell ref="AW21:AW23"/>
-    <mergeCell ref="AO15:AO17"/>
-    <mergeCell ref="AO18:AO20"/>
-    <mergeCell ref="AO21:AO23"/>
-    <mergeCell ref="AN12:AN14"/>
-    <mergeCell ref="AQ12:AQ14"/>
-    <mergeCell ref="AR12:AR14"/>
-    <mergeCell ref="AM12:AM14"/>
-    <mergeCell ref="AM21:AM23"/>
-    <mergeCell ref="AR21:AR23"/>
-    <mergeCell ref="AS21:AS23"/>
-    <mergeCell ref="AQ21:AQ23"/>
-    <mergeCell ref="AT21:AT23"/>
-    <mergeCell ref="AX18:AX20"/>
-    <mergeCell ref="AS18:AS20"/>
-    <mergeCell ref="AQ18:AQ20"/>
-    <mergeCell ref="AR18:AR20"/>
-    <mergeCell ref="AT18:AT20"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="AM2:AM3"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="AQ9:AQ11"/>
-    <mergeCell ref="AR9:AR11"/>
-    <mergeCell ref="AS9:AS11"/>
-    <mergeCell ref="AT9:AT11"/>
-    <mergeCell ref="AW9:AW11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:AL6"/>
-    <mergeCell ref="AM5:AT6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="AR7:AR8"/>
-    <mergeCell ref="AQ7:AQ8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="AU7:AX7"/>
-    <mergeCell ref="AX9:AX11"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <conditionalFormatting sqref="I7:AL23">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>OR(I$7="СБ",I$7="ВС")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS9:AS23">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="6" priority="8">
+    <cfRule type="containsBlanks" dxfId="7" priority="8">
       <formula>LEN(TRIM(AS9))=0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="between">
       <formula>0</formula>
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA9:BA23">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="between">
       <formula>0</formula>
       <formula>10</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="6">
+    <cfRule type="containsBlanks" dxfId="2" priority="6">
       <formula>LEN(TRIM(BA9))=0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11831,66 +11839,66 @@
       <c r="O5" s="85"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="232" t="s">
+      <c r="A6" s="231" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="232" t="s">
+      <c r="B6" s="231" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="232" t="s">
+      <c r="C6" s="231" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="232"/>
-      <c r="E6" s="232" t="s">
+      <c r="D6" s="231"/>
+      <c r="E6" s="231" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="232" t="s">
+      <c r="F6" s="231" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="232" t="s">
+      <c r="G6" s="231" t="s">
         <v>75</v>
       </c>
-      <c r="H6" s="232" t="s">
+      <c r="H6" s="231" t="s">
         <v>798</v>
       </c>
-      <c r="I6" s="232" t="s">
+      <c r="I6" s="231" t="s">
         <v>0</v>
       </c>
-      <c r="J6" s="232" t="s">
+      <c r="J6" s="231" t="s">
         <v>76</v>
       </c>
-      <c r="K6" s="232" t="s">
+      <c r="K6" s="231" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="232" t="s">
+      <c r="L6" s="231" t="s">
         <v>77</v>
       </c>
-      <c r="M6" s="232" t="s">
+      <c r="M6" s="231" t="s">
         <v>78</v>
       </c>
-      <c r="N6" s="232" t="s">
+      <c r="N6" s="231" t="s">
         <v>799</v>
       </c>
-      <c r="O6" s="232" t="s">
+      <c r="O6" s="231" t="s">
         <v>800</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="233"/>
-      <c r="B7" s="234"/>
-      <c r="C7" s="234"/>
-      <c r="D7" s="235"/>
-      <c r="E7" s="234"/>
-      <c r="F7" s="233"/>
-      <c r="G7" s="233"/>
-      <c r="H7" s="233"/>
-      <c r="I7" s="233"/>
-      <c r="J7" s="233"/>
-      <c r="K7" s="233"/>
-      <c r="L7" s="233"/>
-      <c r="M7" s="233"/>
-      <c r="N7" s="233"/>
-      <c r="O7" s="233"/>
+      <c r="A7" s="232"/>
+      <c r="B7" s="233"/>
+      <c r="C7" s="233"/>
+      <c r="D7" s="234"/>
+      <c r="E7" s="233"/>
+      <c r="F7" s="232"/>
+      <c r="G7" s="232"/>
+      <c r="H7" s="232"/>
+      <c r="I7" s="232"/>
+      <c r="J7" s="232"/>
+      <c r="K7" s="232"/>
+      <c r="L7" s="232"/>
+      <c r="M7" s="232"/>
+      <c r="N7" s="232"/>
+      <c r="O7" s="232"/>
     </row>
     <row r="8" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="88">
@@ -11899,10 +11907,10 @@
       <c r="B8" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="236" t="s">
+      <c r="C8" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D8" s="236"/>
+      <c r="D8" s="228"/>
       <c r="E8" s="89" t="s">
         <v>107</v>
       </c>
@@ -11942,10 +11950,10 @@
       <c r="B9" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="236" t="s">
+      <c r="C9" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D9" s="236"/>
+      <c r="D9" s="228"/>
       <c r="E9" s="89" t="s">
         <v>107</v>
       </c>
@@ -11985,10 +11993,10 @@
       <c r="B10" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="236" t="s">
+      <c r="C10" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D10" s="236"/>
+      <c r="D10" s="228"/>
       <c r="E10" s="89" t="s">
         <v>107</v>
       </c>
@@ -12028,10 +12036,10 @@
       <c r="B11" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="236" t="s">
+      <c r="C11" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D11" s="236"/>
+      <c r="D11" s="228"/>
       <c r="E11" s="89" t="s">
         <v>107</v>
       </c>
@@ -12071,10 +12079,10 @@
       <c r="B12" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="236" t="s">
+      <c r="C12" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D12" s="236"/>
+      <c r="D12" s="228"/>
       <c r="E12" s="89" t="s">
         <v>107</v>
       </c>
@@ -12114,10 +12122,10 @@
       <c r="B13" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="236" t="s">
+      <c r="C13" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="236"/>
+      <c r="D13" s="228"/>
       <c r="E13" s="89" t="s">
         <v>107</v>
       </c>
@@ -12157,10 +12165,10 @@
       <c r="B14" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="236" t="s">
+      <c r="C14" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D14" s="236"/>
+      <c r="D14" s="228"/>
       <c r="E14" s="89" t="s">
         <v>107</v>
       </c>
@@ -12200,10 +12208,10 @@
       <c r="B15" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="236" t="s">
+      <c r="C15" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D15" s="236"/>
+      <c r="D15" s="228"/>
       <c r="E15" s="89" t="s">
         <v>107</v>
       </c>
@@ -12241,10 +12249,10 @@
       <c r="B16" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="236" t="s">
+      <c r="C16" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D16" s="236"/>
+      <c r="D16" s="228"/>
       <c r="E16" s="89" t="s">
         <v>107</v>
       </c>
@@ -12282,10 +12290,10 @@
       <c r="B17" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="236" t="s">
+      <c r="C17" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="236"/>
+      <c r="D17" s="228"/>
       <c r="E17" s="89" t="s">
         <v>107</v>
       </c>
@@ -12325,10 +12333,10 @@
       <c r="B18" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="236" t="s">
+      <c r="C18" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D18" s="236"/>
+      <c r="D18" s="228"/>
       <c r="E18" s="89" t="s">
         <v>107</v>
       </c>
@@ -12368,10 +12376,10 @@
       <c r="B19" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="236" t="s">
+      <c r="C19" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D19" s="236"/>
+      <c r="D19" s="228"/>
       <c r="E19" s="89" t="s">
         <v>107</v>
       </c>
@@ -12411,10 +12419,10 @@
       <c r="B20" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="236" t="s">
+      <c r="C20" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D20" s="236"/>
+      <c r="D20" s="228"/>
       <c r="E20" s="89" t="s">
         <v>107</v>
       </c>
@@ -12452,10 +12460,10 @@
       <c r="B21" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="236" t="s">
+      <c r="C21" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D21" s="236"/>
+      <c r="D21" s="228"/>
       <c r="E21" s="89" t="s">
         <v>107</v>
       </c>
@@ -12491,10 +12499,10 @@
       <c r="B22" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="236" t="s">
+      <c r="C22" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D22" s="236"/>
+      <c r="D22" s="228"/>
       <c r="E22" s="89" t="s">
         <v>107</v>
       </c>
@@ -12532,10 +12540,10 @@
       <c r="B23" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="236" t="s">
+      <c r="C23" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D23" s="236"/>
+      <c r="D23" s="228"/>
       <c r="E23" s="89" t="s">
         <v>107</v>
       </c>
@@ -12573,10 +12581,10 @@
       <c r="B24" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="236" t="s">
+      <c r="C24" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D24" s="236"/>
+      <c r="D24" s="228"/>
       <c r="E24" s="89" t="s">
         <v>107</v>
       </c>
@@ -12614,10 +12622,10 @@
       <c r="B25" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="236" t="s">
+      <c r="C25" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D25" s="236"/>
+      <c r="D25" s="228"/>
       <c r="E25" s="89" t="s">
         <v>107</v>
       </c>
@@ -12655,10 +12663,10 @@
       <c r="B26" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="236" t="s">
+      <c r="C26" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D26" s="236"/>
+      <c r="D26" s="228"/>
       <c r="E26" s="89" t="s">
         <v>107</v>
       </c>
@@ -12696,10 +12704,10 @@
       <c r="B27" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="236" t="s">
+      <c r="C27" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D27" s="236"/>
+      <c r="D27" s="228"/>
       <c r="E27" s="89" t="s">
         <v>107</v>
       </c>
@@ -12739,10 +12747,10 @@
       <c r="B28" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="236" t="s">
+      <c r="C28" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D28" s="236"/>
+      <c r="D28" s="228"/>
       <c r="E28" s="89" t="s">
         <v>107</v>
       </c>
@@ -12782,10 +12790,10 @@
       <c r="B29" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="236" t="s">
+      <c r="C29" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D29" s="236"/>
+      <c r="D29" s="228"/>
       <c r="E29" s="89" t="s">
         <v>107</v>
       </c>
@@ -12825,10 +12833,10 @@
       <c r="B30" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="236" t="s">
+      <c r="C30" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D30" s="236"/>
+      <c r="D30" s="228"/>
       <c r="E30" s="89" t="s">
         <v>107</v>
       </c>
@@ -12868,10 +12876,10 @@
       <c r="B31" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="236" t="s">
+      <c r="C31" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D31" s="236"/>
+      <c r="D31" s="228"/>
       <c r="E31" s="89" t="s">
         <v>107</v>
       </c>
@@ -12909,10 +12917,10 @@
       <c r="B32" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="236" t="s">
+      <c r="C32" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D32" s="236"/>
+      <c r="D32" s="228"/>
       <c r="E32" s="89" t="s">
         <v>107</v>
       </c>
@@ -12950,10 +12958,10 @@
       <c r="B33" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="236" t="s">
+      <c r="C33" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D33" s="236"/>
+      <c r="D33" s="228"/>
       <c r="E33" s="89" t="s">
         <v>107</v>
       </c>
@@ -12991,10 +12999,10 @@
       <c r="B34" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="236" t="s">
+      <c r="C34" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D34" s="236"/>
+      <c r="D34" s="228"/>
       <c r="E34" s="89" t="s">
         <v>107</v>
       </c>
@@ -13032,10 +13040,10 @@
       <c r="B35" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="236" t="s">
+      <c r="C35" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D35" s="236"/>
+      <c r="D35" s="228"/>
       <c r="E35" s="89" t="s">
         <v>107</v>
       </c>
@@ -13073,10 +13081,10 @@
       <c r="B36" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="236" t="s">
+      <c r="C36" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D36" s="236"/>
+      <c r="D36" s="228"/>
       <c r="E36" s="89" t="s">
         <v>107</v>
       </c>
@@ -13114,10 +13122,10 @@
       <c r="B37" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="236" t="s">
+      <c r="C37" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D37" s="236"/>
+      <c r="D37" s="228"/>
       <c r="E37" s="89" t="s">
         <v>107</v>
       </c>
@@ -13157,10 +13165,10 @@
       <c r="B38" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C38" s="236" t="s">
+      <c r="C38" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D38" s="236"/>
+      <c r="D38" s="228"/>
       <c r="E38" s="89" t="s">
         <v>107</v>
       </c>
@@ -13200,10 +13208,10 @@
       <c r="B39" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="236" t="s">
+      <c r="C39" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D39" s="236"/>
+      <c r="D39" s="228"/>
       <c r="E39" s="89" t="s">
         <v>107</v>
       </c>
@@ -13241,10 +13249,10 @@
       <c r="B40" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="236" t="s">
+      <c r="C40" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D40" s="236"/>
+      <c r="D40" s="228"/>
       <c r="E40" s="89" t="s">
         <v>107</v>
       </c>
@@ -13282,10 +13290,10 @@
       <c r="B41" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C41" s="236" t="s">
+      <c r="C41" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D41" s="236"/>
+      <c r="D41" s="228"/>
       <c r="E41" s="89" t="s">
         <v>107</v>
       </c>
@@ -13323,10 +13331,10 @@
       <c r="B42" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C42" s="236" t="s">
+      <c r="C42" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D42" s="236"/>
+      <c r="D42" s="228"/>
       <c r="E42" s="89" t="s">
         <v>107</v>
       </c>
@@ -13364,10 +13372,10 @@
       <c r="B43" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C43" s="236" t="s">
+      <c r="C43" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D43" s="236"/>
+      <c r="D43" s="228"/>
       <c r="E43" s="89" t="s">
         <v>107</v>
       </c>
@@ -13403,10 +13411,10 @@
       <c r="B44" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C44" s="236" t="s">
+      <c r="C44" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D44" s="236"/>
+      <c r="D44" s="228"/>
       <c r="E44" s="89" t="s">
         <v>107</v>
       </c>
@@ -13442,10 +13450,10 @@
       <c r="B45" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C45" s="236" t="s">
+      <c r="C45" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D45" s="236"/>
+      <c r="D45" s="228"/>
       <c r="E45" s="89" t="s">
         <v>81</v>
       </c>
@@ -13479,10 +13487,10 @@
       <c r="B46" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C46" s="236" t="s">
+      <c r="C46" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D46" s="236"/>
+      <c r="D46" s="228"/>
       <c r="E46" s="89" t="s">
         <v>307</v>
       </c>
@@ -13520,10 +13528,10 @@
       <c r="B47" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="236" t="s">
+      <c r="C47" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D47" s="236"/>
+      <c r="D47" s="228"/>
       <c r="E47" s="89" t="s">
         <v>307</v>
       </c>
@@ -13561,10 +13569,10 @@
       <c r="B48" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C48" s="236" t="s">
+      <c r="C48" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D48" s="236"/>
+      <c r="D48" s="228"/>
       <c r="E48" s="89" t="s">
         <v>307</v>
       </c>
@@ -13602,10 +13610,10 @@
       <c r="B49" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C49" s="236" t="s">
+      <c r="C49" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D49" s="236"/>
+      <c r="D49" s="228"/>
       <c r="E49" s="89" t="s">
         <v>307</v>
       </c>
@@ -13643,10 +13651,10 @@
       <c r="B50" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C50" s="236" t="s">
+      <c r="C50" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D50" s="236"/>
+      <c r="D50" s="228"/>
       <c r="E50" s="89" t="s">
         <v>307</v>
       </c>
@@ -13684,10 +13692,10 @@
       <c r="B51" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C51" s="236" t="s">
+      <c r="C51" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D51" s="236"/>
+      <c r="D51" s="228"/>
       <c r="E51" s="89" t="s">
         <v>307</v>
       </c>
@@ -13725,10 +13733,10 @@
       <c r="B52" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C52" s="236" t="s">
+      <c r="C52" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D52" s="236"/>
+      <c r="D52" s="228"/>
       <c r="E52" s="89" t="s">
         <v>307</v>
       </c>
@@ -13766,10 +13774,10 @@
       <c r="B53" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C53" s="236" t="s">
+      <c r="C53" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D53" s="236"/>
+      <c r="D53" s="228"/>
       <c r="E53" s="89" t="s">
         <v>307</v>
       </c>
@@ -13807,10 +13815,10 @@
       <c r="B54" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C54" s="236" t="s">
+      <c r="C54" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D54" s="236"/>
+      <c r="D54" s="228"/>
       <c r="E54" s="89" t="s">
         <v>307</v>
       </c>
@@ -13848,10 +13856,10 @@
       <c r="B55" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C55" s="236" t="s">
+      <c r="C55" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D55" s="236"/>
+      <c r="D55" s="228"/>
       <c r="E55" s="89" t="s">
         <v>307</v>
       </c>
@@ -13889,10 +13897,10 @@
       <c r="B56" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C56" s="236" t="s">
+      <c r="C56" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D56" s="236"/>
+      <c r="D56" s="228"/>
       <c r="E56" s="89" t="s">
         <v>307</v>
       </c>
@@ -13930,10 +13938,10 @@
       <c r="B57" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C57" s="236" t="s">
+      <c r="C57" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D57" s="236"/>
+      <c r="D57" s="228"/>
       <c r="E57" s="89" t="s">
         <v>307</v>
       </c>
@@ -13971,10 +13979,10 @@
       <c r="B58" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C58" s="236" t="s">
+      <c r="C58" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D58" s="236"/>
+      <c r="D58" s="228"/>
       <c r="E58" s="89" t="s">
         <v>307</v>
       </c>
@@ -14012,10 +14020,10 @@
       <c r="B59" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C59" s="236" t="s">
+      <c r="C59" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D59" s="236"/>
+      <c r="D59" s="228"/>
       <c r="E59" s="89" t="s">
         <v>307</v>
       </c>
@@ -14053,10 +14061,10 @@
       <c r="B60" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C60" s="236" t="s">
+      <c r="C60" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D60" s="236"/>
+      <c r="D60" s="228"/>
       <c r="E60" s="89" t="s">
         <v>307</v>
       </c>
@@ -14094,10 +14102,10 @@
       <c r="B61" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C61" s="236" t="s">
+      <c r="C61" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D61" s="236"/>
+      <c r="D61" s="228"/>
       <c r="E61" s="89" t="s">
         <v>307</v>
       </c>
@@ -14133,10 +14141,10 @@
       <c r="B62" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C62" s="236" t="s">
+      <c r="C62" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D62" s="236"/>
+      <c r="D62" s="228"/>
       <c r="E62" s="89" t="s">
         <v>307</v>
       </c>
@@ -14172,10 +14180,10 @@
       <c r="B63" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C63" s="236" t="s">
+      <c r="C63" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D63" s="236"/>
+      <c r="D63" s="228"/>
       <c r="E63" s="89" t="s">
         <v>307</v>
       </c>
@@ -14213,10 +14221,10 @@
       <c r="B64" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C64" s="236" t="s">
+      <c r="C64" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D64" s="236"/>
+      <c r="D64" s="228"/>
       <c r="E64" s="89" t="s">
         <v>307</v>
       </c>
@@ -14254,10 +14262,10 @@
       <c r="B65" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="236" t="s">
+      <c r="C65" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D65" s="236"/>
+      <c r="D65" s="228"/>
       <c r="E65" s="89" t="s">
         <v>307</v>
       </c>
@@ -14293,10 +14301,10 @@
       <c r="B66" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C66" s="236" t="s">
+      <c r="C66" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D66" s="236"/>
+      <c r="D66" s="228"/>
       <c r="E66" s="89" t="s">
         <v>307</v>
       </c>
@@ -14334,10 +14342,10 @@
       <c r="B67" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C67" s="236" t="s">
+      <c r="C67" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D67" s="236"/>
+      <c r="D67" s="228"/>
       <c r="E67" s="89" t="s">
         <v>307</v>
       </c>
@@ -14375,10 +14383,10 @@
       <c r="B68" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C68" s="236" t="s">
+      <c r="C68" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D68" s="236"/>
+      <c r="D68" s="228"/>
       <c r="E68" s="89" t="s">
         <v>307</v>
       </c>
@@ -14414,10 +14422,10 @@
       <c r="B69" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C69" s="236" t="s">
+      <c r="C69" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D69" s="236"/>
+      <c r="D69" s="228"/>
       <c r="E69" s="89" t="s">
         <v>103</v>
       </c>
@@ -14451,10 +14459,10 @@
       <c r="B70" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C70" s="236" t="s">
+      <c r="C70" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D70" s="236"/>
+      <c r="D70" s="228"/>
       <c r="E70" s="89" t="s">
         <v>103</v>
       </c>
@@ -14488,10 +14496,10 @@
       <c r="B71" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C71" s="236" t="s">
+      <c r="C71" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D71" s="236"/>
+      <c r="D71" s="228"/>
       <c r="E71" s="89" t="s">
         <v>103</v>
       </c>
@@ -14525,10 +14533,10 @@
       <c r="B72" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C72" s="236" t="s">
+      <c r="C72" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D72" s="236"/>
+      <c r="D72" s="228"/>
       <c r="E72" s="89" t="s">
         <v>103</v>
       </c>
@@ -14562,10 +14570,10 @@
       <c r="B73" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C73" s="236" t="s">
+      <c r="C73" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D73" s="236"/>
+      <c r="D73" s="228"/>
       <c r="E73" s="89" t="s">
         <v>103</v>
       </c>
@@ -14599,10 +14607,10 @@
       <c r="B74" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C74" s="236" t="s">
+      <c r="C74" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D74" s="236"/>
+      <c r="D74" s="228"/>
       <c r="E74" s="89" t="s">
         <v>122</v>
       </c>
@@ -14636,10 +14644,10 @@
       <c r="B75" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C75" s="236" t="s">
+      <c r="C75" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D75" s="236"/>
+      <c r="D75" s="228"/>
       <c r="E75" s="89" t="s">
         <v>122</v>
       </c>
@@ -14675,10 +14683,10 @@
       <c r="B76" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C76" s="236" t="s">
+      <c r="C76" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D76" s="236"/>
+      <c r="D76" s="228"/>
       <c r="E76" s="89" t="s">
         <v>122</v>
       </c>
@@ -14714,10 +14722,10 @@
       <c r="B77" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C77" s="236" t="s">
+      <c r="C77" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D77" s="236"/>
+      <c r="D77" s="228"/>
       <c r="E77" s="89" t="s">
         <v>122</v>
       </c>
@@ -14753,10 +14761,10 @@
       <c r="B78" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C78" s="236" t="s">
+      <c r="C78" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D78" s="236"/>
+      <c r="D78" s="228"/>
       <c r="E78" s="89" t="s">
         <v>122</v>
       </c>
@@ -14792,10 +14800,10 @@
       <c r="B79" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C79" s="236" t="s">
+      <c r="C79" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D79" s="236"/>
+      <c r="D79" s="228"/>
       <c r="E79" s="89" t="s">
         <v>122</v>
       </c>
@@ -14831,10 +14839,10 @@
       <c r="B80" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="236" t="s">
+      <c r="C80" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D80" s="236"/>
+      <c r="D80" s="228"/>
       <c r="E80" s="89" t="s">
         <v>122</v>
       </c>
@@ -14870,10 +14878,10 @@
       <c r="B81" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C81" s="236" t="s">
+      <c r="C81" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D81" s="236"/>
+      <c r="D81" s="228"/>
       <c r="E81" s="89" t="s">
         <v>122</v>
       </c>
@@ -14909,10 +14917,10 @@
       <c r="B82" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C82" s="236" t="s">
+      <c r="C82" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D82" s="236"/>
+      <c r="D82" s="228"/>
       <c r="E82" s="89" t="s">
         <v>122</v>
       </c>
@@ -14948,10 +14956,10 @@
       <c r="B83" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C83" s="236" t="s">
+      <c r="C83" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D83" s="236"/>
+      <c r="D83" s="228"/>
       <c r="E83" s="89" t="s">
         <v>122</v>
       </c>
@@ -14987,10 +14995,10 @@
       <c r="B84" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C84" s="236" t="s">
+      <c r="C84" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D84" s="236"/>
+      <c r="D84" s="228"/>
       <c r="E84" s="89" t="s">
         <v>122</v>
       </c>
@@ -15024,10 +15032,10 @@
       <c r="B85" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C85" s="236" t="s">
+      <c r="C85" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D85" s="236"/>
+      <c r="D85" s="228"/>
       <c r="E85" s="89" t="s">
         <v>122</v>
       </c>
@@ -15063,10 +15071,10 @@
       <c r="B86" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C86" s="236" t="s">
+      <c r="C86" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D86" s="236"/>
+      <c r="D86" s="228"/>
       <c r="E86" s="89" t="s">
         <v>122</v>
       </c>
@@ -15102,10 +15110,10 @@
       <c r="B87" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C87" s="236" t="s">
+      <c r="C87" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D87" s="236"/>
+      <c r="D87" s="228"/>
       <c r="E87" s="89" t="s">
         <v>122</v>
       </c>
@@ -15141,10 +15149,10 @@
       <c r="B88" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C88" s="236" t="s">
+      <c r="C88" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D88" s="236"/>
+      <c r="D88" s="228"/>
       <c r="E88" s="89" t="s">
         <v>122</v>
       </c>
@@ -15180,10 +15188,10 @@
       <c r="B89" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C89" s="236" t="s">
+      <c r="C89" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D89" s="236"/>
+      <c r="D89" s="228"/>
       <c r="E89" s="89" t="s">
         <v>122</v>
       </c>
@@ -15219,10 +15227,10 @@
       <c r="B90" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C90" s="236" t="s">
+      <c r="C90" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D90" s="236"/>
+      <c r="D90" s="228"/>
       <c r="E90" s="89" t="s">
         <v>122</v>
       </c>
@@ -15258,10 +15266,10 @@
       <c r="B91" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C91" s="236" t="s">
+      <c r="C91" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D91" s="236"/>
+      <c r="D91" s="228"/>
       <c r="E91" s="89" t="s">
         <v>122</v>
       </c>
@@ -15297,10 +15305,10 @@
       <c r="B92" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C92" s="236" t="s">
+      <c r="C92" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D92" s="236"/>
+      <c r="D92" s="228"/>
       <c r="E92" s="89" t="s">
         <v>122</v>
       </c>
@@ -15336,10 +15344,10 @@
       <c r="B93" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C93" s="236" t="s">
+      <c r="C93" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D93" s="236"/>
+      <c r="D93" s="228"/>
       <c r="E93" s="89" t="s">
         <v>122</v>
       </c>
@@ -15375,10 +15383,10 @@
       <c r="B94" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C94" s="236" t="s">
+      <c r="C94" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D94" s="236"/>
+      <c r="D94" s="228"/>
       <c r="E94" s="89" t="s">
         <v>122</v>
       </c>
@@ -15414,10 +15422,10 @@
       <c r="B95" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C95" s="236" t="s">
+      <c r="C95" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D95" s="236"/>
+      <c r="D95" s="228"/>
       <c r="E95" s="89" t="s">
         <v>122</v>
       </c>
@@ -15453,10 +15461,10 @@
       <c r="B96" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C96" s="236" t="s">
+      <c r="C96" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D96" s="236"/>
+      <c r="D96" s="228"/>
       <c r="E96" s="89" t="s">
         <v>122</v>
       </c>
@@ -15492,10 +15500,10 @@
       <c r="B97" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C97" s="236" t="s">
+      <c r="C97" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D97" s="236"/>
+      <c r="D97" s="228"/>
       <c r="E97" s="89" t="s">
         <v>122</v>
       </c>
@@ -15529,10 +15537,10 @@
       <c r="B98" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C98" s="236" t="s">
+      <c r="C98" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D98" s="236"/>
+      <c r="D98" s="228"/>
       <c r="E98" s="89" t="s">
         <v>122</v>
       </c>
@@ -15570,10 +15578,10 @@
       <c r="B99" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C99" s="236" t="s">
+      <c r="C99" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D99" s="236"/>
+      <c r="D99" s="228"/>
       <c r="E99" s="89" t="s">
         <v>122</v>
       </c>
@@ -15611,10 +15619,10 @@
       <c r="B100" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C100" s="236" t="s">
+      <c r="C100" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D100" s="236"/>
+      <c r="D100" s="228"/>
       <c r="E100" s="89" t="s">
         <v>122</v>
       </c>
@@ -15650,10 +15658,10 @@
       <c r="B101" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C101" s="236" t="s">
+      <c r="C101" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D101" s="236"/>
+      <c r="D101" s="228"/>
       <c r="E101" s="89" t="s">
         <v>122</v>
       </c>
@@ -15691,10 +15699,10 @@
       <c r="B102" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C102" s="236" t="s">
+      <c r="C102" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D102" s="236"/>
+      <c r="D102" s="228"/>
       <c r="E102" s="89" t="s">
         <v>122</v>
       </c>
@@ -15732,10 +15740,10 @@
       <c r="B103" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C103" s="236" t="s">
+      <c r="C103" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D103" s="236"/>
+      <c r="D103" s="228"/>
       <c r="E103" s="89" t="s">
         <v>122</v>
       </c>
@@ -15773,10 +15781,10 @@
       <c r="B104" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C104" s="236" t="s">
+      <c r="C104" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D104" s="236"/>
+      <c r="D104" s="228"/>
       <c r="E104" s="89" t="s">
         <v>122</v>
       </c>
@@ -15814,10 +15822,10 @@
       <c r="B105" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C105" s="236" t="s">
+      <c r="C105" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D105" s="236"/>
+      <c r="D105" s="228"/>
       <c r="E105" s="89" t="s">
         <v>122</v>
       </c>
@@ -15855,10 +15863,10 @@
       <c r="B106" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C106" s="236" t="s">
+      <c r="C106" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D106" s="236"/>
+      <c r="D106" s="228"/>
       <c r="E106" s="89" t="s">
         <v>122</v>
       </c>
@@ -15896,10 +15904,10 @@
       <c r="B107" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C107" s="236" t="s">
+      <c r="C107" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D107" s="236"/>
+      <c r="D107" s="228"/>
       <c r="E107" s="89" t="s">
         <v>122</v>
       </c>
@@ -15937,10 +15945,10 @@
       <c r="B108" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C108" s="236" t="s">
+      <c r="C108" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D108" s="236"/>
+      <c r="D108" s="228"/>
       <c r="E108" s="89" t="s">
         <v>122</v>
       </c>
@@ -15978,10 +15986,10 @@
       <c r="B109" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C109" s="236" t="s">
+      <c r="C109" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D109" s="236"/>
+      <c r="D109" s="228"/>
       <c r="E109" s="89" t="s">
         <v>122</v>
       </c>
@@ -16019,10 +16027,10 @@
       <c r="B110" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C110" s="236" t="s">
+      <c r="C110" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D110" s="236"/>
+      <c r="D110" s="228"/>
       <c r="E110" s="89" t="s">
         <v>122</v>
       </c>
@@ -16060,10 +16068,10 @@
       <c r="B111" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C111" s="236" t="s">
+      <c r="C111" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D111" s="236"/>
+      <c r="D111" s="228"/>
       <c r="E111" s="89" t="s">
         <v>122</v>
       </c>
@@ -16101,10 +16109,10 @@
       <c r="B112" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C112" s="236" t="s">
+      <c r="C112" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D112" s="236"/>
+      <c r="D112" s="228"/>
       <c r="E112" s="89" t="s">
         <v>122</v>
       </c>
@@ -16142,10 +16150,10 @@
       <c r="B113" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C113" s="236" t="s">
+      <c r="C113" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D113" s="236"/>
+      <c r="D113" s="228"/>
       <c r="E113" s="89" t="s">
         <v>122</v>
       </c>
@@ -16183,10 +16191,10 @@
       <c r="B114" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C114" s="236" t="s">
+      <c r="C114" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D114" s="236"/>
+      <c r="D114" s="228"/>
       <c r="E114" s="89" t="s">
         <v>122</v>
       </c>
@@ -16224,10 +16232,10 @@
       <c r="B115" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C115" s="236" t="s">
+      <c r="C115" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D115" s="236"/>
+      <c r="D115" s="228"/>
       <c r="E115" s="89" t="s">
         <v>122</v>
       </c>
@@ -16265,10 +16273,10 @@
       <c r="B116" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C116" s="236" t="s">
+      <c r="C116" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D116" s="236"/>
+      <c r="D116" s="228"/>
       <c r="E116" s="89" t="s">
         <v>122</v>
       </c>
@@ -16306,10 +16314,10 @@
       <c r="B117" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C117" s="236" t="s">
+      <c r="C117" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D117" s="236"/>
+      <c r="D117" s="228"/>
       <c r="E117" s="89" t="s">
         <v>122</v>
       </c>
@@ -16347,10 +16355,10 @@
       <c r="B118" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C118" s="236" t="s">
+      <c r="C118" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D118" s="236"/>
+      <c r="D118" s="228"/>
       <c r="E118" s="89" t="s">
         <v>122</v>
       </c>
@@ -16388,10 +16396,10 @@
       <c r="B119" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C119" s="236" t="s">
+      <c r="C119" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D119" s="236"/>
+      <c r="D119" s="228"/>
       <c r="E119" s="89" t="s">
         <v>122</v>
       </c>
@@ -16429,10 +16437,10 @@
       <c r="B120" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C120" s="236" t="s">
+      <c r="C120" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D120" s="236"/>
+      <c r="D120" s="228"/>
       <c r="E120" s="89" t="s">
         <v>100</v>
       </c>
@@ -16466,10 +16474,10 @@
       <c r="B121" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C121" s="236" t="s">
+      <c r="C121" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D121" s="236"/>
+      <c r="D121" s="228"/>
       <c r="E121" s="89" t="s">
         <v>100</v>
       </c>
@@ -16505,10 +16513,10 @@
       <c r="B122" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C122" s="236" t="s">
+      <c r="C122" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D122" s="236"/>
+      <c r="D122" s="228"/>
       <c r="E122" s="89" t="s">
         <v>100</v>
       </c>
@@ -16544,10 +16552,10 @@
       <c r="B123" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C123" s="236" t="s">
+      <c r="C123" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D123" s="236"/>
+      <c r="D123" s="228"/>
       <c r="E123" s="89" t="s">
         <v>100</v>
       </c>
@@ -16583,10 +16591,10 @@
       <c r="B124" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C124" s="236" t="s">
+      <c r="C124" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D124" s="236"/>
+      <c r="D124" s="228"/>
       <c r="E124" s="89" t="s">
         <v>100</v>
       </c>
@@ -16624,10 +16632,10 @@
       <c r="B125" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C125" s="236" t="s">
+      <c r="C125" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D125" s="236"/>
+      <c r="D125" s="228"/>
       <c r="E125" s="89" t="s">
         <v>100</v>
       </c>
@@ -16665,10 +16673,10 @@
       <c r="B126" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C126" s="236" t="s">
+      <c r="C126" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D126" s="236"/>
+      <c r="D126" s="228"/>
       <c r="E126" s="89" t="s">
         <v>100</v>
       </c>
@@ -16706,10 +16714,10 @@
       <c r="B127" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C127" s="236" t="s">
+      <c r="C127" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D127" s="236"/>
+      <c r="D127" s="228"/>
       <c r="E127" s="89" t="s">
         <v>100</v>
       </c>
@@ -16747,10 +16755,10 @@
       <c r="B128" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C128" s="236" t="s">
+      <c r="C128" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D128" s="236"/>
+      <c r="D128" s="228"/>
       <c r="E128" s="89" t="s">
         <v>100</v>
       </c>
@@ -16788,10 +16796,10 @@
       <c r="B129" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C129" s="236" t="s">
+      <c r="C129" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D129" s="236"/>
+      <c r="D129" s="228"/>
       <c r="E129" s="89" t="s">
         <v>100</v>
       </c>
@@ -16829,10 +16837,10 @@
       <c r="B130" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C130" s="236" t="s">
+      <c r="C130" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D130" s="236"/>
+      <c r="D130" s="228"/>
       <c r="E130" s="89" t="s">
         <v>100</v>
       </c>
@@ -16870,10 +16878,10 @@
       <c r="B131" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C131" s="236" t="s">
+      <c r="C131" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D131" s="236"/>
+      <c r="D131" s="228"/>
       <c r="E131" s="89" t="s">
         <v>100</v>
       </c>
@@ -16911,10 +16919,10 @@
       <c r="B132" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C132" s="236" t="s">
+      <c r="C132" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D132" s="236"/>
+      <c r="D132" s="228"/>
       <c r="E132" s="89" t="s">
         <v>100</v>
       </c>
@@ -16952,10 +16960,10 @@
       <c r="B133" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C133" s="236" t="s">
+      <c r="C133" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D133" s="236"/>
+      <c r="D133" s="228"/>
       <c r="E133" s="89" t="s">
         <v>100</v>
       </c>
@@ -16993,10 +17001,10 @@
       <c r="B134" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C134" s="236" t="s">
+      <c r="C134" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D134" s="236"/>
+      <c r="D134" s="228"/>
       <c r="E134" s="89" t="s">
         <v>100</v>
       </c>
@@ -17034,10 +17042,10 @@
       <c r="B135" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C135" s="236" t="s">
+      <c r="C135" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D135" s="236"/>
+      <c r="D135" s="228"/>
       <c r="E135" s="89" t="s">
         <v>100</v>
       </c>
@@ -17075,10 +17083,10 @@
       <c r="B136" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C136" s="236" t="s">
+      <c r="C136" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D136" s="236"/>
+      <c r="D136" s="228"/>
       <c r="E136" s="89" t="s">
         <v>100</v>
       </c>
@@ -17116,10 +17124,10 @@
       <c r="B137" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C137" s="236" t="s">
+      <c r="C137" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D137" s="236"/>
+      <c r="D137" s="228"/>
       <c r="E137" s="89" t="s">
         <v>100</v>
       </c>
@@ -17157,10 +17165,10 @@
       <c r="B138" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C138" s="236" t="s">
+      <c r="C138" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D138" s="236"/>
+      <c r="D138" s="228"/>
       <c r="E138" s="89" t="s">
         <v>100</v>
       </c>
@@ -17198,10 +17206,10 @@
       <c r="B139" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C139" s="236" t="s">
+      <c r="C139" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D139" s="236"/>
+      <c r="D139" s="228"/>
       <c r="E139" s="89" t="s">
         <v>100</v>
       </c>
@@ -17239,10 +17247,10 @@
       <c r="B140" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C140" s="236" t="s">
+      <c r="C140" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D140" s="236"/>
+      <c r="D140" s="228"/>
       <c r="E140" s="89" t="s">
         <v>100</v>
       </c>
@@ -17280,10 +17288,10 @@
       <c r="B141" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C141" s="236" t="s">
+      <c r="C141" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D141" s="236"/>
+      <c r="D141" s="228"/>
       <c r="E141" s="89" t="s">
         <v>100</v>
       </c>
@@ -17321,10 +17329,10 @@
       <c r="B142" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C142" s="236" t="s">
+      <c r="C142" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D142" s="236"/>
+      <c r="D142" s="228"/>
       <c r="E142" s="89" t="s">
         <v>100</v>
       </c>
@@ -17362,10 +17370,10 @@
       <c r="B143" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C143" s="236" t="s">
+      <c r="C143" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D143" s="236"/>
+      <c r="D143" s="228"/>
       <c r="E143" s="89" t="s">
         <v>100</v>
       </c>
@@ -17403,10 +17411,10 @@
       <c r="B144" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C144" s="236" t="s">
+      <c r="C144" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D144" s="236"/>
+      <c r="D144" s="228"/>
       <c r="E144" s="89" t="s">
         <v>100</v>
       </c>
@@ -17444,10 +17452,10 @@
       <c r="B145" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C145" s="236" t="s">
+      <c r="C145" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D145" s="236"/>
+      <c r="D145" s="228"/>
       <c r="E145" s="89" t="s">
         <v>100</v>
       </c>
@@ -17485,10 +17493,10 @@
       <c r="B146" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C146" s="236" t="s">
+      <c r="C146" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D146" s="236"/>
+      <c r="D146" s="228"/>
       <c r="E146" s="89" t="s">
         <v>100</v>
       </c>
@@ -17526,10 +17534,10 @@
       <c r="B147" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C147" s="236" t="s">
+      <c r="C147" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D147" s="236"/>
+      <c r="D147" s="228"/>
       <c r="E147" s="89" t="s">
         <v>100</v>
       </c>
@@ -17567,10 +17575,10 @@
       <c r="B148" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C148" s="236" t="s">
+      <c r="C148" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D148" s="236"/>
+      <c r="D148" s="228"/>
       <c r="E148" s="89" t="s">
         <v>100</v>
       </c>
@@ -17608,10 +17616,10 @@
       <c r="B149" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C149" s="236" t="s">
+      <c r="C149" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D149" s="236"/>
+      <c r="D149" s="228"/>
       <c r="E149" s="89" t="s">
         <v>100</v>
       </c>
@@ -17649,10 +17657,10 @@
       <c r="B150" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C150" s="236" t="s">
+      <c r="C150" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D150" s="236"/>
+      <c r="D150" s="228"/>
       <c r="E150" s="89" t="s">
         <v>100</v>
       </c>
@@ -17690,10 +17698,10 @@
       <c r="B151" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C151" s="236" t="s">
+      <c r="C151" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D151" s="236"/>
+      <c r="D151" s="228"/>
       <c r="E151" s="89" t="s">
         <v>100</v>
       </c>
@@ -17731,10 +17739,10 @@
       <c r="B152" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C152" s="236" t="s">
+      <c r="C152" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D152" s="236"/>
+      <c r="D152" s="228"/>
       <c r="E152" s="89" t="s">
         <v>100</v>
       </c>
@@ -17772,10 +17780,10 @@
       <c r="B153" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C153" s="236" t="s">
+      <c r="C153" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D153" s="236"/>
+      <c r="D153" s="228"/>
       <c r="E153" s="89" t="s">
         <v>100</v>
       </c>
@@ -17813,10 +17821,10 @@
       <c r="B154" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C154" s="236" t="s">
+      <c r="C154" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D154" s="236"/>
+      <c r="D154" s="228"/>
       <c r="E154" s="89" t="s">
         <v>100</v>
       </c>
@@ -17854,10 +17862,10 @@
       <c r="B155" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C155" s="236" t="s">
+      <c r="C155" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D155" s="236"/>
+      <c r="D155" s="228"/>
       <c r="E155" s="89" t="s">
         <v>100</v>
       </c>
@@ -17895,10 +17903,10 @@
       <c r="B156" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C156" s="236" t="s">
+      <c r="C156" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D156" s="236"/>
+      <c r="D156" s="228"/>
       <c r="E156" s="89" t="s">
         <v>100</v>
       </c>
@@ -17936,10 +17944,10 @@
       <c r="B157" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C157" s="236" t="s">
+      <c r="C157" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D157" s="236"/>
+      <c r="D157" s="228"/>
       <c r="E157" s="89" t="s">
         <v>100</v>
       </c>
@@ -17977,10 +17985,10 @@
       <c r="B158" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C158" s="236" t="s">
+      <c r="C158" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D158" s="236"/>
+      <c r="D158" s="228"/>
       <c r="E158" s="89" t="s">
         <v>100</v>
       </c>
@@ -18016,10 +18024,10 @@
       <c r="B159" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C159" s="236" t="s">
+      <c r="C159" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D159" s="236"/>
+      <c r="D159" s="228"/>
       <c r="E159" s="89" t="s">
         <v>100</v>
       </c>
@@ -18055,10 +18063,10 @@
       <c r="B160" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C160" s="236" t="s">
+      <c r="C160" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D160" s="236"/>
+      <c r="D160" s="228"/>
       <c r="E160" s="89" t="s">
         <v>100</v>
       </c>
@@ -18094,10 +18102,10 @@
       <c r="B161" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C161" s="236" t="s">
+      <c r="C161" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D161" s="236"/>
+      <c r="D161" s="228"/>
       <c r="E161" s="89" t="s">
         <v>100</v>
       </c>
@@ -18133,10 +18141,10 @@
       <c r="B162" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C162" s="236" t="s">
+      <c r="C162" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D162" s="236"/>
+      <c r="D162" s="228"/>
       <c r="E162" s="89" t="s">
         <v>100</v>
       </c>
@@ -18172,10 +18180,10 @@
       <c r="B163" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C163" s="236" t="s">
+      <c r="C163" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D163" s="236"/>
+      <c r="D163" s="228"/>
       <c r="E163" s="89" t="s">
         <v>100</v>
       </c>
@@ -18213,10 +18221,10 @@
       <c r="B164" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C164" s="236" t="s">
+      <c r="C164" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D164" s="236"/>
+      <c r="D164" s="228"/>
       <c r="E164" s="89" t="s">
         <v>100</v>
       </c>
@@ -18256,10 +18264,10 @@
       <c r="B165" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C165" s="236" t="s">
+      <c r="C165" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D165" s="236"/>
+      <c r="D165" s="228"/>
       <c r="E165" s="89" t="s">
         <v>100</v>
       </c>
@@ -18299,10 +18307,10 @@
       <c r="B166" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C166" s="236" t="s">
+      <c r="C166" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D166" s="236"/>
+      <c r="D166" s="228"/>
       <c r="E166" s="89" t="s">
         <v>100</v>
       </c>
@@ -18340,10 +18348,10 @@
       <c r="B167" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C167" s="236" t="s">
+      <c r="C167" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D167" s="236"/>
+      <c r="D167" s="228"/>
       <c r="E167" s="89" t="s">
         <v>100</v>
       </c>
@@ -18381,10 +18389,10 @@
       <c r="B168" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C168" s="236" t="s">
+      <c r="C168" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D168" s="236"/>
+      <c r="D168" s="228"/>
       <c r="E168" s="89" t="s">
         <v>100</v>
       </c>
@@ -18422,10 +18430,10 @@
       <c r="B169" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C169" s="236" t="s">
+      <c r="C169" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D169" s="236"/>
+      <c r="D169" s="228"/>
       <c r="E169" s="89" t="s">
         <v>100</v>
       </c>
@@ -18463,10 +18471,10 @@
       <c r="B170" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C170" s="236" t="s">
+      <c r="C170" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D170" s="236"/>
+      <c r="D170" s="228"/>
       <c r="E170" s="89" t="s">
         <v>100</v>
       </c>
@@ -18504,10 +18512,10 @@
       <c r="B171" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C171" s="236" t="s">
+      <c r="C171" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D171" s="236"/>
+      <c r="D171" s="228"/>
       <c r="E171" s="89" t="s">
         <v>100</v>
       </c>
@@ -18545,10 +18553,10 @@
       <c r="B172" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C172" s="236" t="s">
+      <c r="C172" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D172" s="236"/>
+      <c r="D172" s="228"/>
       <c r="E172" s="89" t="s">
         <v>100</v>
       </c>
@@ -18584,10 +18592,10 @@
       <c r="B173" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C173" s="236" t="s">
+      <c r="C173" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D173" s="236"/>
+      <c r="D173" s="228"/>
       <c r="E173" s="89" t="s">
         <v>100</v>
       </c>
@@ -18623,10 +18631,10 @@
       <c r="B174" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C174" s="236" t="s">
+      <c r="C174" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D174" s="236"/>
+      <c r="D174" s="228"/>
       <c r="E174" s="89" t="s">
         <v>100</v>
       </c>
@@ -18662,10 +18670,10 @@
       <c r="B175" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C175" s="236" t="s">
+      <c r="C175" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D175" s="236"/>
+      <c r="D175" s="228"/>
       <c r="E175" s="89" t="s">
         <v>100</v>
       </c>
@@ -18701,10 +18709,10 @@
       <c r="B176" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C176" s="236" t="s">
+      <c r="C176" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D176" s="236"/>
+      <c r="D176" s="228"/>
       <c r="E176" s="89" t="s">
         <v>100</v>
       </c>
@@ -18744,10 +18752,10 @@
       <c r="B177" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C177" s="236" t="s">
+      <c r="C177" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D177" s="236"/>
+      <c r="D177" s="228"/>
       <c r="E177" s="89" t="s">
         <v>100</v>
       </c>
@@ -18787,10 +18795,10 @@
       <c r="B178" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C178" s="236" t="s">
+      <c r="C178" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D178" s="236"/>
+      <c r="D178" s="228"/>
       <c r="E178" s="89" t="s">
         <v>100</v>
       </c>
@@ -18830,10 +18838,10 @@
       <c r="B179" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C179" s="236" t="s">
+      <c r="C179" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D179" s="236"/>
+      <c r="D179" s="228"/>
       <c r="E179" s="89" t="s">
         <v>100</v>
       </c>
@@ -18871,10 +18879,10 @@
       <c r="B180" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C180" s="236" t="s">
+      <c r="C180" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D180" s="236"/>
+      <c r="D180" s="228"/>
       <c r="E180" s="89" t="s">
         <v>100</v>
       </c>
@@ -18912,10 +18920,10 @@
       <c r="B181" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C181" s="236" t="s">
+      <c r="C181" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D181" s="236"/>
+      <c r="D181" s="228"/>
       <c r="E181" s="89" t="s">
         <v>100</v>
       </c>
@@ -18953,10 +18961,10 @@
       <c r="B182" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C182" s="236" t="s">
+      <c r="C182" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D182" s="236"/>
+      <c r="D182" s="228"/>
       <c r="E182" s="89" t="s">
         <v>100</v>
       </c>
@@ -18994,10 +19002,10 @@
       <c r="B183" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C183" s="236" t="s">
+      <c r="C183" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D183" s="236"/>
+      <c r="D183" s="228"/>
       <c r="E183" s="89" t="s">
         <v>100</v>
       </c>
@@ -19035,10 +19043,10 @@
       <c r="B184" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C184" s="236" t="s">
+      <c r="C184" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D184" s="236"/>
+      <c r="D184" s="228"/>
       <c r="E184" s="89" t="s">
         <v>100</v>
       </c>
@@ -19076,10 +19084,10 @@
       <c r="B185" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C185" s="236" t="s">
+      <c r="C185" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D185" s="236"/>
+      <c r="D185" s="228"/>
       <c r="E185" s="89" t="s">
         <v>100</v>
       </c>
@@ -19117,10 +19125,10 @@
       <c r="B186" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C186" s="236" t="s">
+      <c r="C186" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D186" s="236"/>
+      <c r="D186" s="228"/>
       <c r="E186" s="89" t="s">
         <v>100</v>
       </c>
@@ -19156,10 +19164,10 @@
       <c r="B187" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C187" s="236" t="s">
+      <c r="C187" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D187" s="236"/>
+      <c r="D187" s="228"/>
       <c r="E187" s="89" t="s">
         <v>130</v>
       </c>
@@ -19193,10 +19201,10 @@
       <c r="B188" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C188" s="236" t="s">
+      <c r="C188" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D188" s="236"/>
+      <c r="D188" s="228"/>
       <c r="E188" s="89" t="s">
         <v>130</v>
       </c>
@@ -19232,10 +19240,10 @@
       <c r="B189" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C189" s="236" t="s">
+      <c r="C189" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D189" s="236"/>
+      <c r="D189" s="228"/>
       <c r="E189" s="89" t="s">
         <v>130</v>
       </c>
@@ -19271,10 +19279,10 @@
       <c r="B190" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C190" s="236" t="s">
+      <c r="C190" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D190" s="236"/>
+      <c r="D190" s="228"/>
       <c r="E190" s="89" t="s">
         <v>130</v>
       </c>
@@ -19310,10 +19318,10 @@
       <c r="B191" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C191" s="236" t="s">
+      <c r="C191" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D191" s="236"/>
+      <c r="D191" s="228"/>
       <c r="E191" s="89" t="s">
         <v>130</v>
       </c>
@@ -19349,10 +19357,10 @@
       <c r="B192" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C192" s="236" t="s">
+      <c r="C192" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D192" s="236"/>
+      <c r="D192" s="228"/>
       <c r="E192" s="89" t="s">
         <v>130</v>
       </c>
@@ -19388,10 +19396,10 @@
       <c r="B193" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C193" s="236" t="s">
+      <c r="C193" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D193" s="236"/>
+      <c r="D193" s="228"/>
       <c r="E193" s="89" t="s">
         <v>130</v>
       </c>
@@ -19427,10 +19435,10 @@
       <c r="B194" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C194" s="236" t="s">
+      <c r="C194" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D194" s="236"/>
+      <c r="D194" s="228"/>
       <c r="E194" s="89" t="s">
         <v>130</v>
       </c>
@@ -19466,10 +19474,10 @@
       <c r="B195" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C195" s="236" t="s">
+      <c r="C195" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D195" s="236"/>
+      <c r="D195" s="228"/>
       <c r="E195" s="89" t="s">
         <v>130</v>
       </c>
@@ -19505,10 +19513,10 @@
       <c r="B196" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C196" s="236" t="s">
+      <c r="C196" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D196" s="236"/>
+      <c r="D196" s="228"/>
       <c r="E196" s="89" t="s">
         <v>130</v>
       </c>
@@ -19544,10 +19552,10 @@
       <c r="B197" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C197" s="236" t="s">
+      <c r="C197" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D197" s="236"/>
+      <c r="D197" s="228"/>
       <c r="E197" s="89" t="s">
         <v>130</v>
       </c>
@@ -19583,10 +19591,10 @@
       <c r="B198" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C198" s="236" t="s">
+      <c r="C198" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D198" s="236"/>
+      <c r="D198" s="228"/>
       <c r="E198" s="89" t="s">
         <v>130</v>
       </c>
@@ -19622,10 +19630,10 @@
       <c r="B199" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C199" s="236" t="s">
+      <c r="C199" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D199" s="236"/>
+      <c r="D199" s="228"/>
       <c r="E199" s="89" t="s">
         <v>130</v>
       </c>
@@ -19661,10 +19669,10 @@
       <c r="B200" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C200" s="236" t="s">
+      <c r="C200" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D200" s="236"/>
+      <c r="D200" s="228"/>
       <c r="E200" s="89" t="s">
         <v>130</v>
       </c>
@@ -19700,10 +19708,10 @@
       <c r="B201" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C201" s="236" t="s">
+      <c r="C201" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D201" s="236"/>
+      <c r="D201" s="228"/>
       <c r="E201" s="89" t="s">
         <v>130</v>
       </c>
@@ -19739,10 +19747,10 @@
       <c r="B202" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C202" s="236" t="s">
+      <c r="C202" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D202" s="236"/>
+      <c r="D202" s="228"/>
       <c r="E202" s="89" t="s">
         <v>130</v>
       </c>
@@ -19778,10 +19786,10 @@
       <c r="B203" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C203" s="236" t="s">
+      <c r="C203" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D203" s="236"/>
+      <c r="D203" s="228"/>
       <c r="E203" s="89" t="s">
         <v>130</v>
       </c>
@@ -19817,10 +19825,10 @@
       <c r="B204" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C204" s="236" t="s">
+      <c r="C204" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D204" s="236"/>
+      <c r="D204" s="228"/>
       <c r="E204" s="89" t="s">
         <v>130</v>
       </c>
@@ -19856,10 +19864,10 @@
       <c r="B205" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C205" s="236" t="s">
+      <c r="C205" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D205" s="236"/>
+      <c r="D205" s="228"/>
       <c r="E205" s="89" t="s">
         <v>130</v>
       </c>
@@ -19895,10 +19903,10 @@
       <c r="B206" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C206" s="236" t="s">
+      <c r="C206" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D206" s="236"/>
+      <c r="D206" s="228"/>
       <c r="E206" s="89" t="s">
         <v>130</v>
       </c>
@@ -19934,10 +19942,10 @@
       <c r="B207" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C207" s="236" t="s">
+      <c r="C207" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D207" s="236"/>
+      <c r="D207" s="228"/>
       <c r="E207" s="89" t="s">
         <v>130</v>
       </c>
@@ -19973,10 +19981,10 @@
       <c r="B208" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C208" s="236" t="s">
+      <c r="C208" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D208" s="236"/>
+      <c r="D208" s="228"/>
       <c r="E208" s="89" t="s">
         <v>130</v>
       </c>
@@ -20012,10 +20020,10 @@
       <c r="B209" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C209" s="236" t="s">
+      <c r="C209" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D209" s="236"/>
+      <c r="D209" s="228"/>
       <c r="E209" s="89" t="s">
         <v>91</v>
       </c>
@@ -20049,10 +20057,10 @@
       <c r="B210" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C210" s="236" t="s">
+      <c r="C210" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D210" s="236"/>
+      <c r="D210" s="228"/>
       <c r="E210" s="89" t="s">
         <v>91</v>
       </c>
@@ -20090,10 +20098,10 @@
       <c r="B211" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C211" s="236" t="s">
+      <c r="C211" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D211" s="236"/>
+      <c r="D211" s="228"/>
       <c r="E211" s="89" t="s">
         <v>91</v>
       </c>
@@ -20131,10 +20139,10 @@
       <c r="B212" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C212" s="236" t="s">
+      <c r="C212" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D212" s="236"/>
+      <c r="D212" s="228"/>
       <c r="E212" s="89" t="s">
         <v>91</v>
       </c>
@@ -20172,10 +20180,10 @@
       <c r="B213" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C213" s="236" t="s">
+      <c r="C213" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D213" s="236"/>
+      <c r="D213" s="228"/>
       <c r="E213" s="89" t="s">
         <v>91</v>
       </c>
@@ -20213,10 +20221,10 @@
       <c r="B214" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C214" s="236" t="s">
+      <c r="C214" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D214" s="236"/>
+      <c r="D214" s="228"/>
       <c r="E214" s="89" t="s">
         <v>91</v>
       </c>
@@ -20252,10 +20260,10 @@
       <c r="B215" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C215" s="236" t="s">
+      <c r="C215" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D215" s="236"/>
+      <c r="D215" s="228"/>
       <c r="E215" s="89" t="s">
         <v>91</v>
       </c>
@@ -20293,10 +20301,10 @@
       <c r="B216" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C216" s="236" t="s">
+      <c r="C216" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D216" s="236"/>
+      <c r="D216" s="228"/>
       <c r="E216" s="89" t="s">
         <v>91</v>
       </c>
@@ -20334,10 +20342,10 @@
       <c r="B217" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C217" s="236" t="s">
+      <c r="C217" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D217" s="236"/>
+      <c r="D217" s="228"/>
       <c r="E217" s="89" t="s">
         <v>91</v>
       </c>
@@ -20375,10 +20383,10 @@
       <c r="B218" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C218" s="236" t="s">
+      <c r="C218" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D218" s="236"/>
+      <c r="D218" s="228"/>
       <c r="E218" s="89" t="s">
         <v>91</v>
       </c>
@@ -20416,10 +20424,10 @@
       <c r="B219" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C219" s="236" t="s">
+      <c r="C219" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D219" s="236"/>
+      <c r="D219" s="228"/>
       <c r="E219" s="89" t="s">
         <v>91</v>
       </c>
@@ -20457,10 +20465,10 @@
       <c r="B220" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C220" s="236" t="s">
+      <c r="C220" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D220" s="236"/>
+      <c r="D220" s="228"/>
       <c r="E220" s="89" t="s">
         <v>91</v>
       </c>
@@ -20498,10 +20506,10 @@
       <c r="B221" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C221" s="236" t="s">
+      <c r="C221" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D221" s="236"/>
+      <c r="D221" s="228"/>
       <c r="E221" s="89" t="s">
         <v>91</v>
       </c>
@@ -20539,10 +20547,10 @@
       <c r="B222" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C222" s="236" t="s">
+      <c r="C222" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D222" s="236"/>
+      <c r="D222" s="228"/>
       <c r="E222" s="89" t="s">
         <v>91</v>
       </c>
@@ -20580,10 +20588,10 @@
       <c r="B223" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C223" s="236" t="s">
+      <c r="C223" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D223" s="236"/>
+      <c r="D223" s="228"/>
       <c r="E223" s="89" t="s">
         <v>91</v>
       </c>
@@ -20621,10 +20629,10 @@
       <c r="B224" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C224" s="236" t="s">
+      <c r="C224" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D224" s="236"/>
+      <c r="D224" s="228"/>
       <c r="E224" s="89" t="s">
         <v>91</v>
       </c>
@@ -20662,10 +20670,10 @@
       <c r="B225" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C225" s="236" t="s">
+      <c r="C225" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D225" s="236"/>
+      <c r="D225" s="228"/>
       <c r="E225" s="89" t="s">
         <v>91</v>
       </c>
@@ -20703,10 +20711,10 @@
       <c r="B226" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C226" s="236" t="s">
+      <c r="C226" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D226" s="236"/>
+      <c r="D226" s="228"/>
       <c r="E226" s="89" t="s">
         <v>91</v>
       </c>
@@ -20744,10 +20752,10 @@
       <c r="B227" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C227" s="236" t="s">
+      <c r="C227" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D227" s="236"/>
+      <c r="D227" s="228"/>
       <c r="E227" s="89" t="s">
         <v>91</v>
       </c>
@@ -20785,10 +20793,10 @@
       <c r="B228" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C228" s="236" t="s">
+      <c r="C228" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D228" s="236"/>
+      <c r="D228" s="228"/>
       <c r="E228" s="89" t="s">
         <v>91</v>
       </c>
@@ -20826,10 +20834,10 @@
       <c r="B229" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C229" s="236" t="s">
+      <c r="C229" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D229" s="236"/>
+      <c r="D229" s="228"/>
       <c r="E229" s="89" t="s">
         <v>91</v>
       </c>
@@ -20867,10 +20875,10 @@
       <c r="B230" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C230" s="236" t="s">
+      <c r="C230" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D230" s="236"/>
+      <c r="D230" s="228"/>
       <c r="E230" s="89" t="s">
         <v>91</v>
       </c>
@@ -20908,10 +20916,10 @@
       <c r="B231" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C231" s="236" t="s">
+      <c r="C231" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D231" s="236"/>
+      <c r="D231" s="228"/>
       <c r="E231" s="89" t="s">
         <v>91</v>
       </c>
@@ -20947,10 +20955,10 @@
       <c r="B232" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C232" s="236" t="s">
+      <c r="C232" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D232" s="236"/>
+      <c r="D232" s="228"/>
       <c r="E232" s="89" t="s">
         <v>91</v>
       </c>
@@ -20988,10 +20996,10 @@
       <c r="B233" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C233" s="236" t="s">
+      <c r="C233" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D233" s="236"/>
+      <c r="D233" s="228"/>
       <c r="E233" s="89" t="s">
         <v>91</v>
       </c>
@@ -21029,10 +21037,10 @@
       <c r="B234" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C234" s="236" t="s">
+      <c r="C234" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D234" s="236"/>
+      <c r="D234" s="228"/>
       <c r="E234" s="89" t="s">
         <v>83</v>
       </c>
@@ -21066,10 +21074,10 @@
       <c r="B235" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C235" s="236" t="s">
+      <c r="C235" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D235" s="236"/>
+      <c r="D235" s="228"/>
       <c r="E235" s="89" t="s">
         <v>83</v>
       </c>
@@ -21103,10 +21111,10 @@
       <c r="B236" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C236" s="236" t="s">
+      <c r="C236" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D236" s="236"/>
+      <c r="D236" s="228"/>
       <c r="E236" s="89" t="s">
         <v>83</v>
       </c>
@@ -21140,10 +21148,10 @@
       <c r="B237" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C237" s="236" t="s">
+      <c r="C237" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D237" s="236"/>
+      <c r="D237" s="228"/>
       <c r="E237" s="89" t="s">
         <v>83</v>
       </c>
@@ -21177,10 +21185,10 @@
       <c r="B238" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C238" s="236" t="s">
+      <c r="C238" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D238" s="236"/>
+      <c r="D238" s="228"/>
       <c r="E238" s="89" t="s">
         <v>83</v>
       </c>
@@ -21216,10 +21224,10 @@
       <c r="B239" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C239" s="236" t="s">
+      <c r="C239" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D239" s="236"/>
+      <c r="D239" s="228"/>
       <c r="E239" s="89" t="s">
         <v>83</v>
       </c>
@@ -21255,10 +21263,10 @@
       <c r="B240" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C240" s="236" t="s">
+      <c r="C240" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D240" s="236"/>
+      <c r="D240" s="228"/>
       <c r="E240" s="89" t="s">
         <v>83</v>
       </c>
@@ -21294,10 +21302,10 @@
       <c r="B241" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C241" s="236" t="s">
+      <c r="C241" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D241" s="236"/>
+      <c r="D241" s="228"/>
       <c r="E241" s="89" t="s">
         <v>83</v>
       </c>
@@ -21333,10 +21341,10 @@
       <c r="B242" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C242" s="236" t="s">
+      <c r="C242" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D242" s="236"/>
+      <c r="D242" s="228"/>
       <c r="E242" s="89" t="s">
         <v>83</v>
       </c>
@@ -21372,10 +21380,10 @@
       <c r="B243" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C243" s="236" t="s">
+      <c r="C243" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D243" s="236"/>
+      <c r="D243" s="228"/>
       <c r="E243" s="89" t="s">
         <v>83</v>
       </c>
@@ -21411,10 +21419,10 @@
       <c r="B244" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C244" s="236" t="s">
+      <c r="C244" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D244" s="236"/>
+      <c r="D244" s="228"/>
       <c r="E244" s="89" t="s">
         <v>83</v>
       </c>
@@ -21450,10 +21458,10 @@
       <c r="B245" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C245" s="236" t="s">
+      <c r="C245" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D245" s="236"/>
+      <c r="D245" s="228"/>
       <c r="E245" s="89" t="s">
         <v>83</v>
       </c>
@@ -21489,10 +21497,10 @@
       <c r="B246" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C246" s="236" t="s">
+      <c r="C246" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D246" s="236"/>
+      <c r="D246" s="228"/>
       <c r="E246" s="89" t="s">
         <v>83</v>
       </c>
@@ -21528,10 +21536,10 @@
       <c r="B247" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C247" s="236" t="s">
+      <c r="C247" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D247" s="236"/>
+      <c r="D247" s="228"/>
       <c r="E247" s="89" t="s">
         <v>83</v>
       </c>
@@ -21567,10 +21575,10 @@
       <c r="B248" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C248" s="236" t="s">
+      <c r="C248" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D248" s="236"/>
+      <c r="D248" s="228"/>
       <c r="E248" s="89" t="s">
         <v>83</v>
       </c>
@@ -21606,10 +21614,10 @@
       <c r="B249" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C249" s="236" t="s">
+      <c r="C249" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D249" s="236"/>
+      <c r="D249" s="228"/>
       <c r="E249" s="89" t="s">
         <v>83</v>
       </c>
@@ -21645,10 +21653,10 @@
       <c r="B250" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C250" s="236" t="s">
+      <c r="C250" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D250" s="236"/>
+      <c r="D250" s="228"/>
       <c r="E250" s="89" t="s">
         <v>83</v>
       </c>
@@ -21684,10 +21692,10 @@
       <c r="B251" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C251" s="236" t="s">
+      <c r="C251" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D251" s="236"/>
+      <c r="D251" s="228"/>
       <c r="E251" s="89" t="s">
         <v>83</v>
       </c>
@@ -21723,10 +21731,10 @@
       <c r="B252" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C252" s="236" t="s">
+      <c r="C252" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D252" s="236"/>
+      <c r="D252" s="228"/>
       <c r="E252" s="89" t="s">
         <v>83</v>
       </c>
@@ -21762,10 +21770,10 @@
       <c r="B253" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C253" s="236" t="s">
+      <c r="C253" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D253" s="236"/>
+      <c r="D253" s="228"/>
       <c r="E253" s="89" t="s">
         <v>83</v>
       </c>
@@ -21801,10 +21809,10 @@
       <c r="B254" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C254" s="236" t="s">
+      <c r="C254" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D254" s="236"/>
+      <c r="D254" s="228"/>
       <c r="E254" s="89" t="s">
         <v>83</v>
       </c>
@@ -21840,10 +21848,10 @@
       <c r="B255" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C255" s="236" t="s">
+      <c r="C255" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D255" s="236"/>
+      <c r="D255" s="228"/>
       <c r="E255" s="89" t="s">
         <v>83</v>
       </c>
@@ -21879,10 +21887,10 @@
       <c r="B256" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C256" s="236" t="s">
+      <c r="C256" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D256" s="236"/>
+      <c r="D256" s="228"/>
       <c r="E256" s="89" t="s">
         <v>83</v>
       </c>
@@ -21918,10 +21926,10 @@
       <c r="B257" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C257" s="236" t="s">
+      <c r="C257" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D257" s="236"/>
+      <c r="D257" s="228"/>
       <c r="E257" s="89" t="s">
         <v>83</v>
       </c>
@@ -21957,10 +21965,10 @@
       <c r="B258" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C258" s="236" t="s">
+      <c r="C258" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D258" s="236"/>
+      <c r="D258" s="228"/>
       <c r="E258" s="89" t="s">
         <v>83</v>
       </c>
@@ -21998,10 +22006,10 @@
       <c r="B259" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C259" s="236" t="s">
+      <c r="C259" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D259" s="236"/>
+      <c r="D259" s="228"/>
       <c r="E259" s="89" t="s">
         <v>83</v>
       </c>
@@ -22039,10 +22047,10 @@
       <c r="B260" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C260" s="236" t="s">
+      <c r="C260" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D260" s="236"/>
+      <c r="D260" s="228"/>
       <c r="E260" s="89" t="s">
         <v>83</v>
       </c>
@@ -22080,10 +22088,10 @@
       <c r="B261" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C261" s="236" t="s">
+      <c r="C261" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D261" s="236"/>
+      <c r="D261" s="228"/>
       <c r="E261" s="89" t="s">
         <v>83</v>
       </c>
@@ -22121,10 +22129,10 @@
       <c r="B262" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C262" s="236" t="s">
+      <c r="C262" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D262" s="236"/>
+      <c r="D262" s="228"/>
       <c r="E262" s="89" t="s">
         <v>83</v>
       </c>
@@ -22162,10 +22170,10 @@
       <c r="B263" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C263" s="236" t="s">
+      <c r="C263" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D263" s="236"/>
+      <c r="D263" s="228"/>
       <c r="E263" s="89" t="s">
         <v>83</v>
       </c>
@@ -22203,10 +22211,10 @@
       <c r="B264" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C264" s="236" t="s">
+      <c r="C264" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D264" s="236"/>
+      <c r="D264" s="228"/>
       <c r="E264" s="89" t="s">
         <v>83</v>
       </c>
@@ -22244,10 +22252,10 @@
       <c r="B265" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C265" s="236" t="s">
+      <c r="C265" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D265" s="236"/>
+      <c r="D265" s="228"/>
       <c r="E265" s="89" t="s">
         <v>83</v>
       </c>
@@ -22285,10 +22293,10 @@
       <c r="B266" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C266" s="236" t="s">
+      <c r="C266" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D266" s="236"/>
+      <c r="D266" s="228"/>
       <c r="E266" s="89" t="s">
         <v>83</v>
       </c>
@@ -22326,10 +22334,10 @@
       <c r="B267" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C267" s="236" t="s">
+      <c r="C267" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D267" s="236"/>
+      <c r="D267" s="228"/>
       <c r="E267" s="89" t="s">
         <v>83</v>
       </c>
@@ -22367,10 +22375,10 @@
       <c r="B268" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C268" s="236" t="s">
+      <c r="C268" s="228" t="s">
         <v>168</v>
       </c>
-      <c r="D268" s="236"/>
+      <c r="D268" s="228"/>
       <c r="E268" s="89" t="s">
         <v>83</v>
       </c>
@@ -22408,10 +22416,10 @@
       <c r="B269" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C269" s="236" t="s">
+      <c r="C269" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D269" s="236"/>
+      <c r="D269" s="228"/>
       <c r="E269" s="89" t="s">
         <v>100</v>
       </c>
@@ -22445,10 +22453,10 @@
       <c r="B270" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C270" s="236" t="s">
+      <c r="C270" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D270" s="236"/>
+      <c r="D270" s="228"/>
       <c r="E270" s="89" t="s">
         <v>100</v>
       </c>
@@ -22482,10 +22490,10 @@
       <c r="B271" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C271" s="236" t="s">
+      <c r="C271" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D271" s="236"/>
+      <c r="D271" s="228"/>
       <c r="E271" s="89" t="s">
         <v>100</v>
       </c>
@@ -22523,10 +22531,10 @@
       <c r="B272" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C272" s="236" t="s">
+      <c r="C272" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D272" s="236"/>
+      <c r="D272" s="228"/>
       <c r="E272" s="89" t="s">
         <v>100</v>
       </c>
@@ -22564,10 +22572,10 @@
       <c r="B273" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C273" s="236" t="s">
+      <c r="C273" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D273" s="236"/>
+      <c r="D273" s="228"/>
       <c r="E273" s="89" t="s">
         <v>100</v>
       </c>
@@ -22605,10 +22613,10 @@
       <c r="B274" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C274" s="236" t="s">
+      <c r="C274" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D274" s="236"/>
+      <c r="D274" s="228"/>
       <c r="E274" s="89" t="s">
         <v>100</v>
       </c>
@@ -22646,10 +22654,10 @@
       <c r="B275" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C275" s="236" t="s">
+      <c r="C275" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D275" s="236"/>
+      <c r="D275" s="228"/>
       <c r="E275" s="89" t="s">
         <v>100</v>
       </c>
@@ -22687,10 +22695,10 @@
       <c r="B276" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C276" s="236" t="s">
+      <c r="C276" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D276" s="236"/>
+      <c r="D276" s="228"/>
       <c r="E276" s="89" t="s">
         <v>100</v>
       </c>
@@ -22728,10 +22736,10 @@
       <c r="B277" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C277" s="236" t="s">
+      <c r="C277" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D277" s="236"/>
+      <c r="D277" s="228"/>
       <c r="E277" s="89" t="s">
         <v>100</v>
       </c>
@@ -22769,10 +22777,10 @@
       <c r="B278" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C278" s="236" t="s">
+      <c r="C278" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D278" s="236"/>
+      <c r="D278" s="228"/>
       <c r="E278" s="89" t="s">
         <v>107</v>
       </c>
@@ -22806,10 +22814,10 @@
       <c r="B279" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C279" s="236" t="s">
+      <c r="C279" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D279" s="236"/>
+      <c r="D279" s="228"/>
       <c r="E279" s="89" t="s">
         <v>107</v>
       </c>
@@ -22845,10 +22853,10 @@
       <c r="B280" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C280" s="236" t="s">
+      <c r="C280" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D280" s="236"/>
+      <c r="D280" s="228"/>
       <c r="E280" s="89" t="s">
         <v>107</v>
       </c>
@@ -22884,10 +22892,10 @@
       <c r="B281" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C281" s="236" t="s">
+      <c r="C281" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D281" s="236"/>
+      <c r="D281" s="228"/>
       <c r="E281" s="89" t="s">
         <v>107</v>
       </c>
@@ -22923,10 +22931,10 @@
       <c r="B282" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C282" s="236" t="s">
+      <c r="C282" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D282" s="236"/>
+      <c r="D282" s="228"/>
       <c r="E282" s="89" t="s">
         <v>107</v>
       </c>
@@ -22962,10 +22970,10 @@
       <c r="B283" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C283" s="236" t="s">
+      <c r="C283" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D283" s="236"/>
+      <c r="D283" s="228"/>
       <c r="E283" s="89" t="s">
         <v>107</v>
       </c>
@@ -23001,10 +23009,10 @@
       <c r="B284" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C284" s="236" t="s">
+      <c r="C284" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D284" s="236"/>
+      <c r="D284" s="228"/>
       <c r="E284" s="89" t="s">
         <v>107</v>
       </c>
@@ -23040,10 +23048,10 @@
       <c r="B285" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C285" s="236" t="s">
+      <c r="C285" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D285" s="236"/>
+      <c r="D285" s="228"/>
       <c r="E285" s="89" t="s">
         <v>107</v>
       </c>
@@ -23081,10 +23089,10 @@
       <c r="B286" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C286" s="236" t="s">
+      <c r="C286" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D286" s="236"/>
+      <c r="D286" s="228"/>
       <c r="E286" s="89" t="s">
         <v>107</v>
       </c>
@@ -23122,10 +23130,10 @@
       <c r="B287" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C287" s="236" t="s">
+      <c r="C287" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D287" s="236"/>
+      <c r="D287" s="228"/>
       <c r="E287" s="89" t="s">
         <v>107</v>
       </c>
@@ -23163,10 +23171,10 @@
       <c r="B288" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C288" s="236" t="s">
+      <c r="C288" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D288" s="236"/>
+      <c r="D288" s="228"/>
       <c r="E288" s="89" t="s">
         <v>107</v>
       </c>
@@ -23204,10 +23212,10 @@
       <c r="B289" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C289" s="236" t="s">
+      <c r="C289" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D289" s="236"/>
+      <c r="D289" s="228"/>
       <c r="E289" s="89" t="s">
         <v>107</v>
       </c>
@@ -23243,10 +23251,10 @@
       <c r="B290" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C290" s="236" t="s">
+      <c r="C290" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D290" s="236"/>
+      <c r="D290" s="228"/>
       <c r="E290" s="89" t="s">
         <v>107</v>
       </c>
@@ -23284,10 +23292,10 @@
       <c r="B291" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C291" s="236" t="s">
+      <c r="C291" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D291" s="236"/>
+      <c r="D291" s="228"/>
       <c r="E291" s="89" t="s">
         <v>107</v>
       </c>
@@ -23325,10 +23333,10 @@
       <c r="B292" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C292" s="236" t="s">
+      <c r="C292" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D292" s="236"/>
+      <c r="D292" s="228"/>
       <c r="E292" s="89" t="s">
         <v>107</v>
       </c>
@@ -23366,10 +23374,10 @@
       <c r="B293" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C293" s="236" t="s">
+      <c r="C293" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D293" s="236"/>
+      <c r="D293" s="228"/>
       <c r="E293" s="89" t="s">
         <v>107</v>
       </c>
@@ -23407,10 +23415,10 @@
       <c r="B294" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C294" s="236" t="s">
+      <c r="C294" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D294" s="236"/>
+      <c r="D294" s="228"/>
       <c r="E294" s="89" t="s">
         <v>107</v>
       </c>
@@ -23448,10 +23456,10 @@
       <c r="B295" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C295" s="236" t="s">
+      <c r="C295" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D295" s="236"/>
+      <c r="D295" s="228"/>
       <c r="E295" s="89" t="s">
         <v>107</v>
       </c>
@@ -23489,10 +23497,10 @@
       <c r="B296" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C296" s="236" t="s">
+      <c r="C296" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D296" s="236"/>
+      <c r="D296" s="228"/>
       <c r="E296" s="89" t="s">
         <v>107</v>
       </c>
@@ -23530,10 +23538,10 @@
       <c r="B297" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C297" s="236" t="s">
+      <c r="C297" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D297" s="236"/>
+      <c r="D297" s="228"/>
       <c r="E297" s="89" t="s">
         <v>107</v>
       </c>
@@ -23571,10 +23579,10 @@
       <c r="B298" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C298" s="236" t="s">
+      <c r="C298" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D298" s="236"/>
+      <c r="D298" s="228"/>
       <c r="E298" s="89" t="s">
         <v>107</v>
       </c>
@@ -23614,10 +23622,10 @@
       <c r="B299" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C299" s="236" t="s">
+      <c r="C299" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D299" s="236"/>
+      <c r="D299" s="228"/>
       <c r="E299" s="89" t="s">
         <v>107</v>
       </c>
@@ -23657,10 +23665,10 @@
       <c r="B300" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C300" s="236" t="s">
+      <c r="C300" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D300" s="236"/>
+      <c r="D300" s="228"/>
       <c r="E300" s="89" t="s">
         <v>107</v>
       </c>
@@ -23700,10 +23708,10 @@
       <c r="B301" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C301" s="236" t="s">
+      <c r="C301" s="228" t="s">
         <v>172</v>
       </c>
-      <c r="D301" s="236"/>
+      <c r="D301" s="228"/>
       <c r="E301" s="89" t="s">
         <v>107</v>
       </c>
@@ -23754,12 +23762,12 @@
       <c r="O302" s="85"/>
     </row>
     <row r="303" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A303" s="237" t="s">
+      <c r="A303" s="229" t="s">
         <v>71</v>
       </c>
-      <c r="B303" s="237"/>
-      <c r="C303" s="237"/>
-      <c r="D303" s="237"/>
+      <c r="B303" s="229"/>
+      <c r="C303" s="229"/>
+      <c r="D303" s="229"/>
       <c r="E303" s="84"/>
       <c r="F303" s="84"/>
       <c r="G303" s="84"/>
@@ -23773,12 +23781,12 @@
       <c r="O303" s="84"/>
     </row>
     <row r="304" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A304" s="237" t="s">
+      <c r="A304" s="229" t="s">
         <v>139</v>
       </c>
-      <c r="B304" s="237"/>
-      <c r="C304" s="237"/>
-      <c r="D304" s="237"/>
+      <c r="B304" s="229"/>
+      <c r="C304" s="229"/>
+      <c r="D304" s="229"/>
       <c r="E304" s="84"/>
       <c r="F304" s="84"/>
       <c r="G304" s="84"/>
@@ -23798,372 +23806,372 @@
       <c r="D305" s="85"/>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A306" s="238" t="s">
+      <c r="A306" s="230" t="s">
         <v>140</v>
       </c>
-      <c r="B306" s="238"/>
-      <c r="C306" s="238"/>
+      <c r="B306" s="230"/>
+      <c r="C306" s="230"/>
       <c r="D306" s="84"/>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A307" s="236" t="s">
+      <c r="A307" s="228" t="s">
         <v>107</v>
       </c>
-      <c r="B307" s="236"/>
-      <c r="C307" s="236"/>
-      <c r="D307" s="236"/>
+      <c r="B307" s="228"/>
+      <c r="C307" s="228"/>
+      <c r="D307" s="228"/>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A308" s="236" t="s">
+      <c r="A308" s="228" t="s">
         <v>218</v>
       </c>
-      <c r="B308" s="236"/>
-      <c r="C308" s="236"/>
-      <c r="D308" s="236"/>
+      <c r="B308" s="228"/>
+      <c r="C308" s="228"/>
+      <c r="D308" s="228"/>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A309" s="236" t="s">
+      <c r="A309" s="228" t="s">
         <v>238</v>
       </c>
-      <c r="B309" s="236"/>
-      <c r="C309" s="236"/>
-      <c r="D309" s="236"/>
+      <c r="B309" s="228"/>
+      <c r="C309" s="228"/>
+      <c r="D309" s="228"/>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A310" s="236" t="s">
+      <c r="A310" s="228" t="s">
         <v>245</v>
       </c>
-      <c r="B310" s="236"/>
-      <c r="C310" s="236"/>
-      <c r="D310" s="236"/>
+      <c r="B310" s="228"/>
+      <c r="C310" s="228"/>
+      <c r="D310" s="228"/>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A311" s="236" t="s">
+      <c r="A311" s="228" t="s">
         <v>115</v>
       </c>
-      <c r="B311" s="236"/>
-      <c r="C311" s="236"/>
-      <c r="D311" s="236"/>
+      <c r="B311" s="228"/>
+      <c r="C311" s="228"/>
+      <c r="D311" s="228"/>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A312" s="236" t="s">
+      <c r="A312" s="228" t="s">
         <v>261</v>
       </c>
-      <c r="B312" s="236"/>
-      <c r="C312" s="236"/>
-      <c r="D312" s="236"/>
+      <c r="B312" s="228"/>
+      <c r="C312" s="228"/>
+      <c r="D312" s="228"/>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A313" s="236" t="s">
+      <c r="A313" s="228" t="s">
         <v>271</v>
       </c>
-      <c r="B313" s="236"/>
-      <c r="C313" s="236"/>
-      <c r="D313" s="236"/>
+      <c r="B313" s="228"/>
+      <c r="C313" s="228"/>
+      <c r="D313" s="228"/>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A314" s="236" t="s">
+      <c r="A314" s="228" t="s">
         <v>245</v>
       </c>
-      <c r="B314" s="236"/>
-      <c r="C314" s="236"/>
-      <c r="D314" s="236"/>
+      <c r="B314" s="228"/>
+      <c r="C314" s="228"/>
+      <c r="D314" s="228"/>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A315" s="236" t="s">
+      <c r="A315" s="228" t="s">
         <v>288</v>
       </c>
-      <c r="B315" s="236"/>
-      <c r="C315" s="236"/>
-      <c r="D315" s="236"/>
+      <c r="B315" s="228"/>
+      <c r="C315" s="228"/>
+      <c r="D315" s="228"/>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A316" s="236" t="s">
+      <c r="A316" s="228" t="s">
         <v>81</v>
       </c>
-      <c r="B316" s="236"/>
-      <c r="C316" s="236"/>
-      <c r="D316" s="236"/>
+      <c r="B316" s="228"/>
+      <c r="C316" s="228"/>
+      <c r="D316" s="228"/>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A317" s="236" t="s">
+      <c r="A317" s="228" t="s">
         <v>121</v>
       </c>
-      <c r="B317" s="236"/>
-      <c r="C317" s="236"/>
-      <c r="D317" s="236"/>
+      <c r="B317" s="228"/>
+      <c r="C317" s="228"/>
+      <c r="D317" s="228"/>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A318" s="236" t="s">
+      <c r="A318" s="228" t="s">
         <v>308</v>
       </c>
-      <c r="B318" s="236"/>
-      <c r="C318" s="236"/>
-      <c r="D318" s="236"/>
+      <c r="B318" s="228"/>
+      <c r="C318" s="228"/>
+      <c r="D318" s="228"/>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A319" s="236" t="s">
+      <c r="A319" s="228" t="s">
         <v>103</v>
       </c>
-      <c r="B319" s="236"/>
-      <c r="C319" s="236"/>
-      <c r="D319" s="236"/>
+      <c r="B319" s="228"/>
+      <c r="C319" s="228"/>
+      <c r="D319" s="228"/>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A320" s="236" t="s">
+      <c r="A320" s="228" t="s">
         <v>122</v>
       </c>
-      <c r="B320" s="236"/>
-      <c r="C320" s="236"/>
-      <c r="D320" s="236"/>
+      <c r="B320" s="228"/>
+      <c r="C320" s="228"/>
+      <c r="D320" s="228"/>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A321" s="236" t="s">
+      <c r="A321" s="228" t="s">
         <v>432</v>
       </c>
-      <c r="B321" s="236"/>
-      <c r="C321" s="236"/>
-      <c r="D321" s="236"/>
+      <c r="B321" s="228"/>
+      <c r="C321" s="228"/>
+      <c r="D321" s="228"/>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A322" s="236" t="s">
+      <c r="A322" s="228" t="s">
         <v>438</v>
       </c>
-      <c r="B322" s="236"/>
-      <c r="C322" s="236"/>
-      <c r="D322" s="236"/>
+      <c r="B322" s="228"/>
+      <c r="C322" s="228"/>
+      <c r="D322" s="228"/>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A323" s="236" t="s">
+      <c r="A323" s="228" t="s">
         <v>99</v>
       </c>
-      <c r="B323" s="236"/>
-      <c r="C323" s="236"/>
-      <c r="D323" s="236"/>
+      <c r="B323" s="228"/>
+      <c r="C323" s="228"/>
+      <c r="D323" s="228"/>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A324" s="236" t="s">
+      <c r="A324" s="228" t="s">
         <v>100</v>
       </c>
-      <c r="B324" s="236"/>
-      <c r="C324" s="236"/>
-      <c r="D324" s="236"/>
+      <c r="B324" s="228"/>
+      <c r="C324" s="228"/>
+      <c r="D324" s="228"/>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A325" s="236" t="s">
+      <c r="A325" s="228" t="s">
         <v>481</v>
       </c>
-      <c r="B325" s="236"/>
-      <c r="C325" s="236"/>
-      <c r="D325" s="236"/>
+      <c r="B325" s="228"/>
+      <c r="C325" s="228"/>
+      <c r="D325" s="228"/>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A326" s="236" t="s">
+      <c r="A326" s="228" t="s">
         <v>245</v>
       </c>
-      <c r="B326" s="236"/>
-      <c r="C326" s="236"/>
-      <c r="D326" s="236"/>
+      <c r="B326" s="228"/>
+      <c r="C326" s="228"/>
+      <c r="D326" s="228"/>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A327" s="236" t="s">
+      <c r="A327" s="228" t="s">
         <v>594</v>
       </c>
-      <c r="B327" s="236"/>
-      <c r="C327" s="236"/>
-      <c r="D327" s="236"/>
+      <c r="B327" s="228"/>
+      <c r="C327" s="228"/>
+      <c r="D327" s="228"/>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A328" s="236" t="s">
+      <c r="A328" s="228" t="s">
         <v>245</v>
       </c>
-      <c r="B328" s="236"/>
-      <c r="C328" s="236"/>
-      <c r="D328" s="236"/>
+      <c r="B328" s="228"/>
+      <c r="C328" s="228"/>
+      <c r="D328" s="228"/>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A329" s="236" t="s">
+      <c r="A329" s="228" t="s">
         <v>613</v>
       </c>
-      <c r="B329" s="236"/>
-      <c r="C329" s="236"/>
-      <c r="D329" s="236"/>
+      <c r="B329" s="228"/>
+      <c r="C329" s="228"/>
+      <c r="D329" s="228"/>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A330" s="236" t="s">
+      <c r="A330" s="228" t="s">
         <v>130</v>
       </c>
-      <c r="B330" s="236"/>
-      <c r="C330" s="236"/>
-      <c r="D330" s="236"/>
+      <c r="B330" s="228"/>
+      <c r="C330" s="228"/>
+      <c r="D330" s="228"/>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A331" s="236" t="s">
+      <c r="A331" s="228" t="s">
         <v>132</v>
       </c>
-      <c r="B331" s="236"/>
-      <c r="C331" s="236"/>
-      <c r="D331" s="236"/>
+      <c r="B331" s="228"/>
+      <c r="C331" s="228"/>
+      <c r="D331" s="228"/>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A332" s="236" t="s">
+      <c r="A332" s="228" t="s">
         <v>91</v>
       </c>
-      <c r="B332" s="236"/>
-      <c r="C332" s="236"/>
-      <c r="D332" s="236"/>
+      <c r="B332" s="228"/>
+      <c r="C332" s="228"/>
+      <c r="D332" s="228"/>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A333" s="236" t="s">
+      <c r="A333" s="228" t="s">
         <v>16</v>
       </c>
-      <c r="B333" s="236"/>
-      <c r="C333" s="236"/>
-      <c r="D333" s="236"/>
+      <c r="B333" s="228"/>
+      <c r="C333" s="228"/>
+      <c r="D333" s="228"/>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A334" s="236" t="s">
+      <c r="A334" s="228" t="s">
         <v>17</v>
       </c>
-      <c r="B334" s="236"/>
-      <c r="C334" s="236"/>
-      <c r="D334" s="236"/>
+      <c r="B334" s="228"/>
+      <c r="C334" s="228"/>
+      <c r="D334" s="228"/>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A335" s="236" t="s">
+      <c r="A335" s="228" t="s">
         <v>83</v>
       </c>
-      <c r="B335" s="236"/>
-      <c r="C335" s="236"/>
-      <c r="D335" s="236"/>
+      <c r="B335" s="228"/>
+      <c r="C335" s="228"/>
+      <c r="D335" s="228"/>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A336" s="236" t="s">
+      <c r="A336" s="228" t="s">
         <v>245</v>
       </c>
-      <c r="B336" s="236"/>
-      <c r="C336" s="236"/>
-      <c r="D336" s="236"/>
+      <c r="B336" s="228"/>
+      <c r="C336" s="228"/>
+      <c r="D336" s="228"/>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A337" s="236" t="s">
+      <c r="A337" s="228" t="s">
         <v>128</v>
       </c>
-      <c r="B337" s="236"/>
-      <c r="C337" s="236"/>
-      <c r="D337" s="236"/>
+      <c r="B337" s="228"/>
+      <c r="C337" s="228"/>
+      <c r="D337" s="228"/>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A338" s="236" t="s">
+      <c r="A338" s="228" t="s">
         <v>106</v>
       </c>
-      <c r="B338" s="236"/>
-      <c r="C338" s="236"/>
-      <c r="D338" s="236"/>
+      <c r="B338" s="228"/>
+      <c r="C338" s="228"/>
+      <c r="D338" s="228"/>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A339" s="236" t="s">
+      <c r="A339" s="228" t="s">
         <v>129</v>
       </c>
-      <c r="B339" s="236"/>
-      <c r="C339" s="236"/>
-      <c r="D339" s="236"/>
+      <c r="B339" s="228"/>
+      <c r="C339" s="228"/>
+      <c r="D339" s="228"/>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A340" s="236" t="s">
+      <c r="A340" s="228" t="s">
         <v>137</v>
       </c>
-      <c r="B340" s="236"/>
-      <c r="C340" s="236"/>
-      <c r="D340" s="236"/>
+      <c r="B340" s="228"/>
+      <c r="C340" s="228"/>
+      <c r="D340" s="228"/>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A341" s="236" t="s">
+      <c r="A341" s="228" t="s">
         <v>138</v>
       </c>
-      <c r="B341" s="236"/>
-      <c r="C341" s="236"/>
-      <c r="D341" s="236"/>
+      <c r="B341" s="228"/>
+      <c r="C341" s="228"/>
+      <c r="D341" s="228"/>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A342" s="236" t="s">
+      <c r="A342" s="228" t="s">
         <v>121</v>
       </c>
-      <c r="B342" s="236"/>
-      <c r="C342" s="236"/>
-      <c r="D342" s="236"/>
+      <c r="B342" s="228"/>
+      <c r="C342" s="228"/>
+      <c r="D342" s="228"/>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A343" s="236" t="s">
+      <c r="A343" s="228" t="s">
         <v>138</v>
       </c>
-      <c r="B343" s="236"/>
-      <c r="C343" s="236"/>
-      <c r="D343" s="236"/>
+      <c r="B343" s="228"/>
+      <c r="C343" s="228"/>
+      <c r="D343" s="228"/>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A344" s="236" t="s">
+      <c r="A344" s="228" t="s">
         <v>100</v>
       </c>
-      <c r="B344" s="236"/>
-      <c r="C344" s="236"/>
-      <c r="D344" s="236"/>
+      <c r="B344" s="228"/>
+      <c r="C344" s="228"/>
+      <c r="D344" s="228"/>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A345" s="236" t="s">
+      <c r="A345" s="228" t="s">
         <v>1023</v>
       </c>
-      <c r="B345" s="236"/>
-      <c r="C345" s="236"/>
-      <c r="D345" s="236"/>
+      <c r="B345" s="228"/>
+      <c r="C345" s="228"/>
+      <c r="D345" s="228"/>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A346" s="236" t="s">
+      <c r="A346" s="228" t="s">
         <v>107</v>
       </c>
-      <c r="B346" s="236"/>
-      <c r="C346" s="236"/>
-      <c r="D346" s="236"/>
+      <c r="B346" s="228"/>
+      <c r="C346" s="228"/>
+      <c r="D346" s="228"/>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A347" s="236" t="s">
+      <c r="A347" s="228" t="s">
         <v>271</v>
       </c>
-      <c r="B347" s="236"/>
-      <c r="C347" s="236"/>
-      <c r="D347" s="236"/>
+      <c r="B347" s="228"/>
+      <c r="C347" s="228"/>
+      <c r="D347" s="228"/>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A348" s="236" t="s">
+      <c r="A348" s="228" t="s">
         <v>108</v>
       </c>
-      <c r="B348" s="236"/>
-      <c r="C348" s="236"/>
-      <c r="D348" s="236"/>
+      <c r="B348" s="228"/>
+      <c r="C348" s="228"/>
+      <c r="D348" s="228"/>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A349" s="236" t="s">
+      <c r="A349" s="228" t="s">
         <v>115</v>
       </c>
-      <c r="B349" s="236"/>
-      <c r="C349" s="236"/>
-      <c r="D349" s="236"/>
+      <c r="B349" s="228"/>
+      <c r="C349" s="228"/>
+      <c r="D349" s="228"/>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A350" s="236" t="s">
+      <c r="A350" s="228" t="s">
         <v>261</v>
       </c>
-      <c r="B350" s="236"/>
-      <c r="C350" s="236"/>
-      <c r="D350" s="236"/>
+      <c r="B350" s="228"/>
+      <c r="C350" s="228"/>
+      <c r="D350" s="228"/>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A351" s="236" t="s">
+      <c r="A351" s="228" t="s">
         <v>128</v>
       </c>
-      <c r="B351" s="236"/>
-      <c r="C351" s="236"/>
-      <c r="D351" s="236"/>
+      <c r="B351" s="228"/>
+      <c r="C351" s="228"/>
+      <c r="D351" s="228"/>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352" s="85"/>
@@ -24173,6 +24181,338 @@
     </row>
   </sheetData>
   <mergeCells count="356">
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="C146:D146"/>
+    <mergeCell ref="C147:D147"/>
+    <mergeCell ref="C148:D148"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="C160:D160"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="C164:D164"/>
+    <mergeCell ref="C165:D165"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="C173:D173"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C178:D178"/>
+    <mergeCell ref="C179:D179"/>
+    <mergeCell ref="C180:D180"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="C186:D186"/>
+    <mergeCell ref="C187:D187"/>
+    <mergeCell ref="C188:D188"/>
+    <mergeCell ref="C189:D189"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="C192:D192"/>
+    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="C196:D196"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="C200:D200"/>
+    <mergeCell ref="C201:D201"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="C203:D203"/>
+    <mergeCell ref="C204:D204"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="C208:D208"/>
+    <mergeCell ref="C209:D209"/>
+    <mergeCell ref="C210:D210"/>
+    <mergeCell ref="C211:D211"/>
+    <mergeCell ref="C212:D212"/>
+    <mergeCell ref="C213:D213"/>
+    <mergeCell ref="C214:D214"/>
+    <mergeCell ref="C215:D215"/>
+    <mergeCell ref="C216:D216"/>
+    <mergeCell ref="C217:D217"/>
+    <mergeCell ref="C218:D218"/>
+    <mergeCell ref="C219:D219"/>
+    <mergeCell ref="C220:D220"/>
+    <mergeCell ref="C221:D221"/>
+    <mergeCell ref="C222:D222"/>
+    <mergeCell ref="C223:D223"/>
+    <mergeCell ref="C224:D224"/>
+    <mergeCell ref="C225:D225"/>
+    <mergeCell ref="C226:D226"/>
+    <mergeCell ref="C227:D227"/>
+    <mergeCell ref="C228:D228"/>
+    <mergeCell ref="C229:D229"/>
+    <mergeCell ref="C230:D230"/>
+    <mergeCell ref="C231:D231"/>
+    <mergeCell ref="C232:D232"/>
+    <mergeCell ref="C233:D233"/>
+    <mergeCell ref="C234:D234"/>
+    <mergeCell ref="C235:D235"/>
+    <mergeCell ref="C236:D236"/>
+    <mergeCell ref="C237:D237"/>
+    <mergeCell ref="C238:D238"/>
+    <mergeCell ref="C239:D239"/>
+    <mergeCell ref="C240:D240"/>
+    <mergeCell ref="C241:D241"/>
+    <mergeCell ref="C242:D242"/>
+    <mergeCell ref="C243:D243"/>
+    <mergeCell ref="C244:D244"/>
+    <mergeCell ref="C245:D245"/>
+    <mergeCell ref="C246:D246"/>
+    <mergeCell ref="C247:D247"/>
+    <mergeCell ref="C248:D248"/>
+    <mergeCell ref="C249:D249"/>
+    <mergeCell ref="C250:D250"/>
+    <mergeCell ref="C251:D251"/>
+    <mergeCell ref="C252:D252"/>
+    <mergeCell ref="C253:D253"/>
+    <mergeCell ref="C254:D254"/>
+    <mergeCell ref="C255:D255"/>
+    <mergeCell ref="C256:D256"/>
+    <mergeCell ref="C257:D257"/>
+    <mergeCell ref="C258:D258"/>
+    <mergeCell ref="C259:D259"/>
+    <mergeCell ref="C260:D260"/>
+    <mergeCell ref="C261:D261"/>
+    <mergeCell ref="C262:D262"/>
+    <mergeCell ref="C263:D263"/>
+    <mergeCell ref="C264:D264"/>
+    <mergeCell ref="C265:D265"/>
+    <mergeCell ref="C266:D266"/>
+    <mergeCell ref="C267:D267"/>
+    <mergeCell ref="C268:D268"/>
+    <mergeCell ref="C269:D269"/>
+    <mergeCell ref="C270:D270"/>
+    <mergeCell ref="C271:D271"/>
+    <mergeCell ref="C272:D272"/>
+    <mergeCell ref="C273:D273"/>
+    <mergeCell ref="C274:D274"/>
+    <mergeCell ref="C275:D275"/>
+    <mergeCell ref="C276:D276"/>
+    <mergeCell ref="C277:D277"/>
+    <mergeCell ref="C278:D278"/>
+    <mergeCell ref="C279:D279"/>
+    <mergeCell ref="C280:D280"/>
+    <mergeCell ref="C281:D281"/>
+    <mergeCell ref="C282:D282"/>
+    <mergeCell ref="C283:D283"/>
+    <mergeCell ref="C284:D284"/>
+    <mergeCell ref="C285:D285"/>
+    <mergeCell ref="C286:D286"/>
+    <mergeCell ref="A313:D313"/>
+    <mergeCell ref="A314:D314"/>
+    <mergeCell ref="A315:D315"/>
+    <mergeCell ref="A316:D316"/>
+    <mergeCell ref="A317:D317"/>
+    <mergeCell ref="A318:D318"/>
+    <mergeCell ref="C287:D287"/>
+    <mergeCell ref="C288:D288"/>
+    <mergeCell ref="C289:D289"/>
+    <mergeCell ref="C290:D290"/>
+    <mergeCell ref="C291:D291"/>
+    <mergeCell ref="C292:D292"/>
+    <mergeCell ref="C293:D293"/>
+    <mergeCell ref="C294:D294"/>
+    <mergeCell ref="C295:D295"/>
+    <mergeCell ref="A337:D337"/>
+    <mergeCell ref="A338:D338"/>
+    <mergeCell ref="A339:D339"/>
+    <mergeCell ref="A340:D340"/>
+    <mergeCell ref="A341:D341"/>
+    <mergeCell ref="A342:D342"/>
+    <mergeCell ref="A343:D343"/>
+    <mergeCell ref="A344:D344"/>
+    <mergeCell ref="C296:D296"/>
+    <mergeCell ref="C297:D297"/>
+    <mergeCell ref="C298:D298"/>
+    <mergeCell ref="C299:D299"/>
+    <mergeCell ref="C300:D300"/>
+    <mergeCell ref="C301:D301"/>
+    <mergeCell ref="A335:D335"/>
+    <mergeCell ref="A303:D303"/>
+    <mergeCell ref="A304:D304"/>
+    <mergeCell ref="A306:C306"/>
+    <mergeCell ref="A307:D307"/>
+    <mergeCell ref="A308:D308"/>
+    <mergeCell ref="A309:D309"/>
+    <mergeCell ref="A310:D310"/>
+    <mergeCell ref="A311:D311"/>
+    <mergeCell ref="A312:D312"/>
     <mergeCell ref="A345:D345"/>
     <mergeCell ref="A346:D346"/>
     <mergeCell ref="A347:D347"/>
@@ -24197,338 +24537,6 @@
     <mergeCell ref="A333:D333"/>
     <mergeCell ref="A334:D334"/>
     <mergeCell ref="A336:D336"/>
-    <mergeCell ref="A337:D337"/>
-    <mergeCell ref="A338:D338"/>
-    <mergeCell ref="A339:D339"/>
-    <mergeCell ref="A340:D340"/>
-    <mergeCell ref="A341:D341"/>
-    <mergeCell ref="A342:D342"/>
-    <mergeCell ref="A343:D343"/>
-    <mergeCell ref="A344:D344"/>
-    <mergeCell ref="C296:D296"/>
-    <mergeCell ref="C297:D297"/>
-    <mergeCell ref="C298:D298"/>
-    <mergeCell ref="C299:D299"/>
-    <mergeCell ref="C300:D300"/>
-    <mergeCell ref="C301:D301"/>
-    <mergeCell ref="A335:D335"/>
-    <mergeCell ref="A303:D303"/>
-    <mergeCell ref="A304:D304"/>
-    <mergeCell ref="A306:C306"/>
-    <mergeCell ref="A307:D307"/>
-    <mergeCell ref="A308:D308"/>
-    <mergeCell ref="A309:D309"/>
-    <mergeCell ref="A310:D310"/>
-    <mergeCell ref="A311:D311"/>
-    <mergeCell ref="A312:D312"/>
-    <mergeCell ref="A313:D313"/>
-    <mergeCell ref="A314:D314"/>
-    <mergeCell ref="A315:D315"/>
-    <mergeCell ref="A316:D316"/>
-    <mergeCell ref="A317:D317"/>
-    <mergeCell ref="A318:D318"/>
-    <mergeCell ref="C287:D287"/>
-    <mergeCell ref="C288:D288"/>
-    <mergeCell ref="C289:D289"/>
-    <mergeCell ref="C290:D290"/>
-    <mergeCell ref="C291:D291"/>
-    <mergeCell ref="C292:D292"/>
-    <mergeCell ref="C293:D293"/>
-    <mergeCell ref="C294:D294"/>
-    <mergeCell ref="C295:D295"/>
-    <mergeCell ref="C278:D278"/>
-    <mergeCell ref="C279:D279"/>
-    <mergeCell ref="C280:D280"/>
-    <mergeCell ref="C281:D281"/>
-    <mergeCell ref="C282:D282"/>
-    <mergeCell ref="C283:D283"/>
-    <mergeCell ref="C284:D284"/>
-    <mergeCell ref="C285:D285"/>
-    <mergeCell ref="C286:D286"/>
-    <mergeCell ref="C269:D269"/>
-    <mergeCell ref="C270:D270"/>
-    <mergeCell ref="C271:D271"/>
-    <mergeCell ref="C272:D272"/>
-    <mergeCell ref="C273:D273"/>
-    <mergeCell ref="C274:D274"/>
-    <mergeCell ref="C275:D275"/>
-    <mergeCell ref="C276:D276"/>
-    <mergeCell ref="C277:D277"/>
-    <mergeCell ref="C260:D260"/>
-    <mergeCell ref="C261:D261"/>
-    <mergeCell ref="C262:D262"/>
-    <mergeCell ref="C263:D263"/>
-    <mergeCell ref="C264:D264"/>
-    <mergeCell ref="C265:D265"/>
-    <mergeCell ref="C266:D266"/>
-    <mergeCell ref="C267:D267"/>
-    <mergeCell ref="C268:D268"/>
-    <mergeCell ref="C251:D251"/>
-    <mergeCell ref="C252:D252"/>
-    <mergeCell ref="C253:D253"/>
-    <mergeCell ref="C254:D254"/>
-    <mergeCell ref="C255:D255"/>
-    <mergeCell ref="C256:D256"/>
-    <mergeCell ref="C257:D257"/>
-    <mergeCell ref="C258:D258"/>
-    <mergeCell ref="C259:D259"/>
-    <mergeCell ref="C242:D242"/>
-    <mergeCell ref="C243:D243"/>
-    <mergeCell ref="C244:D244"/>
-    <mergeCell ref="C245:D245"/>
-    <mergeCell ref="C246:D246"/>
-    <mergeCell ref="C247:D247"/>
-    <mergeCell ref="C248:D248"/>
-    <mergeCell ref="C249:D249"/>
-    <mergeCell ref="C250:D250"/>
-    <mergeCell ref="C233:D233"/>
-    <mergeCell ref="C234:D234"/>
-    <mergeCell ref="C235:D235"/>
-    <mergeCell ref="C236:D236"/>
-    <mergeCell ref="C237:D237"/>
-    <mergeCell ref="C238:D238"/>
-    <mergeCell ref="C239:D239"/>
-    <mergeCell ref="C240:D240"/>
-    <mergeCell ref="C241:D241"/>
-    <mergeCell ref="C224:D224"/>
-    <mergeCell ref="C225:D225"/>
-    <mergeCell ref="C226:D226"/>
-    <mergeCell ref="C227:D227"/>
-    <mergeCell ref="C228:D228"/>
-    <mergeCell ref="C229:D229"/>
-    <mergeCell ref="C230:D230"/>
-    <mergeCell ref="C231:D231"/>
-    <mergeCell ref="C232:D232"/>
-    <mergeCell ref="C215:D215"/>
-    <mergeCell ref="C216:D216"/>
-    <mergeCell ref="C217:D217"/>
-    <mergeCell ref="C218:D218"/>
-    <mergeCell ref="C219:D219"/>
-    <mergeCell ref="C220:D220"/>
-    <mergeCell ref="C221:D221"/>
-    <mergeCell ref="C222:D222"/>
-    <mergeCell ref="C223:D223"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="C208:D208"/>
-    <mergeCell ref="C209:D209"/>
-    <mergeCell ref="C210:D210"/>
-    <mergeCell ref="C211:D211"/>
-    <mergeCell ref="C212:D212"/>
-    <mergeCell ref="C213:D213"/>
-    <mergeCell ref="C214:D214"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="C199:D199"/>
-    <mergeCell ref="C200:D200"/>
-    <mergeCell ref="C201:D201"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="C203:D203"/>
-    <mergeCell ref="C204:D204"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="C188:D188"/>
-    <mergeCell ref="C189:D189"/>
-    <mergeCell ref="C190:D190"/>
-    <mergeCell ref="C191:D191"/>
-    <mergeCell ref="C192:D192"/>
-    <mergeCell ref="C193:D193"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="C179:D179"/>
-    <mergeCell ref="C180:D180"/>
-    <mergeCell ref="C181:D181"/>
-    <mergeCell ref="C182:D182"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="C186:D186"/>
-    <mergeCell ref="C187:D187"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="C173:D173"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C178:D178"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="C163:D163"/>
-    <mergeCell ref="C164:D164"/>
-    <mergeCell ref="C165:D165"/>
-    <mergeCell ref="C166:D166"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="C169:D169"/>
-    <mergeCell ref="C152:D152"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="C157:D157"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C159:D159"/>
-    <mergeCell ref="C160:D160"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="C146:D146"/>
-    <mergeCell ref="C147:D147"/>
-    <mergeCell ref="C148:D148"/>
-    <mergeCell ref="C149:D149"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="C151:D151"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="C121:D121"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24546,116 +24554,116 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:41" x14ac:dyDescent="0.3">
-      <c r="AI2" s="263" t="s">
+      <c r="AI2" s="251" t="s">
         <v>164</v>
       </c>
-      <c r="AJ2" s="263"/>
-      <c r="AK2" s="263"/>
-      <c r="AL2" s="263"/>
-      <c r="AM2" s="263"/>
-      <c r="AN2" s="263" t="s">
+      <c r="AJ2" s="251"/>
+      <c r="AK2" s="251"/>
+      <c r="AL2" s="251"/>
+      <c r="AM2" s="251"/>
+      <c r="AN2" s="251" t="s">
         <v>39</v>
       </c>
-      <c r="AO2" s="263"/>
+      <c r="AO2" s="251"/>
     </row>
     <row r="3" spans="3:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="268" t="s">
+      <c r="C3" s="235" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="271" t="s">
+      <c r="D3" s="238" t="s">
         <v>143</v>
       </c>
-      <c r="E3" s="272"/>
-      <c r="F3" s="272"/>
-      <c r="G3" s="272"/>
-      <c r="H3" s="272"/>
-      <c r="I3" s="272"/>
-      <c r="J3" s="272"/>
-      <c r="K3" s="272"/>
-      <c r="L3" s="272"/>
-      <c r="M3" s="272"/>
-      <c r="N3" s="272"/>
-      <c r="O3" s="272"/>
-      <c r="P3" s="272"/>
-      <c r="Q3" s="272"/>
-      <c r="R3" s="272"/>
-      <c r="S3" s="272"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="272"/>
-      <c r="AA3" s="272"/>
-      <c r="AB3" s="272"/>
-      <c r="AC3" s="272"/>
-      <c r="AD3" s="272"/>
-      <c r="AE3" s="272"/>
-      <c r="AF3" s="272"/>
-      <c r="AG3" s="272"/>
-      <c r="AH3" s="273"/>
-      <c r="AI3" s="277" t="s">
+      <c r="E3" s="239"/>
+      <c r="F3" s="239"/>
+      <c r="G3" s="239"/>
+      <c r="H3" s="239"/>
+      <c r="I3" s="239"/>
+      <c r="J3" s="239"/>
+      <c r="K3" s="239"/>
+      <c r="L3" s="239"/>
+      <c r="M3" s="239"/>
+      <c r="N3" s="239"/>
+      <c r="O3" s="239"/>
+      <c r="P3" s="239"/>
+      <c r="Q3" s="239"/>
+      <c r="R3" s="239"/>
+      <c r="S3" s="239"/>
+      <c r="T3" s="239"/>
+      <c r="U3" s="239"/>
+      <c r="V3" s="239"/>
+      <c r="W3" s="239"/>
+      <c r="X3" s="239"/>
+      <c r="Y3" s="239"/>
+      <c r="Z3" s="239"/>
+      <c r="AA3" s="239"/>
+      <c r="AB3" s="239"/>
+      <c r="AC3" s="239"/>
+      <c r="AD3" s="239"/>
+      <c r="AE3" s="239"/>
+      <c r="AF3" s="239"/>
+      <c r="AG3" s="239"/>
+      <c r="AH3" s="240"/>
+      <c r="AI3" s="244" t="s">
         <v>144</v>
       </c>
-      <c r="AJ3" s="240"/>
-      <c r="AK3" s="279" t="s">
+      <c r="AJ3" s="245"/>
+      <c r="AK3" s="248" t="s">
         <v>145</v>
       </c>
-      <c r="AL3" s="280"/>
-      <c r="AM3" s="281"/>
-      <c r="AN3" s="277" t="s">
+      <c r="AL3" s="249"/>
+      <c r="AM3" s="250"/>
+      <c r="AN3" s="244" t="s">
         <v>144</v>
       </c>
-      <c r="AO3" s="240"/>
+      <c r="AO3" s="245"/>
     </row>
     <row r="4" spans="3:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="269"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="275"/>
-      <c r="F4" s="275"/>
-      <c r="G4" s="275"/>
-      <c r="H4" s="275"/>
-      <c r="I4" s="275"/>
-      <c r="J4" s="275"/>
-      <c r="K4" s="275"/>
-      <c r="L4" s="275"/>
-      <c r="M4" s="275"/>
-      <c r="N4" s="275"/>
-      <c r="O4" s="275"/>
-      <c r="P4" s="275"/>
-      <c r="Q4" s="275"/>
-      <c r="R4" s="275"/>
-      <c r="S4" s="275"/>
-      <c r="T4" s="275"/>
-      <c r="U4" s="275"/>
-      <c r="V4" s="275"/>
-      <c r="W4" s="275"/>
-      <c r="X4" s="275"/>
-      <c r="Y4" s="275"/>
-      <c r="Z4" s="275"/>
-      <c r="AA4" s="275"/>
-      <c r="AB4" s="275"/>
-      <c r="AC4" s="275"/>
-      <c r="AD4" s="275"/>
-      <c r="AE4" s="275"/>
-      <c r="AF4" s="275"/>
-      <c r="AG4" s="275"/>
-      <c r="AH4" s="276"/>
-      <c r="AI4" s="278"/>
-      <c r="AJ4" s="242"/>
-      <c r="AK4" s="264" t="s">
+      <c r="C4" s="236"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
+      <c r="M4" s="242"/>
+      <c r="N4" s="242"/>
+      <c r="O4" s="242"/>
+      <c r="P4" s="242"/>
+      <c r="Q4" s="242"/>
+      <c r="R4" s="242"/>
+      <c r="S4" s="242"/>
+      <c r="T4" s="242"/>
+      <c r="U4" s="242"/>
+      <c r="V4" s="242"/>
+      <c r="W4" s="242"/>
+      <c r="X4" s="242"/>
+      <c r="Y4" s="242"/>
+      <c r="Z4" s="242"/>
+      <c r="AA4" s="242"/>
+      <c r="AB4" s="242"/>
+      <c r="AC4" s="242"/>
+      <c r="AD4" s="242"/>
+      <c r="AE4" s="242"/>
+      <c r="AF4" s="242"/>
+      <c r="AG4" s="242"/>
+      <c r="AH4" s="243"/>
+      <c r="AI4" s="246"/>
+      <c r="AJ4" s="247"/>
+      <c r="AK4" s="252" t="s">
         <v>146</v>
       </c>
-      <c r="AL4" s="265"/>
-      <c r="AM4" s="266" t="s">
+      <c r="AL4" s="253"/>
+      <c r="AM4" s="254" t="s">
         <v>147</v>
       </c>
-      <c r="AN4" s="278"/>
-      <c r="AO4" s="242"/>
+      <c r="AN4" s="246"/>
+      <c r="AO4" s="247"/>
     </row>
     <row r="5" spans="3:41" x14ac:dyDescent="0.3">
-      <c r="C5" s="270"/>
+      <c r="C5" s="237"/>
       <c r="D5" s="76">
         <v>1</v>
       </c>
@@ -24761,7 +24769,7 @@
       <c r="AL5" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="AM5" s="267"/>
+      <c r="AM5" s="255"/>
       <c r="AN5" s="2" t="s">
         <v>156</v>
       </c>
@@ -26280,109 +26288,109 @@
       <c r="C28" t="s">
         <v>173</v>
       </c>
-      <c r="AN28" s="263" t="s">
+      <c r="AN28" s="251" t="s">
         <v>39</v>
       </c>
-      <c r="AO28" s="263"/>
+      <c r="AO28" s="251"/>
     </row>
     <row r="29" spans="3:41" x14ac:dyDescent="0.3">
-      <c r="C29" s="243" t="s">
+      <c r="C29" s="258" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="246" t="s">
+      <c r="D29" s="261" t="s">
         <v>143</v>
       </c>
-      <c r="E29" s="247"/>
-      <c r="F29" s="247"/>
-      <c r="G29" s="247"/>
-      <c r="H29" s="247"/>
-      <c r="I29" s="247"/>
-      <c r="J29" s="247"/>
-      <c r="K29" s="247"/>
-      <c r="L29" s="247"/>
-      <c r="M29" s="247"/>
-      <c r="N29" s="247"/>
-      <c r="O29" s="247"/>
-      <c r="P29" s="247"/>
-      <c r="Q29" s="247"/>
-      <c r="R29" s="247"/>
-      <c r="S29" s="247"/>
-      <c r="T29" s="247"/>
-      <c r="U29" s="247"/>
-      <c r="V29" s="247"/>
-      <c r="W29" s="247"/>
-      <c r="X29" s="247"/>
-      <c r="Y29" s="247"/>
-      <c r="Z29" s="247"/>
-      <c r="AA29" s="247"/>
-      <c r="AB29" s="247"/>
-      <c r="AC29" s="247"/>
-      <c r="AD29" s="247"/>
-      <c r="AE29" s="247"/>
-      <c r="AF29" s="247"/>
-      <c r="AG29" s="247"/>
-      <c r="AH29" s="248"/>
-      <c r="AI29" s="252" t="s">
+      <c r="E29" s="262"/>
+      <c r="F29" s="262"/>
+      <c r="G29" s="262"/>
+      <c r="H29" s="262"/>
+      <c r="I29" s="262"/>
+      <c r="J29" s="262"/>
+      <c r="K29" s="262"/>
+      <c r="L29" s="262"/>
+      <c r="M29" s="262"/>
+      <c r="N29" s="262"/>
+      <c r="O29" s="262"/>
+      <c r="P29" s="262"/>
+      <c r="Q29" s="262"/>
+      <c r="R29" s="262"/>
+      <c r="S29" s="262"/>
+      <c r="T29" s="262"/>
+      <c r="U29" s="262"/>
+      <c r="V29" s="262"/>
+      <c r="W29" s="262"/>
+      <c r="X29" s="262"/>
+      <c r="Y29" s="262"/>
+      <c r="Z29" s="262"/>
+      <c r="AA29" s="262"/>
+      <c r="AB29" s="262"/>
+      <c r="AC29" s="262"/>
+      <c r="AD29" s="262"/>
+      <c r="AE29" s="262"/>
+      <c r="AF29" s="262"/>
+      <c r="AG29" s="262"/>
+      <c r="AH29" s="263"/>
+      <c r="AI29" s="267" t="s">
         <v>144</v>
       </c>
-      <c r="AJ29" s="253"/>
-      <c r="AK29" s="256" t="s">
+      <c r="AJ29" s="268"/>
+      <c r="AK29" s="271" t="s">
         <v>145</v>
       </c>
-      <c r="AL29" s="257"/>
-      <c r="AM29" s="258"/>
-      <c r="AN29" s="239" t="s">
+      <c r="AL29" s="272"/>
+      <c r="AM29" s="273"/>
+      <c r="AN29" s="256" t="s">
         <v>144</v>
       </c>
-      <c r="AO29" s="240"/>
+      <c r="AO29" s="245"/>
     </row>
     <row r="30" spans="3:41" x14ac:dyDescent="0.3">
-      <c r="C30" s="244"/>
-      <c r="D30" s="249"/>
-      <c r="E30" s="250"/>
-      <c r="F30" s="250"/>
-      <c r="G30" s="250"/>
-      <c r="H30" s="250"/>
-      <c r="I30" s="250"/>
-      <c r="J30" s="250"/>
-      <c r="K30" s="250"/>
-      <c r="L30" s="250"/>
-      <c r="M30" s="250"/>
-      <c r="N30" s="250"/>
-      <c r="O30" s="250"/>
-      <c r="P30" s="250"/>
-      <c r="Q30" s="250"/>
-      <c r="R30" s="250"/>
-      <c r="S30" s="250"/>
-      <c r="T30" s="250"/>
-      <c r="U30" s="250"/>
-      <c r="V30" s="250"/>
-      <c r="W30" s="250"/>
-      <c r="X30" s="250"/>
-      <c r="Y30" s="250"/>
-      <c r="Z30" s="250"/>
-      <c r="AA30" s="250"/>
-      <c r="AB30" s="250"/>
-      <c r="AC30" s="250"/>
-      <c r="AD30" s="250"/>
-      <c r="AE30" s="250"/>
-      <c r="AF30" s="250"/>
-      <c r="AG30" s="250"/>
-      <c r="AH30" s="251"/>
-      <c r="AI30" s="254"/>
-      <c r="AJ30" s="255"/>
-      <c r="AK30" s="259" t="s">
+      <c r="C30" s="259"/>
+      <c r="D30" s="264"/>
+      <c r="E30" s="265"/>
+      <c r="F30" s="265"/>
+      <c r="G30" s="265"/>
+      <c r="H30" s="265"/>
+      <c r="I30" s="265"/>
+      <c r="J30" s="265"/>
+      <c r="K30" s="265"/>
+      <c r="L30" s="265"/>
+      <c r="M30" s="265"/>
+      <c r="N30" s="265"/>
+      <c r="O30" s="265"/>
+      <c r="P30" s="265"/>
+      <c r="Q30" s="265"/>
+      <c r="R30" s="265"/>
+      <c r="S30" s="265"/>
+      <c r="T30" s="265"/>
+      <c r="U30" s="265"/>
+      <c r="V30" s="265"/>
+      <c r="W30" s="265"/>
+      <c r="X30" s="265"/>
+      <c r="Y30" s="265"/>
+      <c r="Z30" s="265"/>
+      <c r="AA30" s="265"/>
+      <c r="AB30" s="265"/>
+      <c r="AC30" s="265"/>
+      <c r="AD30" s="265"/>
+      <c r="AE30" s="265"/>
+      <c r="AF30" s="265"/>
+      <c r="AG30" s="265"/>
+      <c r="AH30" s="266"/>
+      <c r="AI30" s="269"/>
+      <c r="AJ30" s="270"/>
+      <c r="AK30" s="274" t="s">
         <v>146</v>
       </c>
-      <c r="AL30" s="260"/>
-      <c r="AM30" s="261" t="s">
+      <c r="AL30" s="275"/>
+      <c r="AM30" s="276" t="s">
         <v>147</v>
       </c>
-      <c r="AN30" s="241"/>
-      <c r="AO30" s="242"/>
+      <c r="AN30" s="257"/>
+      <c r="AO30" s="247"/>
     </row>
     <row r="31" spans="3:41" x14ac:dyDescent="0.3">
-      <c r="C31" s="245"/>
+      <c r="C31" s="260"/>
       <c r="D31" s="76">
         <v>1</v>
       </c>
@@ -26488,7 +26496,7 @@
       <c r="AL31" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="AM31" s="262"/>
+      <c r="AM31" s="277"/>
       <c r="AN31" s="2" t="s">
         <v>156</v>
       </c>
@@ -28006,16 +28014,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="Gb9U3bUL4SsFqB5wHILFGYmhhu3noQsCQzcWrQMWNMr8Kdg1r6B0C3fjzIGSI1EOqWn92wo/lhSK5EvVF3QhVg==" saltValue="J6je12fwHMO7gwNn4A7DIg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="17">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:AH4"/>
-    <mergeCell ref="AI3:AJ4"/>
-    <mergeCell ref="AK3:AM3"/>
-    <mergeCell ref="AN3:AO4"/>
-    <mergeCell ref="AI2:AM2"/>
-    <mergeCell ref="AN2:AO2"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AM4:AM5"/>
-    <mergeCell ref="AN28:AO28"/>
     <mergeCell ref="AN29:AO30"/>
     <mergeCell ref="C29:C31"/>
     <mergeCell ref="D29:AH30"/>
@@ -28023,6 +28021,16 @@
     <mergeCell ref="AK29:AM29"/>
     <mergeCell ref="AK30:AL30"/>
     <mergeCell ref="AM30:AM31"/>
+    <mergeCell ref="AI2:AM2"/>
+    <mergeCell ref="AN2:AO2"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="AN28:AO28"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:AH4"/>
+    <mergeCell ref="AI3:AJ4"/>
+    <mergeCell ref="AK3:AM3"/>
+    <mergeCell ref="AN3:AO4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
